--- a/templates/contracts/vrem_jurnal.xlsx
+++ b/templates/contracts/vrem_jurnal.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\templates\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE87E497-71B7-4E4C-8732-1F2A15375802}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2460CD8D-5BAE-4E98-B341-06AD15AD7AF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="108">
   <si>
     <t xml:space="preserve">ДЕПАРТАМЕНТ ОБРАЗОВАНИЯ И НАУКИ </t>
   </si>
@@ -761,9 +762,6 @@
       <t xml:space="preserve">
 Требования безопасности при проведении занятий по огневой подготовке. Изготовка для стрельбы лежа, порядок заряжания и разряжания оружия.</t>
     </r>
-  </si>
-  <si>
-    <t>{{ROWS}}</t>
   </si>
   <si>
     <t>{{SCHOOL_NAME}}</t>
@@ -2352,7 +2350,7 @@
       <c r="Q19" s="34"/>
       <c r="R19" s="20"/>
       <c r="S19" s="83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T19" s="83"/>
       <c r="U19" s="83"/>
@@ -2406,7 +2404,7 @@
       <c r="Q21" s="34"/>
       <c r="R21" s="20"/>
       <c r="S21" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T21" s="83"/>
       <c r="U21" s="83"/>
@@ -2434,7 +2432,7 @@
       <c r="Q22" s="34"/>
       <c r="R22" s="20"/>
       <c r="S22" s="83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T22" s="83"/>
       <c r="U22" s="83"/>
@@ -2598,7 +2596,7 @@
         <v>6</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
@@ -2623,7 +2621,7 @@
         <v>7</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
@@ -3489,9 +3487,7 @@
       <c r="A65" s="12">
         <v>1</v>
       </c>
-      <c r="B65" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B65" s="54"/>
       <c r="C65" s="55"/>
       <c r="D65" s="55"/>
       <c r="E65" s="55"/>
@@ -4465,7 +4461,7 @@
       </c>
       <c r="T102" s="42"/>
       <c r="U102" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V102" s="43"/>
       <c r="W102" s="41">
@@ -4480,9 +4476,7 @@
       <c r="A103" s="12">
         <v>1</v>
       </c>
-      <c r="B103" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B103" s="54"/>
       <c r="C103" s="55"/>
       <c r="D103" s="55"/>
       <c r="E103" s="55"/>
@@ -4581,7 +4575,7 @@
       <c r="Q106" s="36"/>
       <c r="T106" s="42"/>
       <c r="U106" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V106" s="43"/>
       <c r="W106" s="41">
@@ -5456,7 +5450,7 @@
       </c>
       <c r="T140" s="42"/>
       <c r="U140" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V140" s="43"/>
       <c r="W140" s="41">
@@ -5471,9 +5465,7 @@
       <c r="A141" s="12">
         <v>1</v>
       </c>
-      <c r="B141" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B141" s="54"/>
       <c r="C141" s="55"/>
       <c r="D141" s="55"/>
       <c r="E141" s="55"/>
@@ -6459,7 +6451,7 @@
       </c>
       <c r="T178" s="42"/>
       <c r="U178" s="45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="V178" s="43"/>
       <c r="W178" s="41">
@@ -6474,9 +6466,7 @@
       <c r="A179" s="12">
         <v>1</v>
       </c>
-      <c r="B179" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B179" s="54"/>
       <c r="C179" s="55"/>
       <c r="D179" s="55"/>
       <c r="E179" s="55"/>
@@ -7450,7 +7440,7 @@
       </c>
       <c r="T216" s="42"/>
       <c r="U216" s="69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V216" s="70"/>
       <c r="W216" s="41">
@@ -7465,9 +7455,7 @@
       <c r="A217" s="12">
         <v>1</v>
       </c>
-      <c r="B217" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B217" s="54"/>
       <c r="C217" s="55"/>
       <c r="D217" s="55"/>
       <c r="E217" s="55"/>
@@ -8459,7 +8447,7 @@
       </c>
       <c r="T254" s="42"/>
       <c r="U254" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V254" s="43"/>
       <c r="W254" s="41">
@@ -8474,9 +8462,7 @@
       <c r="A255" s="12">
         <v>1</v>
       </c>
-      <c r="B255" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B255" s="54"/>
       <c r="C255" s="55"/>
       <c r="D255" s="55"/>
       <c r="E255" s="55"/>
@@ -9444,7 +9430,7 @@
       </c>
       <c r="T292" s="42"/>
       <c r="U292" s="45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="V292" s="43"/>
       <c r="W292" s="41">
@@ -9459,9 +9445,7 @@
       <c r="A293" s="12">
         <v>1</v>
       </c>
-      <c r="B293" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B293" s="54"/>
       <c r="C293" s="55"/>
       <c r="D293" s="55"/>
       <c r="E293" s="55"/>
@@ -9614,7 +9598,7 @@
       <c r="Q298" s="36"/>
       <c r="T298" s="42"/>
       <c r="U298" s="45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="V298" s="43"/>
       <c r="W298" s="41">
@@ -10450,9 +10434,7 @@
       <c r="A331" s="12">
         <v>1</v>
       </c>
-      <c r="B331" s="54" t="s">
-        <v>95</v>
-      </c>
+      <c r="B331" s="54"/>
       <c r="C331" s="55"/>
       <c r="D331" s="55"/>
       <c r="E331" s="55"/>
@@ -11992,4 +11974,13 @@
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED5FF723-F28E-4D37-883F-1E824BF23437}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/templates/contracts/vrem_jurnal.xlsx
+++ b/templates/contracts/vrem_jurnal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\templates\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56958DE9-07F5-4677-A633-57AF9BA7539B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5661715-9087-4672-8C8A-2B51B9C2307A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="140">
   <si>
     <t xml:space="preserve">ДЕПАРТАМЕНТ ОБРАЗОВАНИЯ И НАУКИ </t>
   </si>
@@ -979,6 +979,30 @@
   </si>
   <si>
     <t>{{SCORES_USTAVY}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_FIZO}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_STROEVAYA}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_TAKTIKA}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_OGNEVAYA}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_MEDICINA}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_RHBZ}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_BEZOPASNOST}}</t>
+  </si>
+  <si>
+    <t>{{FINAL_USTAVY}}</t>
   </si>
 </sst>
 </file>
@@ -1413,11 +1437,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1457,6 +1481,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1598,12 +1628,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1953,7 +1977,7 @@
     <col min="11" max="11" width="3.140625" style="2" customWidth="1"/>
     <col min="12" max="18" width="3.140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="5.85546875" style="3" customWidth="1"/>
-    <col min="20" max="20" width="4" style="5" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" style="5" customWidth="1"/>
     <col min="21" max="21" width="6.85546875" style="5" customWidth="1"/>
     <col min="22" max="22" width="7.5703125" style="38" customWidth="1"/>
     <col min="23" max="23" width="11" style="1" customWidth="1"/>
@@ -2155,15 +2179,15 @@
       <c r="R10" s="5"/>
       <c r="S10" s="7"/>
       <c r="T10" s="4"/>
-      <c r="U10" s="72" t="s">
+      <c r="U10" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="74"/>
+      <c r="X10" s="74"/>
+      <c r="Y10" s="74"/>
+      <c r="Z10" s="74"/>
+      <c r="AA10" s="74"/>
     </row>
     <row r="11" spans="2:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
@@ -2185,15 +2209,15 @@
       <c r="R11" s="5"/>
       <c r="S11" s="7"/>
       <c r="T11" s="4"/>
-      <c r="U11" s="72" t="s">
+      <c r="U11" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="74"/>
+      <c r="X11" s="74"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="74"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
@@ -2257,15 +2281,15 @@
       <c r="R14" s="5"/>
       <c r="S14" s="7"/>
       <c r="T14" s="4"/>
-      <c r="U14" s="73" t="s">
+      <c r="U14" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="V14" s="73"/>
-      <c r="W14" s="73"/>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="73"/>
-      <c r="Z14" s="73"/>
-      <c r="AA14" s="73"/>
+      <c r="V14" s="75"/>
+      <c r="W14" s="75"/>
+      <c r="X14" s="75"/>
+      <c r="Y14" s="75"/>
+      <c r="Z14" s="75"/>
+      <c r="AA14" s="75"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
@@ -2287,13 +2311,13 @@
       <c r="R15" s="5"/>
       <c r="S15" s="7"/>
       <c r="T15" s="4"/>
-      <c r="U15" s="77"/>
-      <c r="V15" s="77"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="77"/>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="77"/>
+      <c r="U15" s="79"/>
+      <c r="V15" s="79"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="79"/>
+      <c r="Y15" s="79"/>
+      <c r="Z15" s="79"/>
+      <c r="AA15" s="79"/>
     </row>
     <row r="16" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="5"/>
@@ -2315,15 +2339,15 @@
       <c r="R16" s="5"/>
       <c r="S16" s="7"/>
       <c r="T16" s="4"/>
-      <c r="U16" s="74" t="s">
+      <c r="U16" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="74"/>
+      <c r="V16" s="76"/>
+      <c r="W16" s="76"/>
+      <c r="X16" s="76"/>
+      <c r="Y16" s="76"/>
+      <c r="Z16" s="76"/>
+      <c r="AA16" s="76"/>
     </row>
     <row r="17" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
@@ -2345,15 +2369,15 @@
       <c r="R17" s="5"/>
       <c r="S17" s="7"/>
       <c r="T17" s="4"/>
-      <c r="U17" s="74" t="s">
+      <c r="U17" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74"/>
-      <c r="X17" s="74"/>
-      <c r="Y17" s="74"/>
-      <c r="Z17" s="74"/>
-      <c r="AA17" s="74"/>
+      <c r="V17" s="76"/>
+      <c r="W17" s="76"/>
+      <c r="X17" s="76"/>
+      <c r="Y17" s="76"/>
+      <c r="Z17" s="76"/>
+      <c r="AA17" s="76"/>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
@@ -2375,13 +2399,13 @@
       <c r="R18" s="5"/>
       <c r="S18" s="7"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="77"/>
-      <c r="V18" s="77"/>
-      <c r="W18" s="77"/>
-      <c r="X18" s="77"/>
-      <c r="Y18" s="77"/>
-      <c r="Z18" s="77"/>
-      <c r="AA18" s="77"/>
+      <c r="U18" s="79"/>
+      <c r="V18" s="79"/>
+      <c r="W18" s="79"/>
+      <c r="X18" s="79"/>
+      <c r="Y18" s="79"/>
+      <c r="Z18" s="79"/>
+      <c r="AA18" s="79"/>
     </row>
     <row r="19" spans="2:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
@@ -2403,15 +2427,15 @@
       <c r="R19" s="5"/>
       <c r="S19" s="7"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="71" t="s">
+      <c r="U19" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="V19" s="71"/>
-      <c r="W19" s="71"/>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="71"/>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="71"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="73"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="73"/>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
@@ -2433,13 +2457,13 @@
       <c r="R20" s="5"/>
       <c r="S20" s="7"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="77"/>
-      <c r="V20" s="77"/>
-      <c r="W20" s="77"/>
-      <c r="X20" s="77"/>
-      <c r="Y20" s="77"/>
-      <c r="Z20" s="77"/>
-      <c r="AA20" s="77"/>
+      <c r="U20" s="79"/>
+      <c r="V20" s="79"/>
+      <c r="W20" s="79"/>
+      <c r="X20" s="79"/>
+      <c r="Y20" s="79"/>
+      <c r="Z20" s="79"/>
+      <c r="AA20" s="79"/>
     </row>
     <row r="21" spans="2:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
@@ -2461,15 +2485,15 @@
       <c r="R21" s="5"/>
       <c r="S21" s="7"/>
       <c r="T21" s="4"/>
-      <c r="U21" s="71" t="s">
+      <c r="U21" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="V21" s="71"/>
-      <c r="W21" s="71"/>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="71"/>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="71"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="73"/>
     </row>
     <row r="22" spans="2:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
@@ -2491,15 +2515,15 @@
       <c r="R22" s="5"/>
       <c r="S22" s="7"/>
       <c r="T22" s="4"/>
-      <c r="U22" s="71" t="s">
+      <c r="U22" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="V22" s="71"/>
-      <c r="W22" s="71"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="71"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="73"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="73"/>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
@@ -2746,7 +2770,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="T34" s="4"/>
-      <c r="U34" s="77"/>
+      <c r="U34" s="79"/>
       <c r="V34" s="55"/>
       <c r="W34" s="55"/>
       <c r="X34" s="55"/>
@@ -2775,7 +2799,7 @@
       <c r="R35" s="55"/>
       <c r="S35" s="55"/>
       <c r="T35" s="56"/>
-      <c r="U35" s="77" t="s">
+      <c r="U35" s="79" t="s">
         <v>5</v>
       </c>
       <c r="V35" s="55"/>
@@ -2812,57 +2836,57 @@
       <c r="AA36" s="2"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
+      <c r="R37" s="59"/>
+      <c r="S37" s="59"/>
       <c r="T37" s="11"/>
-      <c r="V37" s="57" t="s">
+      <c r="V37" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="W37" s="57"/>
-      <c r="X37" s="57"/>
-      <c r="Y37" s="57"/>
-      <c r="Z37" s="57"/>
-      <c r="AA37" s="57"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="59"/>
+      <c r="Y37" s="59"/>
+      <c r="Z37" s="59"/>
+      <c r="AA37" s="59"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="57"/>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="59"/>
+      <c r="R38" s="59"/>
+      <c r="S38" s="59"/>
       <c r="T38" s="11"/>
     </row>
     <row r="39" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2892,10 +2916,10 @@
       <c r="V39" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W39" s="75" t="s">
+      <c r="W39" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="X39" s="76"/>
+      <c r="X39" s="78"/>
       <c r="Y39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2930,21 +2954,21 @@
       <c r="P40" s="51"/>
       <c r="Q40" s="51"/>
       <c r="R40" s="51"/>
-      <c r="V40" s="69" t="str">
+      <c r="V40" s="71" t="str">
         <f>IF(K64="","",K64)</f>
         <v>{{DATES_FIZO}}</v>
       </c>
-      <c r="W40" s="68" t="s">
+      <c r="W40" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="X40" s="68"/>
-      <c r="Y40" s="69">
+      <c r="X40" s="70"/>
+      <c r="Y40" s="71">
         <v>1</v>
       </c>
-      <c r="Z40" s="70" t="s">
+      <c r="Z40" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AA40" s="79"/>
+      <c r="AA40" s="81"/>
     </row>
     <row r="41" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="51" t="s">
@@ -2970,12 +2994,12 @@
       <c r="P41" s="51"/>
       <c r="Q41" s="51"/>
       <c r="R41" s="51"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="68"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="70"/>
-      <c r="AA41" s="79"/>
+      <c r="V41" s="71"/>
+      <c r="W41" s="70"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="71"/>
+      <c r="Z41" s="72"/>
+      <c r="AA41" s="81"/>
     </row>
     <row r="42" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="51" t="s">
@@ -3001,12 +3025,12 @@
       <c r="P42" s="51"/>
       <c r="Q42" s="51"/>
       <c r="R42" s="51"/>
-      <c r="V42" s="69"/>
-      <c r="W42" s="68"/>
-      <c r="X42" s="68"/>
-      <c r="Y42" s="69"/>
-      <c r="Z42" s="70"/>
-      <c r="AA42" s="79"/>
+      <c r="V42" s="71"/>
+      <c r="W42" s="70"/>
+      <c r="X42" s="70"/>
+      <c r="Y42" s="71"/>
+      <c r="Z42" s="72"/>
+      <c r="AA42" s="81"/>
     </row>
     <row r="43" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="51" t="s">
@@ -3032,21 +3056,21 @@
       <c r="P43" s="51"/>
       <c r="Q43" s="51"/>
       <c r="R43" s="51"/>
-      <c r="V43" s="69" t="str">
+      <c r="V43" s="71" t="str">
         <f>IF(L64="","",L64)</f>
         <v/>
       </c>
-      <c r="W43" s="68" t="s">
+      <c r="W43" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="X43" s="68"/>
-      <c r="Y43" s="69">
+      <c r="X43" s="70"/>
+      <c r="Y43" s="71">
         <v>1</v>
       </c>
-      <c r="Z43" s="70" t="s">
+      <c r="Z43" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="AA43" s="79"/>
+      <c r="AA43" s="81"/>
     </row>
     <row r="44" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="51" t="s">
@@ -3072,12 +3096,12 @@
       <c r="P44" s="51"/>
       <c r="Q44" s="51"/>
       <c r="R44" s="51"/>
-      <c r="V44" s="69"/>
-      <c r="W44" s="68"/>
-      <c r="X44" s="68"/>
-      <c r="Y44" s="69"/>
-      <c r="Z44" s="70"/>
-      <c r="AA44" s="79"/>
+      <c r="V44" s="71"/>
+      <c r="W44" s="70"/>
+      <c r="X44" s="70"/>
+      <c r="Y44" s="71"/>
+      <c r="Z44" s="72"/>
+      <c r="AA44" s="81"/>
     </row>
     <row r="45" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="51" t="s">
@@ -3103,12 +3127,12 @@
       <c r="P45" s="51"/>
       <c r="Q45" s="51"/>
       <c r="R45" s="51"/>
-      <c r="V45" s="69"/>
-      <c r="W45" s="68"/>
-      <c r="X45" s="68"/>
-      <c r="Y45" s="69"/>
-      <c r="Z45" s="70"/>
-      <c r="AA45" s="79"/>
+      <c r="V45" s="71"/>
+      <c r="W45" s="70"/>
+      <c r="X45" s="70"/>
+      <c r="Y45" s="71"/>
+      <c r="Z45" s="72"/>
+      <c r="AA45" s="81"/>
     </row>
     <row r="46" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="51" t="s">
@@ -3134,21 +3158,21 @@
       <c r="P46" s="51"/>
       <c r="Q46" s="51"/>
       <c r="R46" s="51"/>
-      <c r="V46" s="69" t="str">
+      <c r="V46" s="71" t="str">
         <f>IF(M64="","",M64)</f>
         <v/>
       </c>
-      <c r="W46" s="68" t="s">
+      <c r="W46" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="X46" s="68"/>
-      <c r="Y46" s="69">
+      <c r="X46" s="70"/>
+      <c r="Y46" s="71">
         <v>1</v>
       </c>
-      <c r="Z46" s="70" t="s">
+      <c r="Z46" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="AA46" s="79"/>
+      <c r="AA46" s="81"/>
     </row>
     <row r="47" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14"/>
@@ -3171,12 +3195,12 @@
       <c r="R47" s="14"/>
       <c r="S47" s="7"/>
       <c r="T47" s="14"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="68"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="69"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="79"/>
+      <c r="V47" s="71"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="71"/>
+      <c r="Z47" s="72"/>
+      <c r="AA47" s="81"/>
     </row>
     <row r="48" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="50" t="s">
@@ -3202,12 +3226,12 @@
       <c r="R48" s="14"/>
       <c r="S48" s="7"/>
       <c r="T48" s="14"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="68"/>
-      <c r="X48" s="68"/>
-      <c r="Y48" s="69"/>
-      <c r="Z48" s="70"/>
-      <c r="AA48" s="79"/>
+      <c r="V48" s="71"/>
+      <c r="W48" s="70"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="72"/>
+      <c r="AA48" s="81"/>
     </row>
     <row r="49" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="51" t="s">
@@ -3233,12 +3257,12 @@
       <c r="R49" s="14"/>
       <c r="S49" s="7"/>
       <c r="T49" s="14"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="68"/>
-      <c r="X49" s="68"/>
-      <c r="Y49" s="69"/>
-      <c r="Z49" s="70"/>
-      <c r="AA49" s="79"/>
+      <c r="V49" s="71"/>
+      <c r="W49" s="70"/>
+      <c r="X49" s="70"/>
+      <c r="Y49" s="71"/>
+      <c r="Z49" s="72"/>
+      <c r="AA49" s="81"/>
     </row>
     <row r="50" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="51" t="s">
@@ -3261,12 +3285,12 @@
       <c r="R50" s="16"/>
       <c r="S50" s="7"/>
       <c r="T50" s="14"/>
-      <c r="V50" s="69"/>
-      <c r="W50" s="68"/>
-      <c r="X50" s="68"/>
-      <c r="Y50" s="69"/>
-      <c r="Z50" s="70"/>
-      <c r="AA50" s="79"/>
+      <c r="V50" s="71"/>
+      <c r="W50" s="70"/>
+      <c r="X50" s="70"/>
+      <c r="Y50" s="71"/>
+      <c r="Z50" s="72"/>
+      <c r="AA50" s="81"/>
     </row>
     <row r="51" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="51" t="s">
@@ -3289,21 +3313,21 @@
       <c r="R51" s="16"/>
       <c r="S51" s="7"/>
       <c r="T51" s="14"/>
-      <c r="V51" s="69" t="str">
+      <c r="V51" s="71" t="str">
         <f>IF(N64="","",N64)</f>
         <v/>
       </c>
-      <c r="W51" s="68" t="s">
+      <c r="W51" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="X51" s="68"/>
-      <c r="Y51" s="69">
+      <c r="X51" s="70"/>
+      <c r="Y51" s="71">
         <v>1</v>
       </c>
-      <c r="Z51" s="70" t="s">
+      <c r="Z51" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="AA51" s="79"/>
+      <c r="AA51" s="81"/>
     </row>
     <row r="52" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="51" t="s">
@@ -3326,12 +3350,12 @@
       <c r="R52" s="16"/>
       <c r="S52" s="7"/>
       <c r="T52" s="14"/>
-      <c r="V52" s="69"/>
-      <c r="W52" s="68"/>
-      <c r="X52" s="68"/>
-      <c r="Y52" s="69"/>
-      <c r="Z52" s="70"/>
-      <c r="AA52" s="79"/>
+      <c r="V52" s="71"/>
+      <c r="W52" s="70"/>
+      <c r="X52" s="70"/>
+      <c r="Y52" s="71"/>
+      <c r="Z52" s="72"/>
+      <c r="AA52" s="81"/>
     </row>
     <row r="53" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="51" t="s">
@@ -3354,12 +3378,12 @@
       <c r="R53" s="16"/>
       <c r="S53" s="7"/>
       <c r="T53" s="14"/>
-      <c r="V53" s="69"/>
-      <c r="W53" s="68"/>
-      <c r="X53" s="68"/>
-      <c r="Y53" s="69"/>
-      <c r="Z53" s="70"/>
-      <c r="AA53" s="79"/>
+      <c r="V53" s="71"/>
+      <c r="W53" s="70"/>
+      <c r="X53" s="70"/>
+      <c r="Y53" s="71"/>
+      <c r="Z53" s="72"/>
+      <c r="AA53" s="81"/>
     </row>
     <row r="54" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="51" t="s">
@@ -3382,21 +3406,21 @@
       <c r="R54" s="16"/>
       <c r="S54" s="7"/>
       <c r="T54" s="14"/>
-      <c r="V54" s="69" t="str">
+      <c r="V54" s="71" t="str">
         <f>IF(O64="","",O64)</f>
         <v/>
       </c>
-      <c r="W54" s="68" t="s">
+      <c r="W54" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="X54" s="68"/>
-      <c r="Y54" s="69">
+      <c r="X54" s="70"/>
+      <c r="Y54" s="71">
         <v>1</v>
       </c>
-      <c r="Z54" s="70" t="s">
+      <c r="Z54" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AA54" s="79"/>
+      <c r="AA54" s="81"/>
     </row>
     <row r="55" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="51" t="s">
@@ -3419,12 +3443,12 @@
       <c r="R55" s="16"/>
       <c r="S55" s="7"/>
       <c r="T55" s="14"/>
-      <c r="V55" s="69"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="68"/>
-      <c r="Y55" s="69"/>
-      <c r="Z55" s="70"/>
-      <c r="AA55" s="79"/>
+      <c r="V55" s="71"/>
+      <c r="W55" s="70"/>
+      <c r="X55" s="70"/>
+      <c r="Y55" s="71"/>
+      <c r="Z55" s="72"/>
+      <c r="AA55" s="81"/>
     </row>
     <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="17"/>
@@ -3459,12 +3483,12 @@
       <c r="N57" s="17"/>
       <c r="R57" s="21"/>
       <c r="S57" s="7"/>
-      <c r="X57" s="78" t="s">
+      <c r="X57" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="Y57" s="78"/>
-      <c r="Z57" s="78"/>
-      <c r="AA57" s="78"/>
+      <c r="Y57" s="80"/>
+      <c r="Z57" s="80"/>
+      <c r="AA57" s="80"/>
     </row>
     <row r="58" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I58" s="21"/>
@@ -3475,10 +3499,10 @@
       <c r="N58" s="17"/>
       <c r="R58" s="21"/>
       <c r="S58" s="7"/>
-      <c r="X58" s="78"/>
-      <c r="Y58" s="78"/>
-      <c r="Z58" s="78"/>
-      <c r="AA58" s="78"/>
+      <c r="X58" s="80"/>
+      <c r="Y58" s="80"/>
+      <c r="Z58" s="80"/>
+      <c r="AA58" s="80"/>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
@@ -3500,51 +3524,51 @@
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="7"/>
-      <c r="X59" s="78"/>
-      <c r="Y59" s="78"/>
-      <c r="Z59" s="78"/>
-      <c r="AA59" s="78"/>
+      <c r="X59" s="80"/>
+      <c r="Y59" s="80"/>
+      <c r="Z59" s="80"/>
+      <c r="AA59" s="80"/>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K60" s="23">
         <v>1</v>
       </c>
-      <c r="X60" s="78"/>
-      <c r="Y60" s="78"/>
-      <c r="Z60" s="78"/>
-      <c r="AA60" s="78"/>
+      <c r="X60" s="80"/>
+      <c r="Y60" s="80"/>
+      <c r="Z60" s="80"/>
+      <c r="AA60" s="80"/>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="81" t="s">
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="82"/>
+      <c r="F61" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="G61" s="81"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="81"/>
-      <c r="K61" s="81"/>
-      <c r="L61" s="81"/>
-      <c r="M61" s="81"/>
-      <c r="N61" s="81"/>
-      <c r="O61" s="81"/>
-      <c r="P61" s="81"/>
-      <c r="Q61" s="81"/>
-      <c r="R61" s="81"/>
-      <c r="S61" s="81"/>
-      <c r="T61" s="81"/>
+      <c r="G61" s="83"/>
+      <c r="H61" s="83"/>
+      <c r="I61" s="83"/>
+      <c r="J61" s="83"/>
+      <c r="K61" s="83"/>
+      <c r="L61" s="83"/>
+      <c r="M61" s="83"/>
+      <c r="N61" s="83"/>
+      <c r="O61" s="83"/>
+      <c r="P61" s="83"/>
+      <c r="Q61" s="83"/>
+      <c r="R61" s="83"/>
+      <c r="S61" s="83"/>
+      <c r="T61" s="83"/>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="Z62" s="5"/>
     </row>
     <row r="63" spans="1:27" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="104" t="s">
+      <c r="A63" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B63" s="44" t="s">
@@ -3573,17 +3597,17 @@
       <c r="V63" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="W63" s="66" t="s">
+      <c r="W63" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="X63" s="67"/>
-      <c r="Y63" s="66" t="s">
+      <c r="X63" s="69"/>
+      <c r="Y63" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="Z63" s="67"/>
+      <c r="Z63" s="69"/>
     </row>
     <row r="64" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="105"/>
+      <c r="A64" s="43"/>
       <c r="B64" s="47"/>
       <c r="C64" s="48"/>
       <c r="D64" s="48"/>
@@ -3606,17 +3630,17 @@
       <c r="S64" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V64" s="42">
+      <c r="V64" s="57">
         <v>1</v>
       </c>
-      <c r="W64" s="62" t="s">
+      <c r="W64" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="X64" s="63"/>
-      <c r="Y64" s="58">
+      <c r="X64" s="65"/>
+      <c r="Y64" s="60">
         <v>3</v>
       </c>
-      <c r="Z64" s="59"/>
+      <c r="Z64" s="61"/>
     </row>
     <row r="65" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26">
@@ -3643,12 +3667,14 @@
       <c r="P65" s="25"/>
       <c r="Q65" s="25"/>
       <c r="R65" s="25"/>
-      <c r="S65" s="27"/>
-      <c r="V65" s="43"/>
-      <c r="W65" s="64"/>
-      <c r="X65" s="65"/>
-      <c r="Y65" s="60"/>
-      <c r="Z65" s="61"/>
+      <c r="S65" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="V65" s="58"/>
+      <c r="W65" s="66"/>
+      <c r="X65" s="67"/>
+      <c r="Y65" s="62"/>
+      <c r="Z65" s="63"/>
     </row>
     <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
@@ -3672,17 +3698,17 @@
       <c r="Q66" s="25"/>
       <c r="R66" s="25"/>
       <c r="S66" s="27"/>
-      <c r="V66" s="42">
+      <c r="V66" s="57">
         <v>2</v>
       </c>
-      <c r="W66" s="62" t="s">
+      <c r="W66" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="X66" s="63"/>
-      <c r="Y66" s="58">
+      <c r="X66" s="65"/>
+      <c r="Y66" s="60">
         <v>5</v>
       </c>
-      <c r="Z66" s="59"/>
+      <c r="Z66" s="61"/>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="26">
@@ -3706,11 +3732,11 @@
       <c r="Q67" s="25"/>
       <c r="R67" s="25"/>
       <c r="S67" s="27"/>
-      <c r="V67" s="43"/>
-      <c r="W67" s="64"/>
-      <c r="X67" s="65"/>
-      <c r="Y67" s="60"/>
-      <c r="Z67" s="61"/>
+      <c r="V67" s="58"/>
+      <c r="W67" s="66"/>
+      <c r="X67" s="67"/>
+      <c r="Y67" s="62"/>
+      <c r="Z67" s="63"/>
     </row>
     <row r="68" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="26">
@@ -3734,17 +3760,17 @@
       <c r="Q68" s="25"/>
       <c r="R68" s="25"/>
       <c r="S68" s="27"/>
-      <c r="V68" s="42">
+      <c r="V68" s="57">
         <v>3</v>
       </c>
-      <c r="W68" s="62" t="s">
+      <c r="W68" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="X68" s="63"/>
-      <c r="Y68" s="58">
+      <c r="X68" s="65"/>
+      <c r="Y68" s="60">
         <v>7</v>
       </c>
-      <c r="Z68" s="59"/>
+      <c r="Z68" s="61"/>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="26">
@@ -3768,11 +3794,11 @@
       <c r="Q69" s="25"/>
       <c r="R69" s="25"/>
       <c r="S69" s="27"/>
-      <c r="V69" s="43"/>
-      <c r="W69" s="64"/>
-      <c r="X69" s="65"/>
-      <c r="Y69" s="60"/>
-      <c r="Z69" s="61"/>
+      <c r="V69" s="58"/>
+      <c r="W69" s="66"/>
+      <c r="X69" s="67"/>
+      <c r="Y69" s="62"/>
+      <c r="Z69" s="63"/>
     </row>
     <row r="70" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26">
@@ -3796,17 +3822,17 @@
       <c r="Q70" s="25"/>
       <c r="R70" s="25"/>
       <c r="S70" s="27"/>
-      <c r="V70" s="42">
+      <c r="V70" s="57">
         <v>4</v>
       </c>
-      <c r="W70" s="62" t="s">
+      <c r="W70" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="X70" s="63"/>
-      <c r="Y70" s="58">
+      <c r="X70" s="65"/>
+      <c r="Y70" s="60">
         <v>9</v>
       </c>
-      <c r="Z70" s="59"/>
+      <c r="Z70" s="61"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="26">
@@ -3830,11 +3856,11 @@
       <c r="Q71" s="25"/>
       <c r="R71" s="25"/>
       <c r="S71" s="27"/>
-      <c r="V71" s="43"/>
-      <c r="W71" s="64"/>
-      <c r="X71" s="65"/>
-      <c r="Y71" s="60"/>
-      <c r="Z71" s="61"/>
+      <c r="V71" s="58"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="67"/>
+      <c r="Y71" s="62"/>
+      <c r="Z71" s="63"/>
     </row>
     <row r="72" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="26">
@@ -3858,17 +3884,17 @@
       <c r="Q72" s="25"/>
       <c r="R72" s="25"/>
       <c r="S72" s="27"/>
-      <c r="V72" s="42">
+      <c r="V72" s="57">
         <v>5</v>
       </c>
-      <c r="W72" s="62" t="s">
+      <c r="W72" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="X72" s="63"/>
-      <c r="Y72" s="58">
+      <c r="X72" s="65"/>
+      <c r="Y72" s="60">
         <v>11</v>
       </c>
-      <c r="Z72" s="59"/>
+      <c r="Z72" s="61"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="26">
@@ -3892,11 +3918,11 @@
       <c r="Q73" s="25"/>
       <c r="R73" s="25"/>
       <c r="S73" s="27"/>
-      <c r="V73" s="43"/>
-      <c r="W73" s="64"/>
-      <c r="X73" s="65"/>
-      <c r="Y73" s="60"/>
-      <c r="Z73" s="61"/>
+      <c r="V73" s="58"/>
+      <c r="W73" s="66"/>
+      <c r="X73" s="67"/>
+      <c r="Y73" s="62"/>
+      <c r="Z73" s="63"/>
     </row>
     <row r="74" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="26">
@@ -3920,17 +3946,17 @@
       <c r="Q74" s="25"/>
       <c r="R74" s="25"/>
       <c r="S74" s="27"/>
-      <c r="V74" s="42">
+      <c r="V74" s="57">
         <v>6</v>
       </c>
-      <c r="W74" s="62" t="s">
+      <c r="W74" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="X74" s="63"/>
-      <c r="Y74" s="58">
+      <c r="X74" s="65"/>
+      <c r="Y74" s="60">
         <v>13</v>
       </c>
-      <c r="Z74" s="59"/>
+      <c r="Z74" s="61"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="26">
@@ -3954,11 +3980,11 @@
       <c r="Q75" s="25"/>
       <c r="R75" s="25"/>
       <c r="S75" s="27"/>
-      <c r="V75" s="43"/>
-      <c r="W75" s="64"/>
-      <c r="X75" s="65"/>
-      <c r="Y75" s="60"/>
-      <c r="Z75" s="61"/>
+      <c r="V75" s="58"/>
+      <c r="W75" s="66"/>
+      <c r="X75" s="67"/>
+      <c r="Y75" s="62"/>
+      <c r="Z75" s="63"/>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="26">
@@ -3982,17 +4008,17 @@
       <c r="Q76" s="25"/>
       <c r="R76" s="25"/>
       <c r="S76" s="27"/>
-      <c r="V76" s="42">
+      <c r="V76" s="57">
         <v>7</v>
       </c>
-      <c r="W76" s="62" t="s">
+      <c r="W76" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="X76" s="63"/>
-      <c r="Y76" s="58">
+      <c r="X76" s="65"/>
+      <c r="Y76" s="60">
         <v>15</v>
       </c>
-      <c r="Z76" s="59"/>
+      <c r="Z76" s="61"/>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="26">
@@ -4016,11 +4042,11 @@
       <c r="Q77" s="25"/>
       <c r="R77" s="25"/>
       <c r="S77" s="27"/>
-      <c r="V77" s="43"/>
-      <c r="W77" s="64"/>
-      <c r="X77" s="65"/>
-      <c r="Y77" s="60"/>
-      <c r="Z77" s="61"/>
+      <c r="V77" s="58"/>
+      <c r="W77" s="66"/>
+      <c r="X77" s="67"/>
+      <c r="Y77" s="62"/>
+      <c r="Z77" s="63"/>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="26">
@@ -4044,17 +4070,17 @@
       <c r="Q78" s="25"/>
       <c r="R78" s="25"/>
       <c r="S78" s="27"/>
-      <c r="V78" s="42">
+      <c r="V78" s="57">
         <v>8</v>
       </c>
-      <c r="W78" s="62" t="s">
+      <c r="W78" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="X78" s="63"/>
-      <c r="Y78" s="58">
+      <c r="X78" s="65"/>
+      <c r="Y78" s="60">
         <v>17</v>
       </c>
-      <c r="Z78" s="59"/>
+      <c r="Z78" s="61"/>
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
@@ -4078,11 +4104,11 @@
       <c r="Q79" s="25"/>
       <c r="R79" s="25"/>
       <c r="S79" s="27"/>
-      <c r="V79" s="43"/>
-      <c r="W79" s="64"/>
-      <c r="X79" s="65"/>
-      <c r="Y79" s="60"/>
-      <c r="Z79" s="61"/>
+      <c r="V79" s="58"/>
+      <c r="W79" s="66"/>
+      <c r="X79" s="67"/>
+      <c r="Y79" s="62"/>
+      <c r="Z79" s="63"/>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="26">
@@ -4522,15 +4548,15 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="30"/>
-      <c r="B97" s="83"/>
-      <c r="C97" s="83"/>
-      <c r="D97" s="83"/>
-      <c r="E97" s="83"/>
-      <c r="F97" s="83"/>
-      <c r="G97" s="83"/>
-      <c r="H97" s="83"/>
-      <c r="I97" s="83"/>
-      <c r="J97" s="83"/>
+      <c r="B97" s="85"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="85"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="85"/>
+      <c r="I97" s="85"/>
+      <c r="J97" s="85"/>
       <c r="K97" s="31">
         <v>17</v>
       </c>
@@ -4569,46 +4595,46 @@
       <c r="X98" s="23"/>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A99" s="80" t="s">
+      <c r="A99" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B99" s="80"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="80"/>
-      <c r="E99" s="80"/>
-      <c r="F99" s="81" t="s">
+      <c r="B99" s="82"/>
+      <c r="C99" s="82"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82"/>
+      <c r="F99" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="G99" s="81"/>
-      <c r="H99" s="81"/>
-      <c r="I99" s="81"/>
-      <c r="J99" s="81"/>
-      <c r="K99" s="81"/>
-      <c r="L99" s="81"/>
-      <c r="M99" s="81"/>
-      <c r="N99" s="81"/>
-      <c r="O99" s="81"/>
-      <c r="P99" s="81"/>
-      <c r="Q99" s="81"/>
-      <c r="R99" s="81"/>
-      <c r="S99" s="81"/>
-      <c r="T99" s="81"/>
+      <c r="G99" s="83"/>
+      <c r="H99" s="83"/>
+      <c r="I99" s="83"/>
+      <c r="J99" s="83"/>
+      <c r="K99" s="83"/>
+      <c r="L99" s="83"/>
+      <c r="M99" s="83"/>
+      <c r="N99" s="83"/>
+      <c r="O99" s="83"/>
+      <c r="P99" s="83"/>
+      <c r="Q99" s="83"/>
+      <c r="R99" s="83"/>
+      <c r="S99" s="83"/>
+      <c r="T99" s="83"/>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F100" s="82"/>
-      <c r="G100" s="82"/>
-      <c r="H100" s="82"/>
-      <c r="V100" s="57" t="s">
+      <c r="F100" s="84"/>
+      <c r="G100" s="84"/>
+      <c r="H100" s="84"/>
+      <c r="V100" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="W100" s="57"/>
-      <c r="X100" s="57"/>
-      <c r="Y100" s="57"/>
-      <c r="Z100" s="57"/>
-      <c r="AA100" s="57"/>
+      <c r="W100" s="59"/>
+      <c r="X100" s="59"/>
+      <c r="Y100" s="59"/>
+      <c r="Z100" s="59"/>
+      <c r="AA100" s="59"/>
     </row>
     <row r="101" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="104" t="s">
+      <c r="A101" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B101" s="44" t="s">
@@ -4636,10 +4662,10 @@
       <c r="V101" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W101" s="75" t="s">
+      <c r="W101" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="X101" s="76"/>
+      <c r="X101" s="78"/>
       <c r="Y101" s="13" t="s">
         <v>38</v>
       </c>
@@ -4651,7 +4677,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A102" s="105"/>
+      <c r="A102" s="43"/>
       <c r="B102" s="47"/>
       <c r="C102" s="48"/>
       <c r="D102" s="48"/>
@@ -4674,21 +4700,21 @@
       <c r="S102" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V102" s="69" t="str">
+      <c r="V102" s="71" t="str">
         <f>IF(K140="","",K140)</f>
         <v>{{DATES_TAKTIKA}}</v>
       </c>
-      <c r="W102" s="68" t="s">
+      <c r="W102" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="X102" s="84"/>
-      <c r="Y102" s="69">
+      <c r="X102" s="86"/>
+      <c r="Y102" s="71">
         <v>1</v>
       </c>
-      <c r="Z102" s="70" t="s">
+      <c r="Z102" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="AA102" s="79"/>
+      <c r="AA102" s="81"/>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="26">
@@ -4715,13 +4741,15 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25"/>
-      <c r="S103" s="27"/>
-      <c r="V103" s="69"/>
-      <c r="W103" s="84"/>
-      <c r="X103" s="84"/>
-      <c r="Y103" s="69"/>
-      <c r="Z103" s="70"/>
-      <c r="AA103" s="79"/>
+      <c r="S103" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="V103" s="71"/>
+      <c r="W103" s="86"/>
+      <c r="X103" s="86"/>
+      <c r="Y103" s="71"/>
+      <c r="Z103" s="72"/>
+      <c r="AA103" s="81"/>
     </row>
     <row r="104" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26">
@@ -4745,12 +4773,12 @@
       <c r="Q104" s="25"/>
       <c r="R104" s="25"/>
       <c r="S104" s="27"/>
-      <c r="V104" s="69"/>
-      <c r="W104" s="84"/>
-      <c r="X104" s="84"/>
-      <c r="Y104" s="69"/>
-      <c r="Z104" s="70"/>
-      <c r="AA104" s="79"/>
+      <c r="V104" s="71"/>
+      <c r="W104" s="86"/>
+      <c r="X104" s="86"/>
+      <c r="Y104" s="71"/>
+      <c r="Z104" s="72"/>
+      <c r="AA104" s="81"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="26">
@@ -4774,12 +4802,12 @@
       <c r="Q105" s="25"/>
       <c r="R105" s="25"/>
       <c r="S105" s="27"/>
-      <c r="V105" s="69"/>
-      <c r="W105" s="84"/>
-      <c r="X105" s="84"/>
-      <c r="Y105" s="69"/>
-      <c r="Z105" s="70"/>
-      <c r="AA105" s="79"/>
+      <c r="V105" s="71"/>
+      <c r="W105" s="86"/>
+      <c r="X105" s="86"/>
+      <c r="Y105" s="71"/>
+      <c r="Z105" s="72"/>
+      <c r="AA105" s="81"/>
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" s="26">
@@ -4803,21 +4831,21 @@
       <c r="Q106" s="25"/>
       <c r="R106" s="25"/>
       <c r="S106" s="27"/>
-      <c r="V106" s="69" t="str">
+      <c r="V106" s="71" t="str">
         <f>IF(L140="","",L140)</f>
         <v/>
       </c>
-      <c r="W106" s="68" t="s">
+      <c r="W106" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="X106" s="84"/>
-      <c r="Y106" s="69">
+      <c r="X106" s="86"/>
+      <c r="Y106" s="71">
         <v>2</v>
       </c>
-      <c r="Z106" s="70" t="s">
+      <c r="Z106" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="AA106" s="79"/>
+      <c r="AA106" s="81"/>
     </row>
     <row r="107" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26">
@@ -4841,12 +4869,12 @@
       <c r="Q107" s="25"/>
       <c r="R107" s="25"/>
       <c r="S107" s="27"/>
-      <c r="V107" s="69"/>
-      <c r="W107" s="84"/>
-      <c r="X107" s="84"/>
-      <c r="Y107" s="69"/>
-      <c r="Z107" s="70"/>
-      <c r="AA107" s="79"/>
+      <c r="V107" s="71"/>
+      <c r="W107" s="86"/>
+      <c r="X107" s="86"/>
+      <c r="Y107" s="71"/>
+      <c r="Z107" s="72"/>
+      <c r="AA107" s="81"/>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" s="26">
@@ -4870,12 +4898,12 @@
       <c r="Q108" s="25"/>
       <c r="R108" s="25"/>
       <c r="S108" s="27"/>
-      <c r="V108" s="69"/>
-      <c r="W108" s="84"/>
-      <c r="X108" s="84"/>
-      <c r="Y108" s="69"/>
-      <c r="Z108" s="70"/>
-      <c r="AA108" s="79"/>
+      <c r="V108" s="71"/>
+      <c r="W108" s="86"/>
+      <c r="X108" s="86"/>
+      <c r="Y108" s="71"/>
+      <c r="Z108" s="72"/>
+      <c r="AA108" s="81"/>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" s="26">
@@ -4899,12 +4927,12 @@
       <c r="Q109" s="25"/>
       <c r="R109" s="25"/>
       <c r="S109" s="27"/>
-      <c r="V109" s="69"/>
-      <c r="W109" s="84"/>
-      <c r="X109" s="84"/>
-      <c r="Y109" s="69"/>
-      <c r="Z109" s="70"/>
-      <c r="AA109" s="79"/>
+      <c r="V109" s="71"/>
+      <c r="W109" s="86"/>
+      <c r="X109" s="86"/>
+      <c r="Y109" s="71"/>
+      <c r="Z109" s="72"/>
+      <c r="AA109" s="81"/>
     </row>
     <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" s="26">
@@ -4928,12 +4956,12 @@
       <c r="Q110" s="25"/>
       <c r="R110" s="25"/>
       <c r="S110" s="27"/>
-      <c r="V110" s="69"/>
-      <c r="W110" s="84"/>
-      <c r="X110" s="84"/>
-      <c r="Y110" s="69"/>
-      <c r="Z110" s="70"/>
-      <c r="AA110" s="79"/>
+      <c r="V110" s="71"/>
+      <c r="W110" s="86"/>
+      <c r="X110" s="86"/>
+      <c r="Y110" s="71"/>
+      <c r="Z110" s="72"/>
+      <c r="AA110" s="81"/>
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" s="26">
@@ -4957,12 +4985,12 @@
       <c r="Q111" s="25"/>
       <c r="R111" s="25"/>
       <c r="S111" s="27"/>
-      <c r="V111" s="69"/>
-      <c r="W111" s="84"/>
-      <c r="X111" s="84"/>
-      <c r="Y111" s="69"/>
-      <c r="Z111" s="70"/>
-      <c r="AA111" s="79"/>
+      <c r="V111" s="71"/>
+      <c r="W111" s="86"/>
+      <c r="X111" s="86"/>
+      <c r="Y111" s="71"/>
+      <c r="Z111" s="72"/>
+      <c r="AA111" s="81"/>
     </row>
     <row r="112" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="26">
@@ -4986,12 +5014,12 @@
       <c r="Q112" s="25"/>
       <c r="R112" s="25"/>
       <c r="S112" s="27"/>
-      <c r="V112" s="69"/>
-      <c r="W112" s="84"/>
-      <c r="X112" s="84"/>
-      <c r="Y112" s="69"/>
-      <c r="Z112" s="70"/>
-      <c r="AA112" s="79"/>
+      <c r="V112" s="71"/>
+      <c r="W112" s="86"/>
+      <c r="X112" s="86"/>
+      <c r="Y112" s="71"/>
+      <c r="Z112" s="72"/>
+      <c r="AA112" s="81"/>
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" s="26">
@@ -5015,12 +5043,12 @@
       <c r="Q113" s="25"/>
       <c r="R113" s="25"/>
       <c r="S113" s="27"/>
-      <c r="V113" s="69"/>
-      <c r="W113" s="84"/>
-      <c r="X113" s="84"/>
-      <c r="Y113" s="69"/>
-      <c r="Z113" s="70"/>
-      <c r="AA113" s="79"/>
+      <c r="V113" s="71"/>
+      <c r="W113" s="86"/>
+      <c r="X113" s="86"/>
+      <c r="Y113" s="71"/>
+      <c r="Z113" s="72"/>
+      <c r="AA113" s="81"/>
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" s="26">
@@ -5044,21 +5072,21 @@
       <c r="Q114" s="25"/>
       <c r="R114" s="25"/>
       <c r="S114" s="27"/>
-      <c r="V114" s="69" t="str">
+      <c r="V114" s="71" t="str">
         <f>IF(M140="","",M140)</f>
         <v/>
       </c>
-      <c r="W114" s="68" t="s">
+      <c r="W114" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="X114" s="84"/>
-      <c r="Y114" s="69">
+      <c r="X114" s="86"/>
+      <c r="Y114" s="71">
         <v>1</v>
       </c>
-      <c r="Z114" s="70" t="s">
+      <c r="Z114" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="AA114" s="79"/>
+      <c r="AA114" s="81"/>
     </row>
     <row r="115" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26">
@@ -5082,12 +5110,12 @@
       <c r="Q115" s="25"/>
       <c r="R115" s="25"/>
       <c r="S115" s="27"/>
-      <c r="V115" s="69"/>
-      <c r="W115" s="84"/>
-      <c r="X115" s="84"/>
-      <c r="Y115" s="69"/>
-      <c r="Z115" s="70"/>
-      <c r="AA115" s="79"/>
+      <c r="V115" s="71"/>
+      <c r="W115" s="86"/>
+      <c r="X115" s="86"/>
+      <c r="Y115" s="71"/>
+      <c r="Z115" s="72"/>
+      <c r="AA115" s="81"/>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" s="26">
@@ -5111,12 +5139,12 @@
       <c r="Q116" s="25"/>
       <c r="R116" s="25"/>
       <c r="S116" s="27"/>
-      <c r="V116" s="69"/>
-      <c r="W116" s="84"/>
-      <c r="X116" s="84"/>
-      <c r="Y116" s="69"/>
-      <c r="Z116" s="70"/>
-      <c r="AA116" s="79"/>
+      <c r="V116" s="71"/>
+      <c r="W116" s="86"/>
+      <c r="X116" s="86"/>
+      <c r="Y116" s="71"/>
+      <c r="Z116" s="72"/>
+      <c r="AA116" s="81"/>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" s="26">
@@ -5140,12 +5168,12 @@
       <c r="Q117" s="25"/>
       <c r="R117" s="25"/>
       <c r="S117" s="27"/>
-      <c r="V117" s="69"/>
-      <c r="W117" s="84"/>
-      <c r="X117" s="84"/>
-      <c r="Y117" s="69"/>
-      <c r="Z117" s="70"/>
-      <c r="AA117" s="79"/>
+      <c r="V117" s="71"/>
+      <c r="W117" s="86"/>
+      <c r="X117" s="86"/>
+      <c r="Y117" s="71"/>
+      <c r="Z117" s="72"/>
+      <c r="AA117" s="81"/>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" s="26">
@@ -5169,12 +5197,12 @@
       <c r="Q118" s="25"/>
       <c r="R118" s="25"/>
       <c r="S118" s="27"/>
-      <c r="V118" s="69"/>
-      <c r="W118" s="84"/>
-      <c r="X118" s="84"/>
-      <c r="Y118" s="69"/>
-      <c r="Z118" s="70"/>
-      <c r="AA118" s="79"/>
+      <c r="V118" s="71"/>
+      <c r="W118" s="86"/>
+      <c r="X118" s="86"/>
+      <c r="Y118" s="71"/>
+      <c r="Z118" s="72"/>
+      <c r="AA118" s="81"/>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" s="26">
@@ -5198,12 +5226,12 @@
       <c r="Q119" s="25"/>
       <c r="R119" s="25"/>
       <c r="S119" s="27"/>
-      <c r="V119" s="69"/>
-      <c r="W119" s="84"/>
-      <c r="X119" s="84"/>
-      <c r="Y119" s="69"/>
-      <c r="Z119" s="70"/>
-      <c r="AA119" s="79"/>
+      <c r="V119" s="71"/>
+      <c r="W119" s="86"/>
+      <c r="X119" s="86"/>
+      <c r="Y119" s="71"/>
+      <c r="Z119" s="72"/>
+      <c r="AA119" s="81"/>
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" s="26">
@@ -5227,12 +5255,12 @@
       <c r="Q120" s="25"/>
       <c r="R120" s="25"/>
       <c r="S120" s="27"/>
-      <c r="V120" s="69"/>
-      <c r="W120" s="84"/>
-      <c r="X120" s="84"/>
-      <c r="Y120" s="69"/>
-      <c r="Z120" s="70"/>
-      <c r="AA120" s="79"/>
+      <c r="V120" s="71"/>
+      <c r="W120" s="86"/>
+      <c r="X120" s="86"/>
+      <c r="Y120" s="71"/>
+      <c r="Z120" s="72"/>
+      <c r="AA120" s="81"/>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" s="26">
@@ -5256,12 +5284,12 @@
       <c r="Q121" s="25"/>
       <c r="R121" s="25"/>
       <c r="S121" s="27"/>
-      <c r="V121" s="69"/>
-      <c r="W121" s="84"/>
-      <c r="X121" s="84"/>
-      <c r="Y121" s="69"/>
-      <c r="Z121" s="70"/>
-      <c r="AA121" s="79"/>
+      <c r="V121" s="71"/>
+      <c r="W121" s="86"/>
+      <c r="X121" s="86"/>
+      <c r="Y121" s="71"/>
+      <c r="Z121" s="72"/>
+      <c r="AA121" s="81"/>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" s="26">
@@ -5285,12 +5313,12 @@
       <c r="Q122" s="25"/>
       <c r="R122" s="25"/>
       <c r="S122" s="27"/>
-      <c r="V122" s="69"/>
-      <c r="W122" s="85"/>
-      <c r="X122" s="86"/>
-      <c r="Y122" s="69"/>
-      <c r="Z122" s="79"/>
-      <c r="AA122" s="79"/>
+      <c r="V122" s="71"/>
+      <c r="W122" s="87"/>
+      <c r="X122" s="88"/>
+      <c r="Y122" s="71"/>
+      <c r="Z122" s="81"/>
+      <c r="AA122" s="81"/>
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" s="26">
@@ -5314,12 +5342,12 @@
       <c r="Q123" s="25"/>
       <c r="R123" s="25"/>
       <c r="S123" s="27"/>
-      <c r="V123" s="69"/>
-      <c r="W123" s="87"/>
+      <c r="V123" s="71"/>
+      <c r="W123" s="89"/>
       <c r="X123" s="56"/>
-      <c r="Y123" s="69"/>
-      <c r="Z123" s="79"/>
-      <c r="AA123" s="79"/>
+      <c r="Y123" s="71"/>
+      <c r="Z123" s="81"/>
+      <c r="AA123" s="81"/>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="26">
@@ -5343,12 +5371,12 @@
       <c r="Q124" s="25"/>
       <c r="R124" s="25"/>
       <c r="S124" s="27"/>
-      <c r="V124" s="69"/>
-      <c r="W124" s="87"/>
+      <c r="V124" s="71"/>
+      <c r="W124" s="89"/>
       <c r="X124" s="56"/>
-      <c r="Y124" s="69"/>
-      <c r="Z124" s="79"/>
-      <c r="AA124" s="79"/>
+      <c r="Y124" s="71"/>
+      <c r="Z124" s="81"/>
+      <c r="AA124" s="81"/>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="26">
@@ -5372,12 +5400,12 @@
       <c r="Q125" s="25"/>
       <c r="R125" s="25"/>
       <c r="S125" s="27"/>
-      <c r="V125" s="69"/>
-      <c r="W125" s="88"/>
-      <c r="X125" s="89"/>
-      <c r="Y125" s="69"/>
-      <c r="Z125" s="79"/>
-      <c r="AA125" s="79"/>
+      <c r="V125" s="71"/>
+      <c r="W125" s="90"/>
+      <c r="X125" s="91"/>
+      <c r="Y125" s="71"/>
+      <c r="Z125" s="81"/>
+      <c r="AA125" s="81"/>
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="26">
@@ -5401,12 +5429,12 @@
       <c r="Q126" s="25"/>
       <c r="R126" s="25"/>
       <c r="S126" s="27"/>
-      <c r="V126" s="69"/>
-      <c r="W126" s="85"/>
-      <c r="X126" s="86"/>
-      <c r="Y126" s="69"/>
-      <c r="Z126" s="79"/>
-      <c r="AA126" s="79"/>
+      <c r="V126" s="71"/>
+      <c r="W126" s="87"/>
+      <c r="X126" s="88"/>
+      <c r="Y126" s="71"/>
+      <c r="Z126" s="81"/>
+      <c r="AA126" s="81"/>
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" s="26">
@@ -5430,12 +5458,12 @@
       <c r="Q127" s="25"/>
       <c r="R127" s="25"/>
       <c r="S127" s="27"/>
-      <c r="V127" s="69"/>
-      <c r="W127" s="87"/>
+      <c r="V127" s="71"/>
+      <c r="W127" s="89"/>
       <c r="X127" s="56"/>
-      <c r="Y127" s="69"/>
-      <c r="Z127" s="79"/>
-      <c r="AA127" s="79"/>
+      <c r="Y127" s="71"/>
+      <c r="Z127" s="81"/>
+      <c r="AA127" s="81"/>
     </row>
     <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" s="26">
@@ -5459,12 +5487,12 @@
       <c r="Q128" s="25"/>
       <c r="R128" s="25"/>
       <c r="S128" s="27"/>
-      <c r="V128" s="69"/>
-      <c r="W128" s="87"/>
+      <c r="V128" s="71"/>
+      <c r="W128" s="89"/>
       <c r="X128" s="56"/>
-      <c r="Y128" s="69"/>
-      <c r="Z128" s="79"/>
-      <c r="AA128" s="79"/>
+      <c r="Y128" s="71"/>
+      <c r="Z128" s="81"/>
+      <c r="AA128" s="81"/>
     </row>
     <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" s="26">
@@ -5488,12 +5516,12 @@
       <c r="Q129" s="25"/>
       <c r="R129" s="25"/>
       <c r="S129" s="27"/>
-      <c r="V129" s="69"/>
-      <c r="W129" s="88"/>
-      <c r="X129" s="89"/>
-      <c r="Y129" s="69"/>
-      <c r="Z129" s="79"/>
-      <c r="AA129" s="79"/>
+      <c r="V129" s="71"/>
+      <c r="W129" s="90"/>
+      <c r="X129" s="91"/>
+      <c r="Y129" s="71"/>
+      <c r="Z129" s="81"/>
+      <c r="AA129" s="81"/>
     </row>
     <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" s="26">
@@ -5517,12 +5545,12 @@
       <c r="Q130" s="25"/>
       <c r="R130" s="25"/>
       <c r="S130" s="27"/>
-      <c r="V130" s="69"/>
-      <c r="W130" s="85"/>
-      <c r="X130" s="86"/>
-      <c r="Y130" s="69"/>
-      <c r="Z130" s="79"/>
-      <c r="AA130" s="79"/>
+      <c r="V130" s="71"/>
+      <c r="W130" s="87"/>
+      <c r="X130" s="88"/>
+      <c r="Y130" s="71"/>
+      <c r="Z130" s="81"/>
+      <c r="AA130" s="81"/>
     </row>
     <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" s="26">
@@ -5546,12 +5574,12 @@
       <c r="Q131" s="25"/>
       <c r="R131" s="25"/>
       <c r="S131" s="27"/>
-      <c r="V131" s="69"/>
-      <c r="W131" s="87"/>
+      <c r="V131" s="71"/>
+      <c r="W131" s="89"/>
       <c r="X131" s="56"/>
-      <c r="Y131" s="69"/>
-      <c r="Z131" s="79"/>
-      <c r="AA131" s="79"/>
+      <c r="Y131" s="71"/>
+      <c r="Z131" s="81"/>
+      <c r="AA131" s="81"/>
     </row>
     <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" s="26">
@@ -5575,12 +5603,12 @@
       <c r="Q132" s="25"/>
       <c r="R132" s="25"/>
       <c r="S132" s="27"/>
-      <c r="V132" s="69"/>
-      <c r="W132" s="87"/>
+      <c r="V132" s="71"/>
+      <c r="W132" s="89"/>
       <c r="X132" s="56"/>
-      <c r="Y132" s="69"/>
-      <c r="Z132" s="79"/>
-      <c r="AA132" s="79"/>
+      <c r="Y132" s="71"/>
+      <c r="Z132" s="81"/>
+      <c r="AA132" s="81"/>
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" s="26">
@@ -5604,12 +5632,12 @@
       <c r="Q133" s="25"/>
       <c r="R133" s="25"/>
       <c r="S133" s="27"/>
-      <c r="V133" s="69"/>
-      <c r="W133" s="88"/>
-      <c r="X133" s="89"/>
-      <c r="Y133" s="69"/>
-      <c r="Z133" s="79"/>
-      <c r="AA133" s="79"/>
+      <c r="V133" s="71"/>
+      <c r="W133" s="90"/>
+      <c r="X133" s="91"/>
+      <c r="Y133" s="71"/>
+      <c r="Z133" s="81"/>
+      <c r="AA133" s="81"/>
     </row>
     <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" s="26">
@@ -5643,46 +5671,46 @@
       </c>
     </row>
     <row r="136" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A136" s="80" t="s">
+      <c r="A136" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B136" s="80"/>
-      <c r="C136" s="80"/>
-      <c r="D136" s="80"/>
-      <c r="E136" s="80"/>
-      <c r="F136" s="81" t="s">
+      <c r="B136" s="82"/>
+      <c r="C136" s="82"/>
+      <c r="D136" s="82"/>
+      <c r="E136" s="82"/>
+      <c r="F136" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="G136" s="81"/>
-      <c r="H136" s="81"/>
-      <c r="I136" s="81"/>
-      <c r="J136" s="81"/>
-      <c r="K136" s="81"/>
-      <c r="L136" s="81"/>
-      <c r="M136" s="81"/>
-      <c r="N136" s="81"/>
-      <c r="O136" s="81"/>
-      <c r="P136" s="81"/>
-      <c r="Q136" s="81"/>
-      <c r="R136" s="81"/>
-      <c r="S136" s="81"/>
-      <c r="T136" s="81"/>
+      <c r="G136" s="83"/>
+      <c r="H136" s="83"/>
+      <c r="I136" s="83"/>
+      <c r="J136" s="83"/>
+      <c r="K136" s="83"/>
+      <c r="L136" s="83"/>
+      <c r="M136" s="83"/>
+      <c r="N136" s="83"/>
+      <c r="O136" s="83"/>
+      <c r="P136" s="83"/>
+      <c r="Q136" s="83"/>
+      <c r="R136" s="83"/>
+      <c r="S136" s="83"/>
+      <c r="T136" s="83"/>
     </row>
     <row r="137" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F137" s="82"/>
-      <c r="G137" s="82"/>
-      <c r="H137" s="82"/>
-      <c r="V137" s="57" t="s">
+      <c r="F137" s="84"/>
+      <c r="G137" s="84"/>
+      <c r="H137" s="84"/>
+      <c r="V137" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="W137" s="57"/>
-      <c r="X137" s="57"/>
-      <c r="Y137" s="57"/>
-      <c r="Z137" s="57"/>
-      <c r="AA137" s="57"/>
+      <c r="W137" s="59"/>
+      <c r="X137" s="59"/>
+      <c r="Y137" s="59"/>
+      <c r="Z137" s="59"/>
+      <c r="AA137" s="59"/>
     </row>
     <row r="139" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="104" t="s">
+      <c r="A139" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B139" s="44" t="s">
@@ -5710,10 +5738,10 @@
       <c r="V139" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W139" s="90" t="s">
+      <c r="W139" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X139" s="90"/>
+      <c r="X139" s="92"/>
       <c r="Y139" s="13" t="s">
         <v>38</v>
       </c>
@@ -5725,7 +5753,7 @@
       </c>
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A140" s="105"/>
+      <c r="A140" s="43"/>
       <c r="B140" s="47"/>
       <c r="C140" s="48"/>
       <c r="D140" s="48"/>
@@ -5748,21 +5776,21 @@
       <c r="S140" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V140" s="69" t="str">
+      <c r="V140" s="71" t="str">
         <f>IF(K102="","",K102)</f>
         <v>{{DATES_STROEVAYA}}</v>
       </c>
-      <c r="W140" s="68" t="s">
+      <c r="W140" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="X140" s="84"/>
-      <c r="Y140" s="69">
+      <c r="X140" s="86"/>
+      <c r="Y140" s="71">
         <v>1</v>
       </c>
-      <c r="Z140" s="70" t="s">
+      <c r="Z140" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="AA140" s="79"/>
+      <c r="AA140" s="81"/>
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" s="26">
@@ -5789,13 +5817,15 @@
       <c r="P141" s="25"/>
       <c r="Q141" s="25"/>
       <c r="R141" s="25"/>
-      <c r="S141" s="27"/>
-      <c r="V141" s="69"/>
-      <c r="W141" s="84"/>
-      <c r="X141" s="84"/>
-      <c r="Y141" s="69"/>
-      <c r="Z141" s="70"/>
-      <c r="AA141" s="79"/>
+      <c r="S141" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="V141" s="71"/>
+      <c r="W141" s="86"/>
+      <c r="X141" s="86"/>
+      <c r="Y141" s="71"/>
+      <c r="Z141" s="72"/>
+      <c r="AA141" s="81"/>
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" s="26">
@@ -5819,12 +5849,12 @@
       <c r="Q142" s="25"/>
       <c r="R142" s="25"/>
       <c r="S142" s="27"/>
-      <c r="V142" s="69"/>
-      <c r="W142" s="84"/>
-      <c r="X142" s="84"/>
-      <c r="Y142" s="69"/>
-      <c r="Z142" s="70"/>
-      <c r="AA142" s="79"/>
+      <c r="V142" s="71"/>
+      <c r="W142" s="86"/>
+      <c r="X142" s="86"/>
+      <c r="Y142" s="71"/>
+      <c r="Z142" s="72"/>
+      <c r="AA142" s="81"/>
     </row>
     <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" s="26">
@@ -5848,12 +5878,12 @@
       <c r="Q143" s="25"/>
       <c r="R143" s="25"/>
       <c r="S143" s="27"/>
-      <c r="V143" s="69"/>
-      <c r="W143" s="84"/>
-      <c r="X143" s="84"/>
-      <c r="Y143" s="69"/>
-      <c r="Z143" s="70"/>
-      <c r="AA143" s="79"/>
+      <c r="V143" s="71"/>
+      <c r="W143" s="86"/>
+      <c r="X143" s="86"/>
+      <c r="Y143" s="71"/>
+      <c r="Z143" s="72"/>
+      <c r="AA143" s="81"/>
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" s="26">
@@ -5877,12 +5907,12 @@
       <c r="Q144" s="25"/>
       <c r="R144" s="25"/>
       <c r="S144" s="27"/>
-      <c r="V144" s="69"/>
-      <c r="W144" s="84"/>
-      <c r="X144" s="84"/>
-      <c r="Y144" s="69"/>
-      <c r="Z144" s="70"/>
-      <c r="AA144" s="79"/>
+      <c r="V144" s="71"/>
+      <c r="W144" s="86"/>
+      <c r="X144" s="86"/>
+      <c r="Y144" s="71"/>
+      <c r="Z144" s="72"/>
+      <c r="AA144" s="81"/>
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" s="26">
@@ -5906,12 +5936,12 @@
       <c r="Q145" s="25"/>
       <c r="R145" s="25"/>
       <c r="S145" s="27"/>
-      <c r="V145" s="69"/>
-      <c r="W145" s="84"/>
-      <c r="X145" s="84"/>
-      <c r="Y145" s="69"/>
-      <c r="Z145" s="70"/>
-      <c r="AA145" s="79"/>
+      <c r="V145" s="71"/>
+      <c r="W145" s="86"/>
+      <c r="X145" s="86"/>
+      <c r="Y145" s="71"/>
+      <c r="Z145" s="72"/>
+      <c r="AA145" s="81"/>
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" s="26">
@@ -5935,12 +5965,12 @@
       <c r="Q146" s="25"/>
       <c r="R146" s="25"/>
       <c r="S146" s="27"/>
-      <c r="V146" s="69"/>
-      <c r="W146" s="84"/>
-      <c r="X146" s="84"/>
-      <c r="Y146" s="69"/>
-      <c r="Z146" s="70"/>
-      <c r="AA146" s="79"/>
+      <c r="V146" s="71"/>
+      <c r="W146" s="86"/>
+      <c r="X146" s="86"/>
+      <c r="Y146" s="71"/>
+      <c r="Z146" s="72"/>
+      <c r="AA146" s="81"/>
     </row>
     <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" s="26">
@@ -5964,12 +5994,12 @@
       <c r="Q147" s="25"/>
       <c r="R147" s="25"/>
       <c r="S147" s="27"/>
-      <c r="V147" s="69"/>
-      <c r="W147" s="84"/>
-      <c r="X147" s="84"/>
-      <c r="Y147" s="69"/>
-      <c r="Z147" s="70"/>
-      <c r="AA147" s="79"/>
+      <c r="V147" s="71"/>
+      <c r="W147" s="86"/>
+      <c r="X147" s="86"/>
+      <c r="Y147" s="71"/>
+      <c r="Z147" s="72"/>
+      <c r="AA147" s="81"/>
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" s="26">
@@ -5993,12 +6023,12 @@
       <c r="Q148" s="25"/>
       <c r="R148" s="25"/>
       <c r="S148" s="27"/>
-      <c r="V148" s="69"/>
-      <c r="W148" s="84"/>
-      <c r="X148" s="84"/>
-      <c r="Y148" s="69"/>
-      <c r="Z148" s="70"/>
-      <c r="AA148" s="79"/>
+      <c r="V148" s="71"/>
+      <c r="W148" s="86"/>
+      <c r="X148" s="86"/>
+      <c r="Y148" s="71"/>
+      <c r="Z148" s="72"/>
+      <c r="AA148" s="81"/>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" s="26">
@@ -6022,12 +6052,12 @@
       <c r="Q149" s="25"/>
       <c r="R149" s="25"/>
       <c r="S149" s="27"/>
-      <c r="V149" s="69"/>
-      <c r="W149" s="84"/>
-      <c r="X149" s="84"/>
-      <c r="Y149" s="69"/>
-      <c r="Z149" s="70"/>
-      <c r="AA149" s="79"/>
+      <c r="V149" s="71"/>
+      <c r="W149" s="86"/>
+      <c r="X149" s="86"/>
+      <c r="Y149" s="71"/>
+      <c r="Z149" s="72"/>
+      <c r="AA149" s="81"/>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" s="26">
@@ -6051,12 +6081,12 @@
       <c r="Q150" s="25"/>
       <c r="R150" s="25"/>
       <c r="S150" s="27"/>
-      <c r="V150" s="69"/>
-      <c r="W150" s="84"/>
-      <c r="X150" s="84"/>
-      <c r="Y150" s="69"/>
-      <c r="Z150" s="70"/>
-      <c r="AA150" s="79"/>
+      <c r="V150" s="71"/>
+      <c r="W150" s="86"/>
+      <c r="X150" s="86"/>
+      <c r="Y150" s="71"/>
+      <c r="Z150" s="72"/>
+      <c r="AA150" s="81"/>
     </row>
     <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" s="26">
@@ -6080,21 +6110,21 @@
       <c r="Q151" s="25"/>
       <c r="R151" s="25"/>
       <c r="S151" s="27"/>
-      <c r="V151" s="69" t="str">
+      <c r="V151" s="71" t="str">
         <f>IF(L102="","",L102)</f>
         <v/>
       </c>
-      <c r="W151" s="68" t="s">
+      <c r="W151" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="X151" s="84"/>
-      <c r="Y151" s="69">
+      <c r="X151" s="86"/>
+      <c r="Y151" s="71">
         <v>1</v>
       </c>
-      <c r="Z151" s="70" t="s">
+      <c r="Z151" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="AA151" s="79"/>
+      <c r="AA151" s="81"/>
     </row>
     <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" s="26">
@@ -6118,12 +6148,12 @@
       <c r="Q152" s="25"/>
       <c r="R152" s="25"/>
       <c r="S152" s="27"/>
-      <c r="V152" s="69"/>
-      <c r="W152" s="84"/>
-      <c r="X152" s="84"/>
-      <c r="Y152" s="69"/>
-      <c r="Z152" s="70"/>
-      <c r="AA152" s="79"/>
+      <c r="V152" s="71"/>
+      <c r="W152" s="86"/>
+      <c r="X152" s="86"/>
+      <c r="Y152" s="71"/>
+      <c r="Z152" s="72"/>
+      <c r="AA152" s="81"/>
     </row>
     <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" s="26">
@@ -6147,12 +6177,12 @@
       <c r="Q153" s="25"/>
       <c r="R153" s="25"/>
       <c r="S153" s="27"/>
-      <c r="V153" s="69"/>
-      <c r="W153" s="84"/>
-      <c r="X153" s="84"/>
-      <c r="Y153" s="69"/>
-      <c r="Z153" s="70"/>
-      <c r="AA153" s="79"/>
+      <c r="V153" s="71"/>
+      <c r="W153" s="86"/>
+      <c r="X153" s="86"/>
+      <c r="Y153" s="71"/>
+      <c r="Z153" s="72"/>
+      <c r="AA153" s="81"/>
     </row>
     <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" s="26">
@@ -6176,12 +6206,12 @@
       <c r="Q154" s="25"/>
       <c r="R154" s="25"/>
       <c r="S154" s="27"/>
-      <c r="V154" s="69"/>
-      <c r="W154" s="84"/>
-      <c r="X154" s="84"/>
-      <c r="Y154" s="69"/>
-      <c r="Z154" s="70"/>
-      <c r="AA154" s="79"/>
+      <c r="V154" s="71"/>
+      <c r="W154" s="86"/>
+      <c r="X154" s="86"/>
+      <c r="Y154" s="71"/>
+      <c r="Z154" s="72"/>
+      <c r="AA154" s="81"/>
     </row>
     <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" s="26">
@@ -6205,12 +6235,12 @@
       <c r="Q155" s="25"/>
       <c r="R155" s="25"/>
       <c r="S155" s="27"/>
-      <c r="V155" s="69"/>
-      <c r="W155" s="84"/>
-      <c r="X155" s="84"/>
-      <c r="Y155" s="69"/>
-      <c r="Z155" s="70"/>
-      <c r="AA155" s="79"/>
+      <c r="V155" s="71"/>
+      <c r="W155" s="86"/>
+      <c r="X155" s="86"/>
+      <c r="Y155" s="71"/>
+      <c r="Z155" s="72"/>
+      <c r="AA155" s="81"/>
     </row>
     <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" s="26">
@@ -6234,12 +6264,12 @@
       <c r="Q156" s="25"/>
       <c r="R156" s="25"/>
       <c r="S156" s="27"/>
-      <c r="V156" s="69"/>
-      <c r="W156" s="84"/>
-      <c r="X156" s="84"/>
-      <c r="Y156" s="69"/>
-      <c r="Z156" s="70"/>
-      <c r="AA156" s="79"/>
+      <c r="V156" s="71"/>
+      <c r="W156" s="86"/>
+      <c r="X156" s="86"/>
+      <c r="Y156" s="71"/>
+      <c r="Z156" s="72"/>
+      <c r="AA156" s="81"/>
     </row>
     <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" s="26">
@@ -6263,12 +6293,12 @@
       <c r="Q157" s="25"/>
       <c r="R157" s="25"/>
       <c r="S157" s="27"/>
-      <c r="V157" s="69"/>
-      <c r="W157" s="84"/>
-      <c r="X157" s="84"/>
-      <c r="Y157" s="69"/>
-      <c r="Z157" s="70"/>
-      <c r="AA157" s="79"/>
+      <c r="V157" s="71"/>
+      <c r="W157" s="86"/>
+      <c r="X157" s="86"/>
+      <c r="Y157" s="71"/>
+      <c r="Z157" s="72"/>
+      <c r="AA157" s="81"/>
     </row>
     <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" s="26">
@@ -6292,21 +6322,21 @@
       <c r="Q158" s="25"/>
       <c r="R158" s="25"/>
       <c r="S158" s="27"/>
-      <c r="V158" s="69" t="str">
+      <c r="V158" s="71" t="str">
         <f>IF(M102="","",M102)</f>
         <v/>
       </c>
-      <c r="W158" s="68" t="s">
+      <c r="W158" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="X158" s="84"/>
-      <c r="Y158" s="69">
+      <c r="X158" s="86"/>
+      <c r="Y158" s="71">
         <v>1</v>
       </c>
-      <c r="Z158" s="70" t="s">
+      <c r="Z158" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="AA158" s="79"/>
+      <c r="AA158" s="81"/>
     </row>
     <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159" s="26">
@@ -6330,12 +6360,12 @@
       <c r="Q159" s="25"/>
       <c r="R159" s="25"/>
       <c r="S159" s="27"/>
-      <c r="V159" s="69"/>
-      <c r="W159" s="84"/>
-      <c r="X159" s="84"/>
-      <c r="Y159" s="69"/>
-      <c r="Z159" s="70"/>
-      <c r="AA159" s="79"/>
+      <c r="V159" s="71"/>
+      <c r="W159" s="86"/>
+      <c r="X159" s="86"/>
+      <c r="Y159" s="71"/>
+      <c r="Z159" s="72"/>
+      <c r="AA159" s="81"/>
     </row>
     <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160" s="26">
@@ -6359,12 +6389,12 @@
       <c r="Q160" s="25"/>
       <c r="R160" s="25"/>
       <c r="S160" s="27"/>
-      <c r="V160" s="69"/>
-      <c r="W160" s="84"/>
-      <c r="X160" s="84"/>
-      <c r="Y160" s="69"/>
-      <c r="Z160" s="70"/>
-      <c r="AA160" s="79"/>
+      <c r="V160" s="71"/>
+      <c r="W160" s="86"/>
+      <c r="X160" s="86"/>
+      <c r="Y160" s="71"/>
+      <c r="Z160" s="72"/>
+      <c r="AA160" s="81"/>
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" s="26">
@@ -6388,12 +6418,12 @@
       <c r="Q161" s="25"/>
       <c r="R161" s="25"/>
       <c r="S161" s="27"/>
-      <c r="V161" s="69"/>
-      <c r="W161" s="84"/>
-      <c r="X161" s="84"/>
-      <c r="Y161" s="69"/>
-      <c r="Z161" s="70"/>
-      <c r="AA161" s="79"/>
+      <c r="V161" s="71"/>
+      <c r="W161" s="86"/>
+      <c r="X161" s="86"/>
+      <c r="Y161" s="71"/>
+      <c r="Z161" s="72"/>
+      <c r="AA161" s="81"/>
     </row>
     <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" s="26">
@@ -6417,12 +6447,12 @@
       <c r="Q162" s="25"/>
       <c r="R162" s="25"/>
       <c r="S162" s="27"/>
-      <c r="V162" s="69"/>
-      <c r="W162" s="84"/>
-      <c r="X162" s="84"/>
-      <c r="Y162" s="69"/>
-      <c r="Z162" s="70"/>
-      <c r="AA162" s="79"/>
+      <c r="V162" s="71"/>
+      <c r="W162" s="86"/>
+      <c r="X162" s="86"/>
+      <c r="Y162" s="71"/>
+      <c r="Z162" s="72"/>
+      <c r="AA162" s="81"/>
     </row>
     <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" s="26">
@@ -6446,12 +6476,12 @@
       <c r="Q163" s="25"/>
       <c r="R163" s="25"/>
       <c r="S163" s="27"/>
-      <c r="V163" s="69"/>
-      <c r="W163" s="84"/>
-      <c r="X163" s="84"/>
-      <c r="Y163" s="69"/>
-      <c r="Z163" s="70"/>
-      <c r="AA163" s="79"/>
+      <c r="V163" s="71"/>
+      <c r="W163" s="86"/>
+      <c r="X163" s="86"/>
+      <c r="Y163" s="71"/>
+      <c r="Z163" s="72"/>
+      <c r="AA163" s="81"/>
     </row>
     <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" s="26">
@@ -6475,12 +6505,12 @@
       <c r="Q164" s="25"/>
       <c r="R164" s="25"/>
       <c r="S164" s="27"/>
-      <c r="V164" s="69"/>
-      <c r="W164" s="84"/>
-      <c r="X164" s="84"/>
-      <c r="Y164" s="69"/>
-      <c r="Z164" s="70"/>
-      <c r="AA164" s="79"/>
+      <c r="V164" s="71"/>
+      <c r="W164" s="86"/>
+      <c r="X164" s="86"/>
+      <c r="Y164" s="71"/>
+      <c r="Z164" s="72"/>
+      <c r="AA164" s="81"/>
     </row>
     <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" s="26">
@@ -6504,12 +6534,12 @@
       <c r="Q165" s="25"/>
       <c r="R165" s="25"/>
       <c r="S165" s="27"/>
-      <c r="V165" s="69"/>
-      <c r="W165" s="84"/>
-      <c r="X165" s="84"/>
-      <c r="Y165" s="69"/>
-      <c r="Z165" s="70"/>
-      <c r="AA165" s="79"/>
+      <c r="V165" s="71"/>
+      <c r="W165" s="86"/>
+      <c r="X165" s="86"/>
+      <c r="Y165" s="71"/>
+      <c r="Z165" s="72"/>
+      <c r="AA165" s="81"/>
     </row>
     <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" s="26">
@@ -6533,21 +6563,21 @@
       <c r="Q166" s="25"/>
       <c r="R166" s="25"/>
       <c r="S166" s="27"/>
-      <c r="V166" s="69" t="str">
+      <c r="V166" s="71" t="str">
         <f>IF(N102="","",N102)</f>
         <v/>
       </c>
-      <c r="W166" s="68" t="s">
+      <c r="W166" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="X166" s="84"/>
-      <c r="Y166" s="69">
+      <c r="X166" s="86"/>
+      <c r="Y166" s="71">
         <v>1</v>
       </c>
-      <c r="Z166" s="70" t="s">
+      <c r="Z166" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="AA166" s="79"/>
+      <c r="AA166" s="81"/>
     </row>
     <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" s="26">
@@ -6571,12 +6601,12 @@
       <c r="Q167" s="25"/>
       <c r="R167" s="25"/>
       <c r="S167" s="27"/>
-      <c r="V167" s="69"/>
-      <c r="W167" s="84"/>
-      <c r="X167" s="84"/>
-      <c r="Y167" s="69"/>
-      <c r="Z167" s="70"/>
-      <c r="AA167" s="79"/>
+      <c r="V167" s="71"/>
+      <c r="W167" s="86"/>
+      <c r="X167" s="86"/>
+      <c r="Y167" s="71"/>
+      <c r="Z167" s="72"/>
+      <c r="AA167" s="81"/>
     </row>
     <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" s="26">
@@ -6600,12 +6630,12 @@
       <c r="Q168" s="25"/>
       <c r="R168" s="25"/>
       <c r="S168" s="27"/>
-      <c r="V168" s="69"/>
-      <c r="W168" s="84"/>
-      <c r="X168" s="84"/>
-      <c r="Y168" s="69"/>
-      <c r="Z168" s="70"/>
-      <c r="AA168" s="79"/>
+      <c r="V168" s="71"/>
+      <c r="W168" s="86"/>
+      <c r="X168" s="86"/>
+      <c r="Y168" s="71"/>
+      <c r="Z168" s="72"/>
+      <c r="AA168" s="81"/>
     </row>
     <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" s="26">
@@ -6629,12 +6659,12 @@
       <c r="Q169" s="25"/>
       <c r="R169" s="25"/>
       <c r="S169" s="27"/>
-      <c r="V169" s="69"/>
-      <c r="W169" s="84"/>
-      <c r="X169" s="84"/>
-      <c r="Y169" s="69"/>
-      <c r="Z169" s="70"/>
-      <c r="AA169" s="79"/>
+      <c r="V169" s="71"/>
+      <c r="W169" s="86"/>
+      <c r="X169" s="86"/>
+      <c r="Y169" s="71"/>
+      <c r="Z169" s="72"/>
+      <c r="AA169" s="81"/>
     </row>
     <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" s="26">
@@ -6658,12 +6688,12 @@
       <c r="Q170" s="25"/>
       <c r="R170" s="25"/>
       <c r="S170" s="27"/>
-      <c r="V170" s="69"/>
-      <c r="W170" s="84"/>
-      <c r="X170" s="84"/>
-      <c r="Y170" s="69"/>
-      <c r="Z170" s="70"/>
-      <c r="AA170" s="79"/>
+      <c r="V170" s="71"/>
+      <c r="W170" s="86"/>
+      <c r="X170" s="86"/>
+      <c r="Y170" s="71"/>
+      <c r="Z170" s="72"/>
+      <c r="AA170" s="81"/>
     </row>
     <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" s="26">
@@ -6687,12 +6717,12 @@
       <c r="Q171" s="25"/>
       <c r="R171" s="25"/>
       <c r="S171" s="27"/>
-      <c r="V171" s="69"/>
-      <c r="W171" s="84"/>
-      <c r="X171" s="84"/>
-      <c r="Y171" s="69"/>
-      <c r="Z171" s="70"/>
-      <c r="AA171" s="79"/>
+      <c r="V171" s="71"/>
+      <c r="W171" s="86"/>
+      <c r="X171" s="86"/>
+      <c r="Y171" s="71"/>
+      <c r="Z171" s="72"/>
+      <c r="AA171" s="81"/>
     </row>
     <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" s="26">
@@ -6716,12 +6746,12 @@
       <c r="Q172" s="25"/>
       <c r="R172" s="25"/>
       <c r="S172" s="27"/>
-      <c r="V172" s="69"/>
-      <c r="W172" s="84"/>
-      <c r="X172" s="84"/>
-      <c r="Y172" s="69"/>
-      <c r="Z172" s="70"/>
-      <c r="AA172" s="79"/>
+      <c r="V172" s="71"/>
+      <c r="W172" s="86"/>
+      <c r="X172" s="86"/>
+      <c r="Y172" s="71"/>
+      <c r="Z172" s="72"/>
+      <c r="AA172" s="81"/>
     </row>
     <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K173" s="23">
@@ -6732,46 +6762,46 @@
       </c>
     </row>
     <row r="174" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A174" s="80" t="s">
+      <c r="A174" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B174" s="80"/>
-      <c r="C174" s="80"/>
-      <c r="D174" s="80"/>
-      <c r="E174" s="80"/>
-      <c r="F174" s="81" t="s">
+      <c r="B174" s="82"/>
+      <c r="C174" s="82"/>
+      <c r="D174" s="82"/>
+      <c r="E174" s="82"/>
+      <c r="F174" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="G174" s="81"/>
-      <c r="H174" s="81"/>
-      <c r="I174" s="81"/>
-      <c r="J174" s="81"/>
-      <c r="K174" s="81"/>
-      <c r="L174" s="81"/>
-      <c r="M174" s="81"/>
-      <c r="N174" s="81"/>
-      <c r="O174" s="81"/>
-      <c r="P174" s="81"/>
-      <c r="Q174" s="81"/>
-      <c r="R174" s="81"/>
-      <c r="S174" s="81"/>
-      <c r="T174" s="81"/>
+      <c r="G174" s="83"/>
+      <c r="H174" s="83"/>
+      <c r="I174" s="83"/>
+      <c r="J174" s="83"/>
+      <c r="K174" s="83"/>
+      <c r="L174" s="83"/>
+      <c r="M174" s="83"/>
+      <c r="N174" s="83"/>
+      <c r="O174" s="83"/>
+      <c r="P174" s="83"/>
+      <c r="Q174" s="83"/>
+      <c r="R174" s="83"/>
+      <c r="S174" s="83"/>
+      <c r="T174" s="83"/>
     </row>
     <row r="175" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F175" s="82"/>
-      <c r="G175" s="82"/>
-      <c r="H175" s="82"/>
-      <c r="V175" s="57" t="s">
+      <c r="F175" s="84"/>
+      <c r="G175" s="84"/>
+      <c r="H175" s="84"/>
+      <c r="V175" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="W175" s="57"/>
-      <c r="X175" s="57"/>
-      <c r="Y175" s="57"/>
-      <c r="Z175" s="57"/>
-      <c r="AA175" s="57"/>
+      <c r="W175" s="59"/>
+      <c r="X175" s="59"/>
+      <c r="Y175" s="59"/>
+      <c r="Z175" s="59"/>
+      <c r="AA175" s="59"/>
     </row>
     <row r="177" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="104" t="s">
+      <c r="A177" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B177" s="44" t="s">
@@ -6799,10 +6829,10 @@
       <c r="V177" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W177" s="90" t="s">
+      <c r="W177" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X177" s="90"/>
+      <c r="X177" s="92"/>
       <c r="Y177" s="13" t="s">
         <v>38</v>
       </c>
@@ -6814,7 +6844,7 @@
       </c>
     </row>
     <row r="178" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A178" s="105"/>
+      <c r="A178" s="43"/>
       <c r="B178" s="47"/>
       <c r="C178" s="48"/>
       <c r="D178" s="48"/>
@@ -6837,21 +6867,21 @@
       <c r="S178" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V178" s="69" t="str">
+      <c r="V178" s="71" t="str">
         <f>IF(K216="","",K216)</f>
         <v>{{DATES_MEDICINA}}</v>
       </c>
-      <c r="W178" s="68" t="s">
+      <c r="W178" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="X178" s="84"/>
-      <c r="Y178" s="69">
+      <c r="X178" s="86"/>
+      <c r="Y178" s="71">
         <v>1</v>
       </c>
-      <c r="Z178" s="70" t="s">
+      <c r="Z178" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AA178" s="79"/>
+      <c r="AA178" s="81"/>
     </row>
     <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" s="26">
@@ -6878,13 +6908,15 @@
       <c r="P179" s="25"/>
       <c r="Q179" s="25"/>
       <c r="R179" s="25"/>
-      <c r="S179" s="27"/>
-      <c r="V179" s="69"/>
-      <c r="W179" s="84"/>
-      <c r="X179" s="84"/>
-      <c r="Y179" s="69"/>
-      <c r="Z179" s="70"/>
-      <c r="AA179" s="79"/>
+      <c r="S179" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="V179" s="71"/>
+      <c r="W179" s="86"/>
+      <c r="X179" s="86"/>
+      <c r="Y179" s="71"/>
+      <c r="Z179" s="72"/>
+      <c r="AA179" s="81"/>
     </row>
     <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" s="26">
@@ -6908,12 +6940,12 @@
       <c r="Q180" s="25"/>
       <c r="R180" s="25"/>
       <c r="S180" s="27"/>
-      <c r="V180" s="69"/>
-      <c r="W180" s="84"/>
-      <c r="X180" s="84"/>
-      <c r="Y180" s="69"/>
-      <c r="Z180" s="70"/>
-      <c r="AA180" s="79"/>
+      <c r="V180" s="71"/>
+      <c r="W180" s="86"/>
+      <c r="X180" s="86"/>
+      <c r="Y180" s="71"/>
+      <c r="Z180" s="72"/>
+      <c r="AA180" s="81"/>
     </row>
     <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" s="26">
@@ -6937,12 +6969,12 @@
       <c r="Q181" s="25"/>
       <c r="R181" s="25"/>
       <c r="S181" s="27"/>
-      <c r="V181" s="69"/>
-      <c r="W181" s="84"/>
-      <c r="X181" s="84"/>
-      <c r="Y181" s="69"/>
-      <c r="Z181" s="70"/>
-      <c r="AA181" s="79"/>
+      <c r="V181" s="71"/>
+      <c r="W181" s="86"/>
+      <c r="X181" s="86"/>
+      <c r="Y181" s="71"/>
+      <c r="Z181" s="72"/>
+      <c r="AA181" s="81"/>
     </row>
     <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" s="26">
@@ -6966,12 +6998,12 @@
       <c r="Q182" s="25"/>
       <c r="R182" s="25"/>
       <c r="S182" s="27"/>
-      <c r="V182" s="69"/>
-      <c r="W182" s="84"/>
-      <c r="X182" s="84"/>
-      <c r="Y182" s="69"/>
-      <c r="Z182" s="70"/>
-      <c r="AA182" s="79"/>
+      <c r="V182" s="71"/>
+      <c r="W182" s="86"/>
+      <c r="X182" s="86"/>
+      <c r="Y182" s="71"/>
+      <c r="Z182" s="72"/>
+      <c r="AA182" s="81"/>
     </row>
     <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" s="26">
@@ -6995,12 +7027,12 @@
       <c r="Q183" s="25"/>
       <c r="R183" s="25"/>
       <c r="S183" s="27"/>
-      <c r="V183" s="69"/>
-      <c r="W183" s="84"/>
-      <c r="X183" s="84"/>
-      <c r="Y183" s="69"/>
-      <c r="Z183" s="70"/>
-      <c r="AA183" s="79"/>
+      <c r="V183" s="71"/>
+      <c r="W183" s="86"/>
+      <c r="X183" s="86"/>
+      <c r="Y183" s="71"/>
+      <c r="Z183" s="72"/>
+      <c r="AA183" s="81"/>
     </row>
     <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" s="26">
@@ -7024,12 +7056,12 @@
       <c r="Q184" s="25"/>
       <c r="R184" s="25"/>
       <c r="S184" s="27"/>
-      <c r="V184" s="69"/>
-      <c r="W184" s="84"/>
-      <c r="X184" s="84"/>
-      <c r="Y184" s="69"/>
-      <c r="Z184" s="70"/>
-      <c r="AA184" s="79"/>
+      <c r="V184" s="71"/>
+      <c r="W184" s="86"/>
+      <c r="X184" s="86"/>
+      <c r="Y184" s="71"/>
+      <c r="Z184" s="72"/>
+      <c r="AA184" s="81"/>
     </row>
     <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" s="26">
@@ -7053,12 +7085,12 @@
       <c r="Q185" s="25"/>
       <c r="R185" s="25"/>
       <c r="S185" s="27"/>
-      <c r="V185" s="69"/>
-      <c r="W185" s="84"/>
-      <c r="X185" s="84"/>
-      <c r="Y185" s="69"/>
-      <c r="Z185" s="70"/>
-      <c r="AA185" s="79"/>
+      <c r="V185" s="71"/>
+      <c r="W185" s="86"/>
+      <c r="X185" s="86"/>
+      <c r="Y185" s="71"/>
+      <c r="Z185" s="72"/>
+      <c r="AA185" s="81"/>
     </row>
     <row r="186" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="26">
@@ -7082,21 +7114,21 @@
       <c r="Q186" s="25"/>
       <c r="R186" s="25"/>
       <c r="S186" s="27"/>
-      <c r="V186" s="69" t="str">
+      <c r="V186" s="71" t="str">
         <f>IF(L216="","",L216)</f>
         <v/>
       </c>
-      <c r="W186" s="68" t="s">
+      <c r="W186" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="X186" s="84"/>
-      <c r="Y186" s="69">
+      <c r="X186" s="86"/>
+      <c r="Y186" s="71">
         <v>1</v>
       </c>
-      <c r="Z186" s="91" t="s">
+      <c r="Z186" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="AA186" s="79"/>
+      <c r="AA186" s="81"/>
     </row>
     <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" s="26">
@@ -7120,12 +7152,12 @@
       <c r="Q187" s="25"/>
       <c r="R187" s="25"/>
       <c r="S187" s="27"/>
-      <c r="V187" s="69"/>
-      <c r="W187" s="84"/>
-      <c r="X187" s="84"/>
-      <c r="Y187" s="69"/>
-      <c r="Z187" s="92"/>
-      <c r="AA187" s="79"/>
+      <c r="V187" s="71"/>
+      <c r="W187" s="86"/>
+      <c r="X187" s="86"/>
+      <c r="Y187" s="71"/>
+      <c r="Z187" s="94"/>
+      <c r="AA187" s="81"/>
     </row>
     <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" s="26">
@@ -7149,12 +7181,12 @@
       <c r="Q188" s="25"/>
       <c r="R188" s="25"/>
       <c r="S188" s="27"/>
-      <c r="V188" s="69"/>
-      <c r="W188" s="84"/>
-      <c r="X188" s="84"/>
-      <c r="Y188" s="69"/>
-      <c r="Z188" s="92"/>
-      <c r="AA188" s="79"/>
+      <c r="V188" s="71"/>
+      <c r="W188" s="86"/>
+      <c r="X188" s="86"/>
+      <c r="Y188" s="71"/>
+      <c r="Z188" s="94"/>
+      <c r="AA188" s="81"/>
     </row>
     <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" s="26">
@@ -7178,12 +7210,12 @@
       <c r="Q189" s="25"/>
       <c r="R189" s="25"/>
       <c r="S189" s="27"/>
-      <c r="V189" s="69"/>
-      <c r="W189" s="84"/>
-      <c r="X189" s="84"/>
-      <c r="Y189" s="69"/>
-      <c r="Z189" s="92"/>
-      <c r="AA189" s="79"/>
+      <c r="V189" s="71"/>
+      <c r="W189" s="86"/>
+      <c r="X189" s="86"/>
+      <c r="Y189" s="71"/>
+      <c r="Z189" s="94"/>
+      <c r="AA189" s="81"/>
     </row>
     <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" s="26">
@@ -7207,12 +7239,12 @@
       <c r="Q190" s="25"/>
       <c r="R190" s="25"/>
       <c r="S190" s="27"/>
-      <c r="V190" s="69"/>
-      <c r="W190" s="84"/>
-      <c r="X190" s="84"/>
-      <c r="Y190" s="69"/>
-      <c r="Z190" s="92"/>
-      <c r="AA190" s="79"/>
+      <c r="V190" s="71"/>
+      <c r="W190" s="86"/>
+      <c r="X190" s="86"/>
+      <c r="Y190" s="71"/>
+      <c r="Z190" s="94"/>
+      <c r="AA190" s="81"/>
     </row>
     <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" s="26">
@@ -7236,12 +7268,12 @@
       <c r="Q191" s="25"/>
       <c r="R191" s="25"/>
       <c r="S191" s="27"/>
-      <c r="V191" s="69"/>
-      <c r="W191" s="84"/>
-      <c r="X191" s="84"/>
-      <c r="Y191" s="69"/>
-      <c r="Z191" s="92"/>
-      <c r="AA191" s="79"/>
+      <c r="V191" s="71"/>
+      <c r="W191" s="86"/>
+      <c r="X191" s="86"/>
+      <c r="Y191" s="71"/>
+      <c r="Z191" s="94"/>
+      <c r="AA191" s="81"/>
     </row>
     <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" s="26">
@@ -7265,12 +7297,12 @@
       <c r="Q192" s="25"/>
       <c r="R192" s="25"/>
       <c r="S192" s="27"/>
-      <c r="V192" s="69"/>
-      <c r="W192" s="84"/>
-      <c r="X192" s="84"/>
-      <c r="Y192" s="69"/>
-      <c r="Z192" s="92"/>
-      <c r="AA192" s="79"/>
+      <c r="V192" s="71"/>
+      <c r="W192" s="86"/>
+      <c r="X192" s="86"/>
+      <c r="Y192" s="71"/>
+      <c r="Z192" s="94"/>
+      <c r="AA192" s="81"/>
     </row>
     <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" s="26">
@@ -7294,12 +7326,12 @@
       <c r="Q193" s="25"/>
       <c r="R193" s="25"/>
       <c r="S193" s="27"/>
-      <c r="V193" s="69"/>
-      <c r="W193" s="84"/>
-      <c r="X193" s="84"/>
-      <c r="Y193" s="69"/>
-      <c r="Z193" s="92"/>
-      <c r="AA193" s="79"/>
+      <c r="V193" s="71"/>
+      <c r="W193" s="86"/>
+      <c r="X193" s="86"/>
+      <c r="Y193" s="71"/>
+      <c r="Z193" s="94"/>
+      <c r="AA193" s="81"/>
     </row>
     <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" s="26">
@@ -7323,12 +7355,12 @@
       <c r="Q194" s="25"/>
       <c r="R194" s="25"/>
       <c r="S194" s="27"/>
-      <c r="V194" s="69"/>
-      <c r="W194" s="84"/>
-      <c r="X194" s="84"/>
-      <c r="Y194" s="69"/>
-      <c r="Z194" s="93"/>
-      <c r="AA194" s="79"/>
+      <c r="V194" s="71"/>
+      <c r="W194" s="86"/>
+      <c r="X194" s="86"/>
+      <c r="Y194" s="71"/>
+      <c r="Z194" s="95"/>
+      <c r="AA194" s="81"/>
     </row>
     <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" s="26">
@@ -7352,12 +7384,12 @@
       <c r="Q195" s="25"/>
       <c r="R195" s="25"/>
       <c r="S195" s="27"/>
-      <c r="V195" s="69"/>
-      <c r="W195" s="79"/>
-      <c r="X195" s="79"/>
-      <c r="Y195" s="79"/>
-      <c r="Z195" s="79"/>
-      <c r="AA195" s="79"/>
+      <c r="V195" s="71"/>
+      <c r="W195" s="81"/>
+      <c r="X195" s="81"/>
+      <c r="Y195" s="81"/>
+      <c r="Z195" s="81"/>
+      <c r="AA195" s="81"/>
     </row>
     <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" s="26">
@@ -7381,12 +7413,12 @@
       <c r="Q196" s="25"/>
       <c r="R196" s="25"/>
       <c r="S196" s="27"/>
-      <c r="V196" s="69"/>
-      <c r="W196" s="79"/>
-      <c r="X196" s="79"/>
-      <c r="Y196" s="79"/>
-      <c r="Z196" s="79"/>
-      <c r="AA196" s="79"/>
+      <c r="V196" s="71"/>
+      <c r="W196" s="81"/>
+      <c r="X196" s="81"/>
+      <c r="Y196" s="81"/>
+      <c r="Z196" s="81"/>
+      <c r="AA196" s="81"/>
     </row>
     <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" s="26">
@@ -7410,12 +7442,12 @@
       <c r="Q197" s="25"/>
       <c r="R197" s="25"/>
       <c r="S197" s="27"/>
-      <c r="V197" s="69"/>
-      <c r="W197" s="79"/>
-      <c r="X197" s="79"/>
-      <c r="Y197" s="79"/>
-      <c r="Z197" s="79"/>
-      <c r="AA197" s="79"/>
+      <c r="V197" s="71"/>
+      <c r="W197" s="81"/>
+      <c r="X197" s="81"/>
+      <c r="Y197" s="81"/>
+      <c r="Z197" s="81"/>
+      <c r="AA197" s="81"/>
     </row>
     <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" s="26">
@@ -7439,12 +7471,12 @@
       <c r="Q198" s="25"/>
       <c r="R198" s="25"/>
       <c r="S198" s="27"/>
-      <c r="V198" s="69"/>
-      <c r="W198" s="79"/>
-      <c r="X198" s="79"/>
-      <c r="Y198" s="79"/>
-      <c r="Z198" s="79"/>
-      <c r="AA198" s="79"/>
+      <c r="V198" s="71"/>
+      <c r="W198" s="81"/>
+      <c r="X198" s="81"/>
+      <c r="Y198" s="81"/>
+      <c r="Z198" s="81"/>
+      <c r="AA198" s="81"/>
     </row>
     <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" s="26">
@@ -7468,12 +7500,12 @@
       <c r="Q199" s="25"/>
       <c r="R199" s="25"/>
       <c r="S199" s="27"/>
-      <c r="V199" s="69"/>
-      <c r="W199" s="79"/>
-      <c r="X199" s="79"/>
-      <c r="Y199" s="79"/>
-      <c r="Z199" s="79"/>
-      <c r="AA199" s="79"/>
+      <c r="V199" s="71"/>
+      <c r="W199" s="81"/>
+      <c r="X199" s="81"/>
+      <c r="Y199" s="81"/>
+      <c r="Z199" s="81"/>
+      <c r="AA199" s="81"/>
     </row>
     <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" s="26">
@@ -7497,12 +7529,12 @@
       <c r="Q200" s="25"/>
       <c r="R200" s="25"/>
       <c r="S200" s="27"/>
-      <c r="V200" s="69"/>
-      <c r="W200" s="79"/>
-      <c r="X200" s="79"/>
-      <c r="Y200" s="79"/>
-      <c r="Z200" s="79"/>
-      <c r="AA200" s="79"/>
+      <c r="V200" s="71"/>
+      <c r="W200" s="81"/>
+      <c r="X200" s="81"/>
+      <c r="Y200" s="81"/>
+      <c r="Z200" s="81"/>
+      <c r="AA200" s="81"/>
     </row>
     <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" s="26">
@@ -7526,12 +7558,12 @@
       <c r="Q201" s="25"/>
       <c r="R201" s="25"/>
       <c r="S201" s="27"/>
-      <c r="V201" s="69"/>
-      <c r="W201" s="79"/>
-      <c r="X201" s="79"/>
-      <c r="Y201" s="79"/>
-      <c r="Z201" s="79"/>
-      <c r="AA201" s="79"/>
+      <c r="V201" s="71"/>
+      <c r="W201" s="81"/>
+      <c r="X201" s="81"/>
+      <c r="Y201" s="81"/>
+      <c r="Z201" s="81"/>
+      <c r="AA201" s="81"/>
     </row>
     <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" s="26">
@@ -7555,12 +7587,12 @@
       <c r="Q202" s="25"/>
       <c r="R202" s="25"/>
       <c r="S202" s="27"/>
-      <c r="V202" s="69"/>
-      <c r="W202" s="79"/>
-      <c r="X202" s="79"/>
-      <c r="Y202" s="79"/>
-      <c r="Z202" s="79"/>
-      <c r="AA202" s="79"/>
+      <c r="V202" s="71"/>
+      <c r="W202" s="81"/>
+      <c r="X202" s="81"/>
+      <c r="Y202" s="81"/>
+      <c r="Z202" s="81"/>
+      <c r="AA202" s="81"/>
     </row>
     <row r="203" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A203" s="26">
@@ -7584,12 +7616,12 @@
       <c r="Q203" s="25"/>
       <c r="R203" s="25"/>
       <c r="S203" s="27"/>
-      <c r="V203" s="69"/>
-      <c r="W203" s="79"/>
-      <c r="X203" s="79"/>
-      <c r="Y203" s="79"/>
-      <c r="Z203" s="79"/>
-      <c r="AA203" s="79"/>
+      <c r="V203" s="71"/>
+      <c r="W203" s="81"/>
+      <c r="X203" s="81"/>
+      <c r="Y203" s="81"/>
+      <c r="Z203" s="81"/>
+      <c r="AA203" s="81"/>
     </row>
     <row r="204" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A204" s="26">
@@ -7613,12 +7645,12 @@
       <c r="Q204" s="25"/>
       <c r="R204" s="25"/>
       <c r="S204" s="27"/>
-      <c r="V204" s="69"/>
-      <c r="W204" s="79"/>
-      <c r="X204" s="79"/>
-      <c r="Y204" s="79"/>
-      <c r="Z204" s="79"/>
-      <c r="AA204" s="79"/>
+      <c r="V204" s="71"/>
+      <c r="W204" s="81"/>
+      <c r="X204" s="81"/>
+      <c r="Y204" s="81"/>
+      <c r="Z204" s="81"/>
+      <c r="AA204" s="81"/>
     </row>
     <row r="205" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A205" s="26">
@@ -7642,12 +7674,12 @@
       <c r="Q205" s="25"/>
       <c r="R205" s="25"/>
       <c r="S205" s="27"/>
-      <c r="V205" s="69"/>
-      <c r="W205" s="79"/>
-      <c r="X205" s="79"/>
-      <c r="Y205" s="79"/>
-      <c r="Z205" s="79"/>
-      <c r="AA205" s="79"/>
+      <c r="V205" s="71"/>
+      <c r="W205" s="81"/>
+      <c r="X205" s="81"/>
+      <c r="Y205" s="81"/>
+      <c r="Z205" s="81"/>
+      <c r="AA205" s="81"/>
     </row>
     <row r="206" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A206" s="26">
@@ -7671,12 +7703,12 @@
       <c r="Q206" s="25"/>
       <c r="R206" s="25"/>
       <c r="S206" s="27"/>
-      <c r="V206" s="69"/>
-      <c r="W206" s="79"/>
-      <c r="X206" s="79"/>
-      <c r="Y206" s="79"/>
-      <c r="Z206" s="79"/>
-      <c r="AA206" s="79"/>
+      <c r="V206" s="71"/>
+      <c r="W206" s="81"/>
+      <c r="X206" s="81"/>
+      <c r="Y206" s="81"/>
+      <c r="Z206" s="81"/>
+      <c r="AA206" s="81"/>
     </row>
     <row r="207" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A207" s="26">
@@ -7700,12 +7732,12 @@
       <c r="Q207" s="25"/>
       <c r="R207" s="25"/>
       <c r="S207" s="27"/>
-      <c r="V207" s="69"/>
-      <c r="W207" s="79"/>
-      <c r="X207" s="79"/>
-      <c r="Y207" s="79"/>
-      <c r="Z207" s="79"/>
-      <c r="AA207" s="79"/>
+      <c r="V207" s="71"/>
+      <c r="W207" s="81"/>
+      <c r="X207" s="81"/>
+      <c r="Y207" s="81"/>
+      <c r="Z207" s="81"/>
+      <c r="AA207" s="81"/>
     </row>
     <row r="208" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A208" s="26">
@@ -7729,12 +7761,12 @@
       <c r="Q208" s="25"/>
       <c r="R208" s="25"/>
       <c r="S208" s="27"/>
-      <c r="V208" s="69"/>
-      <c r="W208" s="79"/>
-      <c r="X208" s="79"/>
-      <c r="Y208" s="79"/>
-      <c r="Z208" s="79"/>
-      <c r="AA208" s="79"/>
+      <c r="V208" s="71"/>
+      <c r="W208" s="81"/>
+      <c r="X208" s="81"/>
+      <c r="Y208" s="81"/>
+      <c r="Z208" s="81"/>
+      <c r="AA208" s="81"/>
     </row>
     <row r="209" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A209" s="26">
@@ -7758,12 +7790,12 @@
       <c r="Q209" s="25"/>
       <c r="R209" s="25"/>
       <c r="S209" s="27"/>
-      <c r="V209" s="69"/>
-      <c r="W209" s="79"/>
-      <c r="X209" s="79"/>
-      <c r="Y209" s="79"/>
-      <c r="Z209" s="79"/>
-      <c r="AA209" s="79"/>
+      <c r="V209" s="71"/>
+      <c r="W209" s="81"/>
+      <c r="X209" s="81"/>
+      <c r="Y209" s="81"/>
+      <c r="Z209" s="81"/>
+      <c r="AA209" s="81"/>
     </row>
     <row r="210" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A210" s="26">
@@ -7787,12 +7819,12 @@
       <c r="Q210" s="25"/>
       <c r="R210" s="25"/>
       <c r="S210" s="27"/>
-      <c r="V210" s="69"/>
-      <c r="W210" s="79"/>
-      <c r="X210" s="79"/>
-      <c r="Y210" s="79"/>
-      <c r="Z210" s="79"/>
-      <c r="AA210" s="79"/>
+      <c r="V210" s="71"/>
+      <c r="W210" s="81"/>
+      <c r="X210" s="81"/>
+      <c r="Y210" s="81"/>
+      <c r="Z210" s="81"/>
+      <c r="AA210" s="81"/>
     </row>
     <row r="211" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K211" s="23">
@@ -7803,46 +7835,46 @@
       </c>
     </row>
     <row r="212" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A212" s="80" t="s">
+      <c r="A212" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B212" s="80"/>
-      <c r="C212" s="80"/>
-      <c r="D212" s="80"/>
-      <c r="E212" s="80"/>
-      <c r="F212" s="81" t="s">
+      <c r="B212" s="82"/>
+      <c r="C212" s="82"/>
+      <c r="D212" s="82"/>
+      <c r="E212" s="82"/>
+      <c r="F212" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="G212" s="81"/>
-      <c r="H212" s="81"/>
-      <c r="I212" s="81"/>
-      <c r="J212" s="81"/>
-      <c r="K212" s="81"/>
-      <c r="L212" s="81"/>
-      <c r="M212" s="81"/>
-      <c r="N212" s="81"/>
-      <c r="O212" s="81"/>
-      <c r="P212" s="81"/>
-      <c r="Q212" s="81"/>
-      <c r="R212" s="81"/>
-      <c r="S212" s="81"/>
-      <c r="T212" s="81"/>
+      <c r="G212" s="83"/>
+      <c r="H212" s="83"/>
+      <c r="I212" s="83"/>
+      <c r="J212" s="83"/>
+      <c r="K212" s="83"/>
+      <c r="L212" s="83"/>
+      <c r="M212" s="83"/>
+      <c r="N212" s="83"/>
+      <c r="O212" s="83"/>
+      <c r="P212" s="83"/>
+      <c r="Q212" s="83"/>
+      <c r="R212" s="83"/>
+      <c r="S212" s="83"/>
+      <c r="T212" s="83"/>
     </row>
     <row r="213" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F213" s="82"/>
-      <c r="G213" s="82"/>
-      <c r="H213" s="82"/>
-      <c r="V213" s="57" t="s">
+      <c r="F213" s="84"/>
+      <c r="G213" s="84"/>
+      <c r="H213" s="84"/>
+      <c r="V213" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="W213" s="57"/>
-      <c r="X213" s="57"/>
-      <c r="Y213" s="57"/>
-      <c r="Z213" s="57"/>
-      <c r="AA213" s="57"/>
+      <c r="W213" s="59"/>
+      <c r="X213" s="59"/>
+      <c r="Y213" s="59"/>
+      <c r="Z213" s="59"/>
+      <c r="AA213" s="59"/>
     </row>
     <row r="215" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A215" s="104" t="s">
+      <c r="A215" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B215" s="44" t="s">
@@ -7870,10 +7902,10 @@
       <c r="V215" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W215" s="90" t="s">
+      <c r="W215" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X215" s="90"/>
+      <c r="X215" s="92"/>
       <c r="Y215" s="13" t="s">
         <v>38</v>
       </c>
@@ -7885,7 +7917,7 @@
       </c>
     </row>
     <row r="216" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A216" s="105"/>
+      <c r="A216" s="43"/>
       <c r="B216" s="47"/>
       <c r="C216" s="48"/>
       <c r="D216" s="48"/>
@@ -7908,21 +7940,21 @@
       <c r="S216" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V216" s="69" t="str">
+      <c r="V216" s="71" t="str">
         <f>IF(K178="","",K178)</f>
         <v>{{DATES_OGNEVAYA}}</v>
       </c>
-      <c r="W216" s="94" t="s">
+      <c r="W216" s="96" t="s">
         <v>95</v>
       </c>
-      <c r="X216" s="95"/>
-      <c r="Y216" s="69">
+      <c r="X216" s="97"/>
+      <c r="Y216" s="71">
         <v>1</v>
       </c>
-      <c r="Z216" s="70" t="s">
+      <c r="Z216" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AA216" s="79"/>
+      <c r="AA216" s="81"/>
     </row>
     <row r="217" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A217" s="26">
@@ -7949,13 +7981,15 @@
       <c r="P217" s="25"/>
       <c r="Q217" s="25"/>
       <c r="R217" s="25"/>
-      <c r="S217" s="27"/>
-      <c r="V217" s="69"/>
-      <c r="W217" s="95"/>
-      <c r="X217" s="95"/>
-      <c r="Y217" s="69"/>
-      <c r="Z217" s="70"/>
-      <c r="AA217" s="79"/>
+      <c r="S217" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="V217" s="71"/>
+      <c r="W217" s="97"/>
+      <c r="X217" s="97"/>
+      <c r="Y217" s="71"/>
+      <c r="Z217" s="72"/>
+      <c r="AA217" s="81"/>
     </row>
     <row r="218" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A218" s="26">
@@ -7979,12 +8013,12 @@
       <c r="Q218" s="25"/>
       <c r="R218" s="25"/>
       <c r="S218" s="27"/>
-      <c r="V218" s="69"/>
-      <c r="W218" s="95"/>
-      <c r="X218" s="95"/>
-      <c r="Y218" s="69"/>
-      <c r="Z218" s="70"/>
-      <c r="AA218" s="79"/>
+      <c r="V218" s="71"/>
+      <c r="W218" s="97"/>
+      <c r="X218" s="97"/>
+      <c r="Y218" s="71"/>
+      <c r="Z218" s="72"/>
+      <c r="AA218" s="81"/>
     </row>
     <row r="219" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A219" s="26">
@@ -8008,12 +8042,12 @@
       <c r="Q219" s="25"/>
       <c r="R219" s="25"/>
       <c r="S219" s="27"/>
-      <c r="V219" s="69"/>
-      <c r="W219" s="95"/>
-      <c r="X219" s="95"/>
-      <c r="Y219" s="69"/>
-      <c r="Z219" s="70"/>
-      <c r="AA219" s="79"/>
+      <c r="V219" s="71"/>
+      <c r="W219" s="97"/>
+      <c r="X219" s="97"/>
+      <c r="Y219" s="71"/>
+      <c r="Z219" s="72"/>
+      <c r="AA219" s="81"/>
     </row>
     <row r="220" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A220" s="26">
@@ -8037,12 +8071,12 @@
       <c r="Q220" s="25"/>
       <c r="R220" s="25"/>
       <c r="S220" s="27"/>
-      <c r="V220" s="69"/>
-      <c r="W220" s="95"/>
-      <c r="X220" s="95"/>
-      <c r="Y220" s="69"/>
-      <c r="Z220" s="70"/>
-      <c r="AA220" s="79"/>
+      <c r="V220" s="71"/>
+      <c r="W220" s="97"/>
+      <c r="X220" s="97"/>
+      <c r="Y220" s="71"/>
+      <c r="Z220" s="72"/>
+      <c r="AA220" s="81"/>
     </row>
     <row r="221" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A221" s="26">
@@ -8066,12 +8100,12 @@
       <c r="Q221" s="25"/>
       <c r="R221" s="25"/>
       <c r="S221" s="27"/>
-      <c r="V221" s="69"/>
-      <c r="W221" s="95"/>
-      <c r="X221" s="95"/>
-      <c r="Y221" s="69"/>
-      <c r="Z221" s="70"/>
-      <c r="AA221" s="79"/>
+      <c r="V221" s="71"/>
+      <c r="W221" s="97"/>
+      <c r="X221" s="97"/>
+      <c r="Y221" s="71"/>
+      <c r="Z221" s="72"/>
+      <c r="AA221" s="81"/>
     </row>
     <row r="222" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A222" s="26">
@@ -8095,12 +8129,12 @@
       <c r="Q222" s="25"/>
       <c r="R222" s="25"/>
       <c r="S222" s="27"/>
-      <c r="V222" s="69"/>
-      <c r="W222" s="95"/>
-      <c r="X222" s="95"/>
-      <c r="Y222" s="69"/>
-      <c r="Z222" s="70"/>
-      <c r="AA222" s="79"/>
+      <c r="V222" s="71"/>
+      <c r="W222" s="97"/>
+      <c r="X222" s="97"/>
+      <c r="Y222" s="71"/>
+      <c r="Z222" s="72"/>
+      <c r="AA222" s="81"/>
     </row>
     <row r="223" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A223" s="26">
@@ -8124,12 +8158,12 @@
       <c r="Q223" s="25"/>
       <c r="R223" s="25"/>
       <c r="S223" s="27"/>
-      <c r="V223" s="69"/>
-      <c r="W223" s="95"/>
-      <c r="X223" s="95"/>
-      <c r="Y223" s="69"/>
-      <c r="Z223" s="70"/>
-      <c r="AA223" s="79"/>
+      <c r="V223" s="71"/>
+      <c r="W223" s="97"/>
+      <c r="X223" s="97"/>
+      <c r="Y223" s="71"/>
+      <c r="Z223" s="72"/>
+      <c r="AA223" s="81"/>
     </row>
     <row r="224" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A224" s="26">
@@ -8153,12 +8187,12 @@
       <c r="Q224" s="25"/>
       <c r="R224" s="25"/>
       <c r="S224" s="27"/>
-      <c r="V224" s="69"/>
-      <c r="W224" s="95"/>
-      <c r="X224" s="95"/>
-      <c r="Y224" s="69"/>
-      <c r="Z224" s="70"/>
-      <c r="AA224" s="79"/>
+      <c r="V224" s="71"/>
+      <c r="W224" s="97"/>
+      <c r="X224" s="97"/>
+      <c r="Y224" s="71"/>
+      <c r="Z224" s="72"/>
+      <c r="AA224" s="81"/>
     </row>
     <row r="225" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A225" s="26">
@@ -8182,21 +8216,21 @@
       <c r="Q225" s="25"/>
       <c r="R225" s="25"/>
       <c r="S225" s="27"/>
-      <c r="V225" s="69" t="str">
+      <c r="V225" s="71" t="str">
         <f>IF(L178="","",L178)</f>
         <v/>
       </c>
-      <c r="W225" s="94" t="s">
+      <c r="W225" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="X225" s="95"/>
-      <c r="Y225" s="69">
+      <c r="X225" s="97"/>
+      <c r="Y225" s="71">
         <v>2</v>
       </c>
-      <c r="Z225" s="70" t="s">
+      <c r="Z225" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AA225" s="79"/>
+      <c r="AA225" s="81"/>
     </row>
     <row r="226" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A226" s="26">
@@ -8220,12 +8254,12 @@
       <c r="Q226" s="25"/>
       <c r="R226" s="25"/>
       <c r="S226" s="27"/>
-      <c r="V226" s="69"/>
-      <c r="W226" s="95"/>
-      <c r="X226" s="95"/>
-      <c r="Y226" s="69"/>
-      <c r="Z226" s="70"/>
-      <c r="AA226" s="79"/>
+      <c r="V226" s="71"/>
+      <c r="W226" s="97"/>
+      <c r="X226" s="97"/>
+      <c r="Y226" s="71"/>
+      <c r="Z226" s="72"/>
+      <c r="AA226" s="81"/>
     </row>
     <row r="227" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A227" s="26">
@@ -8249,12 +8283,12 @@
       <c r="Q227" s="25"/>
       <c r="R227" s="25"/>
       <c r="S227" s="27"/>
-      <c r="V227" s="69"/>
-      <c r="W227" s="95"/>
-      <c r="X227" s="95"/>
-      <c r="Y227" s="69"/>
-      <c r="Z227" s="70"/>
-      <c r="AA227" s="79"/>
+      <c r="V227" s="71"/>
+      <c r="W227" s="97"/>
+      <c r="X227" s="97"/>
+      <c r="Y227" s="71"/>
+      <c r="Z227" s="72"/>
+      <c r="AA227" s="81"/>
     </row>
     <row r="228" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A228" s="26">
@@ -8278,12 +8312,12 @@
       <c r="Q228" s="25"/>
       <c r="R228" s="25"/>
       <c r="S228" s="27"/>
-      <c r="V228" s="69"/>
-      <c r="W228" s="95"/>
-      <c r="X228" s="95"/>
-      <c r="Y228" s="69"/>
-      <c r="Z228" s="70"/>
-      <c r="AA228" s="79"/>
+      <c r="V228" s="71"/>
+      <c r="W228" s="97"/>
+      <c r="X228" s="97"/>
+      <c r="Y228" s="71"/>
+      <c r="Z228" s="72"/>
+      <c r="AA228" s="81"/>
     </row>
     <row r="229" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A229" s="26">
@@ -8307,12 +8341,12 @@
       <c r="Q229" s="25"/>
       <c r="R229" s="25"/>
       <c r="S229" s="27"/>
-      <c r="V229" s="69"/>
-      <c r="W229" s="95"/>
-      <c r="X229" s="95"/>
-      <c r="Y229" s="69"/>
-      <c r="Z229" s="70"/>
-      <c r="AA229" s="79"/>
+      <c r="V229" s="71"/>
+      <c r="W229" s="97"/>
+      <c r="X229" s="97"/>
+      <c r="Y229" s="71"/>
+      <c r="Z229" s="72"/>
+      <c r="AA229" s="81"/>
     </row>
     <row r="230" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A230" s="26">
@@ -8336,12 +8370,12 @@
       <c r="Q230" s="25"/>
       <c r="R230" s="25"/>
       <c r="S230" s="27"/>
-      <c r="V230" s="69"/>
-      <c r="W230" s="95"/>
-      <c r="X230" s="95"/>
-      <c r="Y230" s="69"/>
-      <c r="Z230" s="70"/>
-      <c r="AA230" s="79"/>
+      <c r="V230" s="71"/>
+      <c r="W230" s="97"/>
+      <c r="X230" s="97"/>
+      <c r="Y230" s="71"/>
+      <c r="Z230" s="72"/>
+      <c r="AA230" s="81"/>
     </row>
     <row r="231" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A231" s="26">
@@ -8365,21 +8399,21 @@
       <c r="Q231" s="25"/>
       <c r="R231" s="25"/>
       <c r="S231" s="27"/>
-      <c r="V231" s="69" t="str">
+      <c r="V231" s="71" t="str">
         <f>IF(M178="","",M178)</f>
         <v/>
       </c>
-      <c r="W231" s="94" t="s">
+      <c r="W231" s="96" t="s">
         <v>97</v>
       </c>
-      <c r="X231" s="95"/>
-      <c r="Y231" s="69">
+      <c r="X231" s="97"/>
+      <c r="Y231" s="71">
         <v>1</v>
       </c>
-      <c r="Z231" s="96" t="s">
+      <c r="Z231" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="AA231" s="79"/>
+      <c r="AA231" s="81"/>
     </row>
     <row r="232" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A232" s="26">
@@ -8403,12 +8437,12 @@
       <c r="Q232" s="25"/>
       <c r="R232" s="25"/>
       <c r="S232" s="27"/>
-      <c r="V232" s="69"/>
-      <c r="W232" s="95"/>
-      <c r="X232" s="95"/>
-      <c r="Y232" s="69"/>
-      <c r="Z232" s="96"/>
-      <c r="AA232" s="79"/>
+      <c r="V232" s="71"/>
+      <c r="W232" s="97"/>
+      <c r="X232" s="97"/>
+      <c r="Y232" s="71"/>
+      <c r="Z232" s="98"/>
+      <c r="AA232" s="81"/>
     </row>
     <row r="233" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A233" s="26">
@@ -8432,12 +8466,12 @@
       <c r="Q233" s="25"/>
       <c r="R233" s="25"/>
       <c r="S233" s="27"/>
-      <c r="V233" s="69"/>
-      <c r="W233" s="95"/>
-      <c r="X233" s="95"/>
-      <c r="Y233" s="69"/>
-      <c r="Z233" s="96"/>
-      <c r="AA233" s="79"/>
+      <c r="V233" s="71"/>
+      <c r="W233" s="97"/>
+      <c r="X233" s="97"/>
+      <c r="Y233" s="71"/>
+      <c r="Z233" s="98"/>
+      <c r="AA233" s="81"/>
     </row>
     <row r="234" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A234" s="26">
@@ -8461,12 +8495,12 @@
       <c r="Q234" s="25"/>
       <c r="R234" s="25"/>
       <c r="S234" s="27"/>
-      <c r="V234" s="69"/>
-      <c r="W234" s="95"/>
-      <c r="X234" s="95"/>
-      <c r="Y234" s="69"/>
-      <c r="Z234" s="96"/>
-      <c r="AA234" s="79"/>
+      <c r="V234" s="71"/>
+      <c r="W234" s="97"/>
+      <c r="X234" s="97"/>
+      <c r="Y234" s="71"/>
+      <c r="Z234" s="98"/>
+      <c r="AA234" s="81"/>
     </row>
     <row r="235" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A235" s="26">
@@ -8490,12 +8524,12 @@
       <c r="Q235" s="25"/>
       <c r="R235" s="25"/>
       <c r="S235" s="27"/>
-      <c r="V235" s="69"/>
-      <c r="W235" s="95"/>
-      <c r="X235" s="95"/>
-      <c r="Y235" s="69"/>
-      <c r="Z235" s="96"/>
-      <c r="AA235" s="79"/>
+      <c r="V235" s="71"/>
+      <c r="W235" s="97"/>
+      <c r="X235" s="97"/>
+      <c r="Y235" s="71"/>
+      <c r="Z235" s="98"/>
+      <c r="AA235" s="81"/>
     </row>
     <row r="236" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A236" s="26">
@@ -8519,12 +8553,12 @@
       <c r="Q236" s="25"/>
       <c r="R236" s="25"/>
       <c r="S236" s="27"/>
-      <c r="V236" s="69"/>
-      <c r="W236" s="95"/>
-      <c r="X236" s="95"/>
-      <c r="Y236" s="69"/>
-      <c r="Z236" s="96"/>
-      <c r="AA236" s="79"/>
+      <c r="V236" s="71"/>
+      <c r="W236" s="97"/>
+      <c r="X236" s="97"/>
+      <c r="Y236" s="71"/>
+      <c r="Z236" s="98"/>
+      <c r="AA236" s="81"/>
     </row>
     <row r="237" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A237" s="26">
@@ -8548,21 +8582,21 @@
       <c r="Q237" s="25"/>
       <c r="R237" s="25"/>
       <c r="S237" s="27"/>
-      <c r="V237" s="69" t="str">
+      <c r="V237" s="71" t="str">
         <f>IF(N178="","",N178)</f>
         <v/>
       </c>
-      <c r="W237" s="94" t="s">
+      <c r="W237" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="X237" s="95"/>
-      <c r="Y237" s="69">
+      <c r="X237" s="97"/>
+      <c r="Y237" s="71">
         <v>1</v>
       </c>
-      <c r="Z237" s="96" t="s">
+      <c r="Z237" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="AA237" s="79"/>
+      <c r="AA237" s="81"/>
     </row>
     <row r="238" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A238" s="26">
@@ -8586,12 +8620,12 @@
       <c r="Q238" s="25"/>
       <c r="R238" s="25"/>
       <c r="S238" s="27"/>
-      <c r="V238" s="69"/>
-      <c r="W238" s="95"/>
-      <c r="X238" s="95"/>
-      <c r="Y238" s="69"/>
-      <c r="Z238" s="96"/>
-      <c r="AA238" s="79"/>
+      <c r="V238" s="71"/>
+      <c r="W238" s="97"/>
+      <c r="X238" s="97"/>
+      <c r="Y238" s="71"/>
+      <c r="Z238" s="98"/>
+      <c r="AA238" s="81"/>
     </row>
     <row r="239" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A239" s="26">
@@ -8615,12 +8649,12 @@
       <c r="Q239" s="25"/>
       <c r="R239" s="25"/>
       <c r="S239" s="27"/>
-      <c r="V239" s="69"/>
-      <c r="W239" s="95"/>
-      <c r="X239" s="95"/>
-      <c r="Y239" s="69"/>
-      <c r="Z239" s="96"/>
-      <c r="AA239" s="79"/>
+      <c r="V239" s="71"/>
+      <c r="W239" s="97"/>
+      <c r="X239" s="97"/>
+      <c r="Y239" s="71"/>
+      <c r="Z239" s="98"/>
+      <c r="AA239" s="81"/>
     </row>
     <row r="240" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A240" s="26">
@@ -8644,12 +8678,12 @@
       <c r="Q240" s="25"/>
       <c r="R240" s="25"/>
       <c r="S240" s="27"/>
-      <c r="V240" s="69"/>
-      <c r="W240" s="95"/>
-      <c r="X240" s="95"/>
-      <c r="Y240" s="69"/>
-      <c r="Z240" s="96"/>
-      <c r="AA240" s="79"/>
+      <c r="V240" s="71"/>
+      <c r="W240" s="97"/>
+      <c r="X240" s="97"/>
+      <c r="Y240" s="71"/>
+      <c r="Z240" s="98"/>
+      <c r="AA240" s="81"/>
     </row>
     <row r="241" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A241" s="26">
@@ -8673,12 +8707,12 @@
       <c r="Q241" s="25"/>
       <c r="R241" s="25"/>
       <c r="S241" s="27"/>
-      <c r="V241" s="69"/>
-      <c r="W241" s="95"/>
-      <c r="X241" s="95"/>
-      <c r="Y241" s="69"/>
-      <c r="Z241" s="96"/>
-      <c r="AA241" s="79"/>
+      <c r="V241" s="71"/>
+      <c r="W241" s="97"/>
+      <c r="X241" s="97"/>
+      <c r="Y241" s="71"/>
+      <c r="Z241" s="98"/>
+      <c r="AA241" s="81"/>
     </row>
     <row r="242" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A242" s="26">
@@ -8702,12 +8736,12 @@
       <c r="Q242" s="25"/>
       <c r="R242" s="25"/>
       <c r="S242" s="27"/>
-      <c r="V242" s="69"/>
-      <c r="W242" s="95"/>
-      <c r="X242" s="95"/>
-      <c r="Y242" s="69"/>
-      <c r="Z242" s="96"/>
-      <c r="AA242" s="79"/>
+      <c r="V242" s="71"/>
+      <c r="W242" s="97"/>
+      <c r="X242" s="97"/>
+      <c r="Y242" s="71"/>
+      <c r="Z242" s="98"/>
+      <c r="AA242" s="81"/>
     </row>
     <row r="243" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A243" s="26">
@@ -8731,12 +8765,12 @@
       <c r="Q243" s="25"/>
       <c r="R243" s="25"/>
       <c r="S243" s="27"/>
-      <c r="V243" s="69"/>
-      <c r="W243" s="95"/>
-      <c r="X243" s="95"/>
-      <c r="Y243" s="69"/>
-      <c r="Z243" s="96"/>
-      <c r="AA243" s="79"/>
+      <c r="V243" s="71"/>
+      <c r="W243" s="97"/>
+      <c r="X243" s="97"/>
+      <c r="Y243" s="71"/>
+      <c r="Z243" s="98"/>
+      <c r="AA243" s="81"/>
     </row>
     <row r="244" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A244" s="26">
@@ -8760,21 +8794,21 @@
       <c r="Q244" s="25"/>
       <c r="R244" s="25"/>
       <c r="S244" s="27"/>
-      <c r="V244" s="69" t="str">
+      <c r="V244" s="71" t="str">
         <f>IF(O178="","",O178)</f>
         <v/>
       </c>
-      <c r="W244" s="68" t="s">
+      <c r="W244" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="X244" s="68"/>
-      <c r="Y244" s="69">
+      <c r="X244" s="70"/>
+      <c r="Y244" s="71">
         <v>4</v>
       </c>
-      <c r="Z244" s="70" t="s">
+      <c r="Z244" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="AA244" s="79"/>
+      <c r="AA244" s="81"/>
     </row>
     <row r="245" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A245" s="26">
@@ -8798,12 +8832,12 @@
       <c r="Q245" s="25"/>
       <c r="R245" s="25"/>
       <c r="S245" s="27"/>
-      <c r="V245" s="69"/>
-      <c r="W245" s="68"/>
-      <c r="X245" s="68"/>
-      <c r="Y245" s="69"/>
-      <c r="Z245" s="70"/>
-      <c r="AA245" s="79"/>
+      <c r="V245" s="71"/>
+      <c r="W245" s="70"/>
+      <c r="X245" s="70"/>
+      <c r="Y245" s="71"/>
+      <c r="Z245" s="72"/>
+      <c r="AA245" s="81"/>
     </row>
     <row r="246" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A246" s="26">
@@ -8827,12 +8861,12 @@
       <c r="Q246" s="25"/>
       <c r="R246" s="25"/>
       <c r="S246" s="27"/>
-      <c r="V246" s="69"/>
-      <c r="W246" s="68"/>
-      <c r="X246" s="68"/>
-      <c r="Y246" s="69"/>
-      <c r="Z246" s="70"/>
-      <c r="AA246" s="79"/>
+      <c r="V246" s="71"/>
+      <c r="W246" s="70"/>
+      <c r="X246" s="70"/>
+      <c r="Y246" s="71"/>
+      <c r="Z246" s="72"/>
+      <c r="AA246" s="81"/>
     </row>
     <row r="247" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A247" s="26">
@@ -8856,12 +8890,12 @@
       <c r="Q247" s="25"/>
       <c r="R247" s="25"/>
       <c r="S247" s="27"/>
-      <c r="V247" s="69"/>
-      <c r="W247" s="68"/>
-      <c r="X247" s="68"/>
-      <c r="Y247" s="69"/>
-      <c r="Z247" s="70"/>
-      <c r="AA247" s="79"/>
+      <c r="V247" s="71"/>
+      <c r="W247" s="70"/>
+      <c r="X247" s="70"/>
+      <c r="Y247" s="71"/>
+      <c r="Z247" s="72"/>
+      <c r="AA247" s="81"/>
     </row>
     <row r="248" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A248" s="26">
@@ -8885,12 +8919,12 @@
       <c r="Q248" s="25"/>
       <c r="R248" s="25"/>
       <c r="S248" s="27"/>
-      <c r="V248" s="69"/>
-      <c r="W248" s="68"/>
-      <c r="X248" s="68"/>
-      <c r="Y248" s="69"/>
-      <c r="Z248" s="70"/>
-      <c r="AA248" s="79"/>
+      <c r="V248" s="71"/>
+      <c r="W248" s="70"/>
+      <c r="X248" s="70"/>
+      <c r="Y248" s="71"/>
+      <c r="Z248" s="72"/>
+      <c r="AA248" s="81"/>
     </row>
     <row r="249" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K249" s="23">
@@ -8901,46 +8935,46 @@
       </c>
     </row>
     <row r="250" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A250" s="80" t="s">
+      <c r="A250" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B250" s="80"/>
-      <c r="C250" s="80"/>
-      <c r="D250" s="80"/>
-      <c r="E250" s="80"/>
-      <c r="F250" s="81" t="s">
+      <c r="B250" s="82"/>
+      <c r="C250" s="82"/>
+      <c r="D250" s="82"/>
+      <c r="E250" s="82"/>
+      <c r="F250" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="G250" s="81"/>
-      <c r="H250" s="81"/>
-      <c r="I250" s="81"/>
-      <c r="J250" s="81"/>
-      <c r="K250" s="81"/>
-      <c r="L250" s="81"/>
-      <c r="M250" s="81"/>
-      <c r="N250" s="81"/>
-      <c r="O250" s="81"/>
-      <c r="P250" s="81"/>
-      <c r="Q250" s="81"/>
-      <c r="R250" s="81"/>
-      <c r="S250" s="81"/>
-      <c r="T250" s="81"/>
+      <c r="G250" s="83"/>
+      <c r="H250" s="83"/>
+      <c r="I250" s="83"/>
+      <c r="J250" s="83"/>
+      <c r="K250" s="83"/>
+      <c r="L250" s="83"/>
+      <c r="M250" s="83"/>
+      <c r="N250" s="83"/>
+      <c r="O250" s="83"/>
+      <c r="P250" s="83"/>
+      <c r="Q250" s="83"/>
+      <c r="R250" s="83"/>
+      <c r="S250" s="83"/>
+      <c r="T250" s="83"/>
     </row>
     <row r="251" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F251" s="82"/>
-      <c r="G251" s="82"/>
-      <c r="H251" s="82"/>
-      <c r="V251" s="57" t="s">
+      <c r="F251" s="84"/>
+      <c r="G251" s="84"/>
+      <c r="H251" s="84"/>
+      <c r="V251" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="W251" s="57"/>
-      <c r="X251" s="57"/>
-      <c r="Y251" s="57"/>
-      <c r="Z251" s="57"/>
-      <c r="AA251" s="57"/>
+      <c r="W251" s="59"/>
+      <c r="X251" s="59"/>
+      <c r="Y251" s="59"/>
+      <c r="Z251" s="59"/>
+      <c r="AA251" s="59"/>
     </row>
     <row r="253" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="104" t="s">
+      <c r="A253" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B253" s="44" t="s">
@@ -8968,10 +9002,10 @@
       <c r="V253" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W253" s="90" t="s">
+      <c r="W253" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X253" s="90"/>
+      <c r="X253" s="92"/>
       <c r="Y253" s="13" t="s">
         <v>38</v>
       </c>
@@ -8983,7 +9017,7 @@
       </c>
     </row>
     <row r="254" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A254" s="105"/>
+      <c r="A254" s="43"/>
       <c r="B254" s="47"/>
       <c r="C254" s="48"/>
       <c r="D254" s="48"/>
@@ -9006,21 +9040,21 @@
       <c r="S254" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V254" s="69" t="str">
+      <c r="V254" s="71" t="str">
         <f>IF(K292="","",K292)</f>
         <v>{{DATES_BEZOPASNOST}}</v>
       </c>
-      <c r="W254" s="68" t="s">
+      <c r="W254" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="X254" s="84"/>
-      <c r="Y254" s="69">
+      <c r="X254" s="86"/>
+      <c r="Y254" s="71">
         <v>1</v>
       </c>
-      <c r="Z254" s="70" t="s">
+      <c r="Z254" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="AA254" s="79"/>
+      <c r="AA254" s="81"/>
     </row>
     <row r="255" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A255" s="26">
@@ -9047,13 +9081,15 @@
       <c r="P255" s="25"/>
       <c r="Q255" s="25"/>
       <c r="R255" s="25"/>
-      <c r="S255" s="27"/>
-      <c r="V255" s="69"/>
-      <c r="W255" s="84"/>
-      <c r="X255" s="84"/>
-      <c r="Y255" s="69"/>
-      <c r="Z255" s="70"/>
-      <c r="AA255" s="79"/>
+      <c r="S255" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="V255" s="71"/>
+      <c r="W255" s="86"/>
+      <c r="X255" s="86"/>
+      <c r="Y255" s="71"/>
+      <c r="Z255" s="72"/>
+      <c r="AA255" s="81"/>
     </row>
     <row r="256" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A256" s="26">
@@ -9077,12 +9113,12 @@
       <c r="Q256" s="25"/>
       <c r="R256" s="25"/>
       <c r="S256" s="27"/>
-      <c r="V256" s="69"/>
-      <c r="W256" s="84"/>
-      <c r="X256" s="84"/>
-      <c r="Y256" s="69"/>
-      <c r="Z256" s="70"/>
-      <c r="AA256" s="79"/>
+      <c r="V256" s="71"/>
+      <c r="W256" s="86"/>
+      <c r="X256" s="86"/>
+      <c r="Y256" s="71"/>
+      <c r="Z256" s="72"/>
+      <c r="AA256" s="81"/>
     </row>
     <row r="257" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A257" s="26">
@@ -9106,12 +9142,12 @@
       <c r="Q257" s="25"/>
       <c r="R257" s="25"/>
       <c r="S257" s="27"/>
-      <c r="V257" s="69"/>
-      <c r="W257" s="84"/>
-      <c r="X257" s="84"/>
-      <c r="Y257" s="69"/>
-      <c r="Z257" s="70"/>
-      <c r="AA257" s="79"/>
+      <c r="V257" s="71"/>
+      <c r="W257" s="86"/>
+      <c r="X257" s="86"/>
+      <c r="Y257" s="71"/>
+      <c r="Z257" s="72"/>
+      <c r="AA257" s="81"/>
     </row>
     <row r="258" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A258" s="26">
@@ -9135,12 +9171,12 @@
       <c r="Q258" s="25"/>
       <c r="R258" s="25"/>
       <c r="S258" s="27"/>
-      <c r="V258" s="69"/>
-      <c r="W258" s="84"/>
-      <c r="X258" s="84"/>
-      <c r="Y258" s="69"/>
-      <c r="Z258" s="70"/>
-      <c r="AA258" s="79"/>
+      <c r="V258" s="71"/>
+      <c r="W258" s="86"/>
+      <c r="X258" s="86"/>
+      <c r="Y258" s="71"/>
+      <c r="Z258" s="72"/>
+      <c r="AA258" s="81"/>
     </row>
     <row r="259" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A259" s="26">
@@ -9164,12 +9200,12 @@
       <c r="Q259" s="25"/>
       <c r="R259" s="25"/>
       <c r="S259" s="27"/>
-      <c r="V259" s="69"/>
-      <c r="W259" s="84"/>
-      <c r="X259" s="84"/>
-      <c r="Y259" s="69"/>
-      <c r="Z259" s="70"/>
-      <c r="AA259" s="79"/>
+      <c r="V259" s="71"/>
+      <c r="W259" s="86"/>
+      <c r="X259" s="86"/>
+      <c r="Y259" s="71"/>
+      <c r="Z259" s="72"/>
+      <c r="AA259" s="81"/>
     </row>
     <row r="260" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A260" s="26">
@@ -9193,12 +9229,12 @@
       <c r="Q260" s="25"/>
       <c r="R260" s="25"/>
       <c r="S260" s="27"/>
-      <c r="V260" s="69"/>
-      <c r="W260" s="84"/>
-      <c r="X260" s="84"/>
-      <c r="Y260" s="69"/>
-      <c r="Z260" s="79"/>
-      <c r="AA260" s="79"/>
+      <c r="V260" s="71"/>
+      <c r="W260" s="86"/>
+      <c r="X260" s="86"/>
+      <c r="Y260" s="71"/>
+      <c r="Z260" s="81"/>
+      <c r="AA260" s="81"/>
     </row>
     <row r="261" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A261" s="26">
@@ -9222,12 +9258,12 @@
       <c r="Q261" s="25"/>
       <c r="R261" s="25"/>
       <c r="S261" s="27"/>
-      <c r="V261" s="69"/>
-      <c r="W261" s="84"/>
-      <c r="X261" s="84"/>
-      <c r="Y261" s="69"/>
-      <c r="Z261" s="79"/>
-      <c r="AA261" s="79"/>
+      <c r="V261" s="71"/>
+      <c r="W261" s="86"/>
+      <c r="X261" s="86"/>
+      <c r="Y261" s="71"/>
+      <c r="Z261" s="81"/>
+      <c r="AA261" s="81"/>
     </row>
     <row r="262" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A262" s="26">
@@ -9251,12 +9287,12 @@
       <c r="Q262" s="25"/>
       <c r="R262" s="25"/>
       <c r="S262" s="27"/>
-      <c r="V262" s="69"/>
-      <c r="W262" s="84"/>
-      <c r="X262" s="84"/>
-      <c r="Y262" s="69"/>
-      <c r="Z262" s="79"/>
-      <c r="AA262" s="79"/>
+      <c r="V262" s="71"/>
+      <c r="W262" s="86"/>
+      <c r="X262" s="86"/>
+      <c r="Y262" s="71"/>
+      <c r="Z262" s="81"/>
+      <c r="AA262" s="81"/>
     </row>
     <row r="263" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A263" s="26">
@@ -9280,12 +9316,12 @@
       <c r="Q263" s="25"/>
       <c r="R263" s="25"/>
       <c r="S263" s="27"/>
-      <c r="V263" s="69"/>
-      <c r="W263" s="84"/>
-      <c r="X263" s="84"/>
-      <c r="Y263" s="69"/>
-      <c r="Z263" s="79"/>
-      <c r="AA263" s="79"/>
+      <c r="V263" s="71"/>
+      <c r="W263" s="86"/>
+      <c r="X263" s="86"/>
+      <c r="Y263" s="71"/>
+      <c r="Z263" s="81"/>
+      <c r="AA263" s="81"/>
     </row>
     <row r="264" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A264" s="26">
@@ -9309,12 +9345,12 @@
       <c r="Q264" s="25"/>
       <c r="R264" s="25"/>
       <c r="S264" s="27"/>
-      <c r="V264" s="69"/>
-      <c r="W264" s="84"/>
-      <c r="X264" s="84"/>
-      <c r="Y264" s="69"/>
-      <c r="Z264" s="79"/>
-      <c r="AA264" s="79"/>
+      <c r="V264" s="71"/>
+      <c r="W264" s="86"/>
+      <c r="X264" s="86"/>
+      <c r="Y264" s="71"/>
+      <c r="Z264" s="81"/>
+      <c r="AA264" s="81"/>
     </row>
     <row r="265" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A265" s="26">
@@ -9338,12 +9374,12 @@
       <c r="Q265" s="25"/>
       <c r="R265" s="25"/>
       <c r="S265" s="27"/>
-      <c r="V265" s="69"/>
-      <c r="W265" s="84"/>
-      <c r="X265" s="84"/>
-      <c r="Y265" s="69"/>
-      <c r="Z265" s="79"/>
-      <c r="AA265" s="79"/>
+      <c r="V265" s="71"/>
+      <c r="W265" s="86"/>
+      <c r="X265" s="86"/>
+      <c r="Y265" s="71"/>
+      <c r="Z265" s="81"/>
+      <c r="AA265" s="81"/>
     </row>
     <row r="266" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A266" s="26">
@@ -9367,12 +9403,12 @@
       <c r="Q266" s="25"/>
       <c r="R266" s="25"/>
       <c r="S266" s="27"/>
-      <c r="V266" s="69"/>
-      <c r="W266" s="84"/>
-      <c r="X266" s="84"/>
-      <c r="Y266" s="69"/>
-      <c r="Z266" s="79"/>
-      <c r="AA266" s="79"/>
+      <c r="V266" s="71"/>
+      <c r="W266" s="86"/>
+      <c r="X266" s="86"/>
+      <c r="Y266" s="71"/>
+      <c r="Z266" s="81"/>
+      <c r="AA266" s="81"/>
     </row>
     <row r="267" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A267" s="26">
@@ -9396,12 +9432,12 @@
       <c r="Q267" s="25"/>
       <c r="R267" s="25"/>
       <c r="S267" s="27"/>
-      <c r="V267" s="69"/>
-      <c r="W267" s="84"/>
-      <c r="X267" s="84"/>
-      <c r="Y267" s="69"/>
-      <c r="Z267" s="79"/>
-      <c r="AA267" s="79"/>
+      <c r="V267" s="71"/>
+      <c r="W267" s="86"/>
+      <c r="X267" s="86"/>
+      <c r="Y267" s="71"/>
+      <c r="Z267" s="81"/>
+      <c r="AA267" s="81"/>
     </row>
     <row r="268" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A268" s="26">
@@ -9425,12 +9461,12 @@
       <c r="Q268" s="25"/>
       <c r="R268" s="25"/>
       <c r="S268" s="27"/>
-      <c r="V268" s="69"/>
-      <c r="W268" s="84"/>
-      <c r="X268" s="84"/>
-      <c r="Y268" s="69"/>
-      <c r="Z268" s="79"/>
-      <c r="AA268" s="79"/>
+      <c r="V268" s="71"/>
+      <c r="W268" s="86"/>
+      <c r="X268" s="86"/>
+      <c r="Y268" s="71"/>
+      <c r="Z268" s="81"/>
+      <c r="AA268" s="81"/>
     </row>
     <row r="269" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A269" s="26">
@@ -9454,12 +9490,12 @@
       <c r="Q269" s="25"/>
       <c r="R269" s="25"/>
       <c r="S269" s="27"/>
-      <c r="V269" s="69"/>
-      <c r="W269" s="84"/>
-      <c r="X269" s="84"/>
-      <c r="Y269" s="69"/>
-      <c r="Z269" s="79"/>
-      <c r="AA269" s="79"/>
+      <c r="V269" s="71"/>
+      <c r="W269" s="86"/>
+      <c r="X269" s="86"/>
+      <c r="Y269" s="71"/>
+      <c r="Z269" s="81"/>
+      <c r="AA269" s="81"/>
     </row>
     <row r="270" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A270" s="26">
@@ -9483,12 +9519,12 @@
       <c r="Q270" s="25"/>
       <c r="R270" s="25"/>
       <c r="S270" s="27"/>
-      <c r="V270" s="69"/>
-      <c r="W270" s="84"/>
-      <c r="X270" s="84"/>
-      <c r="Y270" s="69"/>
-      <c r="Z270" s="79"/>
-      <c r="AA270" s="79"/>
+      <c r="V270" s="71"/>
+      <c r="W270" s="86"/>
+      <c r="X270" s="86"/>
+      <c r="Y270" s="71"/>
+      <c r="Z270" s="81"/>
+      <c r="AA270" s="81"/>
     </row>
     <row r="271" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A271" s="26">
@@ -9512,12 +9548,12 @@
       <c r="Q271" s="25"/>
       <c r="R271" s="25"/>
       <c r="S271" s="27"/>
-      <c r="V271" s="69"/>
-      <c r="W271" s="84"/>
-      <c r="X271" s="84"/>
-      <c r="Y271" s="69"/>
-      <c r="Z271" s="79"/>
-      <c r="AA271" s="79"/>
+      <c r="V271" s="71"/>
+      <c r="W271" s="86"/>
+      <c r="X271" s="86"/>
+      <c r="Y271" s="71"/>
+      <c r="Z271" s="81"/>
+      <c r="AA271" s="81"/>
     </row>
     <row r="272" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A272" s="26">
@@ -9541,12 +9577,12 @@
       <c r="Q272" s="25"/>
       <c r="R272" s="25"/>
       <c r="S272" s="27"/>
-      <c r="V272" s="69"/>
-      <c r="W272" s="84"/>
-      <c r="X272" s="84"/>
-      <c r="Y272" s="69"/>
-      <c r="Z272" s="79"/>
-      <c r="AA272" s="79"/>
+      <c r="V272" s="71"/>
+      <c r="W272" s="86"/>
+      <c r="X272" s="86"/>
+      <c r="Y272" s="71"/>
+      <c r="Z272" s="81"/>
+      <c r="AA272" s="81"/>
     </row>
     <row r="273" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A273" s="26">
@@ -9570,12 +9606,12 @@
       <c r="Q273" s="25"/>
       <c r="R273" s="25"/>
       <c r="S273" s="27"/>
-      <c r="V273" s="69"/>
-      <c r="W273" s="84"/>
-      <c r="X273" s="84"/>
-      <c r="Y273" s="69"/>
-      <c r="Z273" s="79"/>
-      <c r="AA273" s="79"/>
+      <c r="V273" s="71"/>
+      <c r="W273" s="86"/>
+      <c r="X273" s="86"/>
+      <c r="Y273" s="71"/>
+      <c r="Z273" s="81"/>
+      <c r="AA273" s="81"/>
     </row>
     <row r="274" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A274" s="26">
@@ -9599,12 +9635,12 @@
       <c r="Q274" s="25"/>
       <c r="R274" s="25"/>
       <c r="S274" s="27"/>
-      <c r="V274" s="69"/>
-      <c r="W274" s="84"/>
-      <c r="X274" s="84"/>
-      <c r="Y274" s="69"/>
-      <c r="Z274" s="79"/>
-      <c r="AA274" s="79"/>
+      <c r="V274" s="71"/>
+      <c r="W274" s="86"/>
+      <c r="X274" s="86"/>
+      <c r="Y274" s="71"/>
+      <c r="Z274" s="81"/>
+      <c r="AA274" s="81"/>
     </row>
     <row r="275" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A275" s="26">
@@ -9628,12 +9664,12 @@
       <c r="Q275" s="25"/>
       <c r="R275" s="25"/>
       <c r="S275" s="27"/>
-      <c r="V275" s="69"/>
-      <c r="W275" s="84"/>
-      <c r="X275" s="84"/>
-      <c r="Y275" s="69"/>
-      <c r="Z275" s="79"/>
-      <c r="AA275" s="79"/>
+      <c r="V275" s="71"/>
+      <c r="W275" s="86"/>
+      <c r="X275" s="86"/>
+      <c r="Y275" s="71"/>
+      <c r="Z275" s="81"/>
+      <c r="AA275" s="81"/>
     </row>
     <row r="276" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A276" s="26">
@@ -9657,12 +9693,12 @@
       <c r="Q276" s="25"/>
       <c r="R276" s="25"/>
       <c r="S276" s="27"/>
-      <c r="V276" s="69"/>
-      <c r="W276" s="84"/>
-      <c r="X276" s="84"/>
-      <c r="Y276" s="69"/>
-      <c r="Z276" s="79"/>
-      <c r="AA276" s="79"/>
+      <c r="V276" s="71"/>
+      <c r="W276" s="86"/>
+      <c r="X276" s="86"/>
+      <c r="Y276" s="71"/>
+      <c r="Z276" s="81"/>
+      <c r="AA276" s="81"/>
     </row>
     <row r="277" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A277" s="26">
@@ -9686,12 +9722,12 @@
       <c r="Q277" s="25"/>
       <c r="R277" s="25"/>
       <c r="S277" s="27"/>
-      <c r="V277" s="69"/>
-      <c r="W277" s="84"/>
-      <c r="X277" s="84"/>
-      <c r="Y277" s="69"/>
-      <c r="Z277" s="79"/>
-      <c r="AA277" s="79"/>
+      <c r="V277" s="71"/>
+      <c r="W277" s="86"/>
+      <c r="X277" s="86"/>
+      <c r="Y277" s="71"/>
+      <c r="Z277" s="81"/>
+      <c r="AA277" s="81"/>
     </row>
     <row r="278" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A278" s="26">
@@ -9715,12 +9751,12 @@
       <c r="Q278" s="25"/>
       <c r="R278" s="25"/>
       <c r="S278" s="27"/>
-      <c r="V278" s="69"/>
-      <c r="W278" s="84"/>
-      <c r="X278" s="84"/>
-      <c r="Y278" s="69"/>
-      <c r="Z278" s="79"/>
-      <c r="AA278" s="79"/>
+      <c r="V278" s="71"/>
+      <c r="W278" s="86"/>
+      <c r="X278" s="86"/>
+      <c r="Y278" s="71"/>
+      <c r="Z278" s="81"/>
+      <c r="AA278" s="81"/>
     </row>
     <row r="279" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A279" s="26">
@@ -9744,12 +9780,12 @@
       <c r="Q279" s="25"/>
       <c r="R279" s="25"/>
       <c r="S279" s="27"/>
-      <c r="V279" s="69"/>
-      <c r="W279" s="84"/>
-      <c r="X279" s="84"/>
-      <c r="Y279" s="69"/>
-      <c r="Z279" s="79"/>
-      <c r="AA279" s="79"/>
+      <c r="V279" s="71"/>
+      <c r="W279" s="86"/>
+      <c r="X279" s="86"/>
+      <c r="Y279" s="71"/>
+      <c r="Z279" s="81"/>
+      <c r="AA279" s="81"/>
     </row>
     <row r="280" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A280" s="26">
@@ -9773,12 +9809,12 @@
       <c r="Q280" s="25"/>
       <c r="R280" s="25"/>
       <c r="S280" s="27"/>
-      <c r="V280" s="69"/>
-      <c r="W280" s="84"/>
-      <c r="X280" s="84"/>
-      <c r="Y280" s="69"/>
-      <c r="Z280" s="79"/>
-      <c r="AA280" s="79"/>
+      <c r="V280" s="71"/>
+      <c r="W280" s="86"/>
+      <c r="X280" s="86"/>
+      <c r="Y280" s="71"/>
+      <c r="Z280" s="81"/>
+      <c r="AA280" s="81"/>
     </row>
     <row r="281" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A281" s="26">
@@ -9802,12 +9838,12 @@
       <c r="Q281" s="25"/>
       <c r="R281" s="25"/>
       <c r="S281" s="27"/>
-      <c r="V281" s="69"/>
-      <c r="W281" s="84"/>
-      <c r="X281" s="84"/>
-      <c r="Y281" s="69"/>
-      <c r="Z281" s="79"/>
-      <c r="AA281" s="79"/>
+      <c r="V281" s="71"/>
+      <c r="W281" s="86"/>
+      <c r="X281" s="86"/>
+      <c r="Y281" s="71"/>
+      <c r="Z281" s="81"/>
+      <c r="AA281" s="81"/>
     </row>
     <row r="282" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A282" s="26">
@@ -9831,12 +9867,12 @@
       <c r="Q282" s="25"/>
       <c r="R282" s="25"/>
       <c r="S282" s="27"/>
-      <c r="V282" s="69"/>
-      <c r="W282" s="84"/>
-      <c r="X282" s="84"/>
-      <c r="Y282" s="69"/>
-      <c r="Z282" s="79"/>
-      <c r="AA282" s="79"/>
+      <c r="V282" s="71"/>
+      <c r="W282" s="86"/>
+      <c r="X282" s="86"/>
+      <c r="Y282" s="71"/>
+      <c r="Z282" s="81"/>
+      <c r="AA282" s="81"/>
     </row>
     <row r="283" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A283" s="26">
@@ -9860,12 +9896,12 @@
       <c r="Q283" s="25"/>
       <c r="R283" s="25"/>
       <c r="S283" s="27"/>
-      <c r="V283" s="69"/>
-      <c r="W283" s="84"/>
-      <c r="X283" s="84"/>
-      <c r="Y283" s="69"/>
-      <c r="Z283" s="79"/>
-      <c r="AA283" s="79"/>
+      <c r="V283" s="71"/>
+      <c r="W283" s="86"/>
+      <c r="X283" s="86"/>
+      <c r="Y283" s="71"/>
+      <c r="Z283" s="81"/>
+      <c r="AA283" s="81"/>
     </row>
     <row r="284" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A284" s="26">
@@ -9889,12 +9925,12 @@
       <c r="Q284" s="25"/>
       <c r="R284" s="25"/>
       <c r="S284" s="27"/>
-      <c r="V284" s="69"/>
-      <c r="W284" s="84"/>
-      <c r="X284" s="84"/>
-      <c r="Y284" s="69"/>
-      <c r="Z284" s="79"/>
-      <c r="AA284" s="79"/>
+      <c r="V284" s="71"/>
+      <c r="W284" s="86"/>
+      <c r="X284" s="86"/>
+      <c r="Y284" s="71"/>
+      <c r="Z284" s="81"/>
+      <c r="AA284" s="81"/>
     </row>
     <row r="285" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A285" s="26">
@@ -9918,12 +9954,12 @@
       <c r="Q285" s="25"/>
       <c r="R285" s="25"/>
       <c r="S285" s="27"/>
-      <c r="V285" s="69"/>
-      <c r="W285" s="84"/>
-      <c r="X285" s="84"/>
-      <c r="Y285" s="69"/>
-      <c r="Z285" s="79"/>
-      <c r="AA285" s="79"/>
+      <c r="V285" s="71"/>
+      <c r="W285" s="86"/>
+      <c r="X285" s="86"/>
+      <c r="Y285" s="71"/>
+      <c r="Z285" s="81"/>
+      <c r="AA285" s="81"/>
     </row>
     <row r="286" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A286" s="26">
@@ -9947,12 +9983,12 @@
       <c r="Q286" s="25"/>
       <c r="R286" s="25"/>
       <c r="S286" s="27"/>
-      <c r="V286" s="69"/>
-      <c r="W286" s="84"/>
-      <c r="X286" s="84"/>
-      <c r="Y286" s="69"/>
-      <c r="Z286" s="79"/>
-      <c r="AA286" s="79"/>
+      <c r="V286" s="71"/>
+      <c r="W286" s="86"/>
+      <c r="X286" s="86"/>
+      <c r="Y286" s="71"/>
+      <c r="Z286" s="81"/>
+      <c r="AA286" s="81"/>
     </row>
     <row r="287" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K287" s="23">
@@ -9963,46 +9999,46 @@
       </c>
     </row>
     <row r="288" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A288" s="80" t="s">
+      <c r="A288" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B288" s="80"/>
-      <c r="C288" s="80"/>
-      <c r="D288" s="80"/>
-      <c r="E288" s="80"/>
-      <c r="F288" s="81" t="s">
+      <c r="B288" s="82"/>
+      <c r="C288" s="82"/>
+      <c r="D288" s="82"/>
+      <c r="E288" s="82"/>
+      <c r="F288" s="83" t="s">
         <v>56</v>
       </c>
-      <c r="G288" s="81"/>
-      <c r="H288" s="81"/>
-      <c r="I288" s="81"/>
-      <c r="J288" s="81"/>
-      <c r="K288" s="81"/>
-      <c r="L288" s="81"/>
-      <c r="M288" s="81"/>
-      <c r="N288" s="81"/>
-      <c r="O288" s="81"/>
-      <c r="P288" s="81"/>
-      <c r="Q288" s="81"/>
-      <c r="R288" s="81"/>
-      <c r="S288" s="81"/>
-      <c r="T288" s="81"/>
+      <c r="G288" s="83"/>
+      <c r="H288" s="83"/>
+      <c r="I288" s="83"/>
+      <c r="J288" s="83"/>
+      <c r="K288" s="83"/>
+      <c r="L288" s="83"/>
+      <c r="M288" s="83"/>
+      <c r="N288" s="83"/>
+      <c r="O288" s="83"/>
+      <c r="P288" s="83"/>
+      <c r="Q288" s="83"/>
+      <c r="R288" s="83"/>
+      <c r="S288" s="83"/>
+      <c r="T288" s="83"/>
     </row>
     <row r="289" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F289" s="82"/>
-      <c r="G289" s="82"/>
-      <c r="H289" s="82"/>
-      <c r="V289" s="57" t="s">
+      <c r="F289" s="84"/>
+      <c r="G289" s="84"/>
+      <c r="H289" s="84"/>
+      <c r="V289" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="W289" s="57"/>
-      <c r="X289" s="57"/>
-      <c r="Y289" s="57"/>
-      <c r="Z289" s="57"/>
-      <c r="AA289" s="57"/>
+      <c r="W289" s="59"/>
+      <c r="X289" s="59"/>
+      <c r="Y289" s="59"/>
+      <c r="Z289" s="59"/>
+      <c r="AA289" s="59"/>
     </row>
     <row r="291" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A291" s="104" t="s">
+      <c r="A291" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B291" s="44" t="s">
@@ -10030,10 +10066,10 @@
       <c r="V291" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W291" s="90" t="s">
+      <c r="W291" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X291" s="90"/>
+      <c r="X291" s="92"/>
       <c r="Y291" s="13" t="s">
         <v>38</v>
       </c>
@@ -10045,7 +10081,7 @@
       </c>
     </row>
     <row r="292" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A292" s="105"/>
+      <c r="A292" s="43"/>
       <c r="B292" s="47"/>
       <c r="C292" s="48"/>
       <c r="D292" s="48"/>
@@ -10068,21 +10104,21 @@
       <c r="S292" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V292" s="69" t="str">
+      <c r="V292" s="71" t="str">
         <f>IF(K254="","",K254)</f>
         <v>{{DATES_RHBZ}}</v>
       </c>
-      <c r="W292" s="68" t="s">
+      <c r="W292" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="X292" s="84"/>
-      <c r="Y292" s="69">
+      <c r="X292" s="86"/>
+      <c r="Y292" s="71">
         <v>1</v>
       </c>
-      <c r="Z292" s="70" t="s">
+      <c r="Z292" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="AA292" s="79"/>
+      <c r="AA292" s="81"/>
     </row>
     <row r="293" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A293" s="26">
@@ -10109,13 +10145,15 @@
       <c r="P293" s="25"/>
       <c r="Q293" s="25"/>
       <c r="R293" s="25"/>
-      <c r="S293" s="27"/>
-      <c r="V293" s="69"/>
-      <c r="W293" s="84"/>
-      <c r="X293" s="84"/>
-      <c r="Y293" s="69"/>
-      <c r="Z293" s="70"/>
-      <c r="AA293" s="79"/>
+      <c r="S293" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="V293" s="71"/>
+      <c r="W293" s="86"/>
+      <c r="X293" s="86"/>
+      <c r="Y293" s="71"/>
+      <c r="Z293" s="72"/>
+      <c r="AA293" s="81"/>
     </row>
     <row r="294" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A294" s="26">
@@ -10139,12 +10177,12 @@
       <c r="Q294" s="25"/>
       <c r="R294" s="25"/>
       <c r="S294" s="27"/>
-      <c r="V294" s="69"/>
-      <c r="W294" s="84"/>
-      <c r="X294" s="84"/>
-      <c r="Y294" s="69"/>
-      <c r="Z294" s="70"/>
-      <c r="AA294" s="79"/>
+      <c r="V294" s="71"/>
+      <c r="W294" s="86"/>
+      <c r="X294" s="86"/>
+      <c r="Y294" s="71"/>
+      <c r="Z294" s="72"/>
+      <c r="AA294" s="81"/>
     </row>
     <row r="295" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A295" s="26">
@@ -10168,12 +10206,12 @@
       <c r="Q295" s="25"/>
       <c r="R295" s="25"/>
       <c r="S295" s="27"/>
-      <c r="V295" s="69"/>
-      <c r="W295" s="84"/>
-      <c r="X295" s="84"/>
-      <c r="Y295" s="69"/>
-      <c r="Z295" s="70"/>
-      <c r="AA295" s="79"/>
+      <c r="V295" s="71"/>
+      <c r="W295" s="86"/>
+      <c r="X295" s="86"/>
+      <c r="Y295" s="71"/>
+      <c r="Z295" s="72"/>
+      <c r="AA295" s="81"/>
     </row>
     <row r="296" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A296" s="26">
@@ -10197,12 +10235,12 @@
       <c r="Q296" s="25"/>
       <c r="R296" s="25"/>
       <c r="S296" s="27"/>
-      <c r="V296" s="69"/>
-      <c r="W296" s="84"/>
-      <c r="X296" s="84"/>
-      <c r="Y296" s="69"/>
-      <c r="Z296" s="70"/>
-      <c r="AA296" s="79"/>
+      <c r="V296" s="71"/>
+      <c r="W296" s="86"/>
+      <c r="X296" s="86"/>
+      <c r="Y296" s="71"/>
+      <c r="Z296" s="72"/>
+      <c r="AA296" s="81"/>
     </row>
     <row r="297" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A297" s="26">
@@ -10226,12 +10264,12 @@
       <c r="Q297" s="25"/>
       <c r="R297" s="25"/>
       <c r="S297" s="27"/>
-      <c r="V297" s="69"/>
-      <c r="W297" s="84"/>
-      <c r="X297" s="84"/>
-      <c r="Y297" s="69"/>
-      <c r="Z297" s="70"/>
-      <c r="AA297" s="79"/>
+      <c r="V297" s="71"/>
+      <c r="W297" s="86"/>
+      <c r="X297" s="86"/>
+      <c r="Y297" s="71"/>
+      <c r="Z297" s="72"/>
+      <c r="AA297" s="81"/>
     </row>
     <row r="298" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="26">
@@ -10255,21 +10293,21 @@
       <c r="Q298" s="25"/>
       <c r="R298" s="25"/>
       <c r="S298" s="27"/>
-      <c r="V298" s="69" t="str">
+      <c r="V298" s="71" t="str">
         <f>IF(L254="","",L254)</f>
         <v/>
       </c>
-      <c r="W298" s="68" t="s">
+      <c r="W298" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="X298" s="84"/>
-      <c r="Y298" s="69">
+      <c r="X298" s="86"/>
+      <c r="Y298" s="71">
         <v>1</v>
       </c>
-      <c r="Z298" s="91" t="s">
+      <c r="Z298" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="AA298" s="79"/>
+      <c r="AA298" s="81"/>
     </row>
     <row r="299" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A299" s="26">
@@ -10293,12 +10331,12 @@
       <c r="Q299" s="25"/>
       <c r="R299" s="25"/>
       <c r="S299" s="27"/>
-      <c r="V299" s="69"/>
-      <c r="W299" s="84"/>
-      <c r="X299" s="84"/>
-      <c r="Y299" s="69"/>
-      <c r="Z299" s="92"/>
-      <c r="AA299" s="79"/>
+      <c r="V299" s="71"/>
+      <c r="W299" s="86"/>
+      <c r="X299" s="86"/>
+      <c r="Y299" s="71"/>
+      <c r="Z299" s="94"/>
+      <c r="AA299" s="81"/>
     </row>
     <row r="300" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A300" s="26">
@@ -10322,12 +10360,12 @@
       <c r="Q300" s="25"/>
       <c r="R300" s="25"/>
       <c r="S300" s="27"/>
-      <c r="V300" s="69"/>
-      <c r="W300" s="84"/>
-      <c r="X300" s="84"/>
-      <c r="Y300" s="69"/>
-      <c r="Z300" s="92"/>
-      <c r="AA300" s="79"/>
+      <c r="V300" s="71"/>
+      <c r="W300" s="86"/>
+      <c r="X300" s="86"/>
+      <c r="Y300" s="71"/>
+      <c r="Z300" s="94"/>
+      <c r="AA300" s="81"/>
     </row>
     <row r="301" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A301" s="26">
@@ -10351,12 +10389,12 @@
       <c r="Q301" s="25"/>
       <c r="R301" s="25"/>
       <c r="S301" s="27"/>
-      <c r="V301" s="69"/>
-      <c r="W301" s="84"/>
-      <c r="X301" s="84"/>
-      <c r="Y301" s="69"/>
-      <c r="Z301" s="92"/>
-      <c r="AA301" s="79"/>
+      <c r="V301" s="71"/>
+      <c r="W301" s="86"/>
+      <c r="X301" s="86"/>
+      <c r="Y301" s="71"/>
+      <c r="Z301" s="94"/>
+      <c r="AA301" s="81"/>
     </row>
     <row r="302" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A302" s="26">
@@ -10380,12 +10418,12 @@
       <c r="Q302" s="25"/>
       <c r="R302" s="25"/>
       <c r="S302" s="27"/>
-      <c r="V302" s="69"/>
-      <c r="W302" s="84"/>
-      <c r="X302" s="84"/>
-      <c r="Y302" s="69"/>
-      <c r="Z302" s="92"/>
-      <c r="AA302" s="79"/>
+      <c r="V302" s="71"/>
+      <c r="W302" s="86"/>
+      <c r="X302" s="86"/>
+      <c r="Y302" s="71"/>
+      <c r="Z302" s="94"/>
+      <c r="AA302" s="81"/>
     </row>
     <row r="303" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A303" s="26">
@@ -10409,12 +10447,12 @@
       <c r="Q303" s="25"/>
       <c r="R303" s="25"/>
       <c r="S303" s="27"/>
-      <c r="V303" s="69"/>
-      <c r="W303" s="84"/>
-      <c r="X303" s="84"/>
-      <c r="Y303" s="69"/>
-      <c r="Z303" s="92"/>
-      <c r="AA303" s="79"/>
+      <c r="V303" s="71"/>
+      <c r="W303" s="86"/>
+      <c r="X303" s="86"/>
+      <c r="Y303" s="71"/>
+      <c r="Z303" s="94"/>
+      <c r="AA303" s="81"/>
     </row>
     <row r="304" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A304" s="26">
@@ -10438,12 +10476,12 @@
       <c r="Q304" s="25"/>
       <c r="R304" s="25"/>
       <c r="S304" s="27"/>
-      <c r="V304" s="69"/>
-      <c r="W304" s="84"/>
-      <c r="X304" s="84"/>
-      <c r="Y304" s="69"/>
-      <c r="Z304" s="93"/>
-      <c r="AA304" s="79"/>
+      <c r="V304" s="71"/>
+      <c r="W304" s="86"/>
+      <c r="X304" s="86"/>
+      <c r="Y304" s="71"/>
+      <c r="Z304" s="95"/>
+      <c r="AA304" s="81"/>
     </row>
     <row r="305" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A305" s="26">
@@ -10467,12 +10505,12 @@
       <c r="Q305" s="25"/>
       <c r="R305" s="25"/>
       <c r="S305" s="27"/>
-      <c r="V305" s="69"/>
-      <c r="W305" s="84"/>
-      <c r="X305" s="84"/>
-      <c r="Y305" s="69"/>
-      <c r="Z305" s="79"/>
-      <c r="AA305" s="79"/>
+      <c r="V305" s="71"/>
+      <c r="W305" s="86"/>
+      <c r="X305" s="86"/>
+      <c r="Y305" s="71"/>
+      <c r="Z305" s="81"/>
+      <c r="AA305" s="81"/>
     </row>
     <row r="306" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A306" s="26">
@@ -10496,12 +10534,12 @@
       <c r="Q306" s="25"/>
       <c r="R306" s="25"/>
       <c r="S306" s="27"/>
-      <c r="V306" s="69"/>
-      <c r="W306" s="84"/>
-      <c r="X306" s="84"/>
-      <c r="Y306" s="69"/>
-      <c r="Z306" s="79"/>
-      <c r="AA306" s="79"/>
+      <c r="V306" s="71"/>
+      <c r="W306" s="86"/>
+      <c r="X306" s="86"/>
+      <c r="Y306" s="71"/>
+      <c r="Z306" s="81"/>
+      <c r="AA306" s="81"/>
     </row>
     <row r="307" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A307" s="26">
@@ -10525,12 +10563,12 @@
       <c r="Q307" s="25"/>
       <c r="R307" s="25"/>
       <c r="S307" s="27"/>
-      <c r="V307" s="69"/>
-      <c r="W307" s="84"/>
-      <c r="X307" s="84"/>
-      <c r="Y307" s="69"/>
-      <c r="Z307" s="79"/>
-      <c r="AA307" s="79"/>
+      <c r="V307" s="71"/>
+      <c r="W307" s="86"/>
+      <c r="X307" s="86"/>
+      <c r="Y307" s="71"/>
+      <c r="Z307" s="81"/>
+      <c r="AA307" s="81"/>
     </row>
     <row r="308" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A308" s="26">
@@ -10554,12 +10592,12 @@
       <c r="Q308" s="25"/>
       <c r="R308" s="25"/>
       <c r="S308" s="27"/>
-      <c r="V308" s="69"/>
-      <c r="W308" s="84"/>
-      <c r="X308" s="84"/>
-      <c r="Y308" s="69"/>
-      <c r="Z308" s="79"/>
-      <c r="AA308" s="79"/>
+      <c r="V308" s="71"/>
+      <c r="W308" s="86"/>
+      <c r="X308" s="86"/>
+      <c r="Y308" s="71"/>
+      <c r="Z308" s="81"/>
+      <c r="AA308" s="81"/>
     </row>
     <row r="309" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A309" s="26">
@@ -10583,12 +10621,12 @@
       <c r="Q309" s="25"/>
       <c r="R309" s="25"/>
       <c r="S309" s="27"/>
-      <c r="V309" s="69"/>
-      <c r="W309" s="84"/>
-      <c r="X309" s="84"/>
-      <c r="Y309" s="69"/>
-      <c r="Z309" s="79"/>
-      <c r="AA309" s="79"/>
+      <c r="V309" s="71"/>
+      <c r="W309" s="86"/>
+      <c r="X309" s="86"/>
+      <c r="Y309" s="71"/>
+      <c r="Z309" s="81"/>
+      <c r="AA309" s="81"/>
     </row>
     <row r="310" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A310" s="26">
@@ -10612,12 +10650,12 @@
       <c r="Q310" s="25"/>
       <c r="R310" s="25"/>
       <c r="S310" s="27"/>
-      <c r="V310" s="69"/>
-      <c r="W310" s="84"/>
-      <c r="X310" s="84"/>
-      <c r="Y310" s="69"/>
-      <c r="Z310" s="79"/>
-      <c r="AA310" s="79"/>
+      <c r="V310" s="71"/>
+      <c r="W310" s="86"/>
+      <c r="X310" s="86"/>
+      <c r="Y310" s="71"/>
+      <c r="Z310" s="81"/>
+      <c r="AA310" s="81"/>
     </row>
     <row r="311" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A311" s="26">
@@ -10641,12 +10679,12 @@
       <c r="Q311" s="25"/>
       <c r="R311" s="25"/>
       <c r="S311" s="27"/>
-      <c r="V311" s="69"/>
-      <c r="W311" s="84"/>
-      <c r="X311" s="84"/>
-      <c r="Y311" s="69"/>
-      <c r="Z311" s="79"/>
-      <c r="AA311" s="79"/>
+      <c r="V311" s="71"/>
+      <c r="W311" s="86"/>
+      <c r="X311" s="86"/>
+      <c r="Y311" s="71"/>
+      <c r="Z311" s="81"/>
+      <c r="AA311" s="81"/>
     </row>
     <row r="312" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A312" s="26">
@@ -10670,12 +10708,12 @@
       <c r="Q312" s="25"/>
       <c r="R312" s="25"/>
       <c r="S312" s="27"/>
-      <c r="V312" s="69"/>
-      <c r="W312" s="84"/>
-      <c r="X312" s="84"/>
-      <c r="Y312" s="69"/>
-      <c r="Z312" s="79"/>
-      <c r="AA312" s="79"/>
+      <c r="V312" s="71"/>
+      <c r="W312" s="86"/>
+      <c r="X312" s="86"/>
+      <c r="Y312" s="71"/>
+      <c r="Z312" s="81"/>
+      <c r="AA312" s="81"/>
     </row>
     <row r="313" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A313" s="26">
@@ -10699,12 +10737,12 @@
       <c r="Q313" s="25"/>
       <c r="R313" s="25"/>
       <c r="S313" s="27"/>
-      <c r="V313" s="69"/>
-      <c r="W313" s="84"/>
-      <c r="X313" s="84"/>
-      <c r="Y313" s="69"/>
-      <c r="Z313" s="79"/>
-      <c r="AA313" s="79"/>
+      <c r="V313" s="71"/>
+      <c r="W313" s="86"/>
+      <c r="X313" s="86"/>
+      <c r="Y313" s="71"/>
+      <c r="Z313" s="81"/>
+      <c r="AA313" s="81"/>
     </row>
     <row r="314" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A314" s="26">
@@ -10728,12 +10766,12 @@
       <c r="Q314" s="25"/>
       <c r="R314" s="25"/>
       <c r="S314" s="27"/>
-      <c r="V314" s="69"/>
-      <c r="W314" s="84"/>
-      <c r="X314" s="84"/>
-      <c r="Y314" s="69"/>
-      <c r="Z314" s="79"/>
-      <c r="AA314" s="79"/>
+      <c r="V314" s="71"/>
+      <c r="W314" s="86"/>
+      <c r="X314" s="86"/>
+      <c r="Y314" s="71"/>
+      <c r="Z314" s="81"/>
+      <c r="AA314" s="81"/>
     </row>
     <row r="315" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A315" s="26">
@@ -10757,12 +10795,12 @@
       <c r="Q315" s="25"/>
       <c r="R315" s="25"/>
       <c r="S315" s="27"/>
-      <c r="V315" s="69"/>
-      <c r="W315" s="84"/>
-      <c r="X315" s="84"/>
-      <c r="Y315" s="69"/>
-      <c r="Z315" s="79"/>
-      <c r="AA315" s="79"/>
+      <c r="V315" s="71"/>
+      <c r="W315" s="86"/>
+      <c r="X315" s="86"/>
+      <c r="Y315" s="71"/>
+      <c r="Z315" s="81"/>
+      <c r="AA315" s="81"/>
     </row>
     <row r="316" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A316" s="26">
@@ -10786,12 +10824,12 @@
       <c r="Q316" s="25"/>
       <c r="R316" s="25"/>
       <c r="S316" s="27"/>
-      <c r="V316" s="69"/>
-      <c r="W316" s="84"/>
-      <c r="X316" s="84"/>
-      <c r="Y316" s="69"/>
-      <c r="Z316" s="79"/>
-      <c r="AA316" s="79"/>
+      <c r="V316" s="71"/>
+      <c r="W316" s="86"/>
+      <c r="X316" s="86"/>
+      <c r="Y316" s="71"/>
+      <c r="Z316" s="81"/>
+      <c r="AA316" s="81"/>
     </row>
     <row r="317" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A317" s="26">
@@ -10815,12 +10853,12 @@
       <c r="Q317" s="25"/>
       <c r="R317" s="25"/>
       <c r="S317" s="27"/>
-      <c r="V317" s="69"/>
-      <c r="W317" s="84"/>
-      <c r="X317" s="84"/>
-      <c r="Y317" s="69"/>
-      <c r="Z317" s="79"/>
-      <c r="AA317" s="79"/>
+      <c r="V317" s="71"/>
+      <c r="W317" s="86"/>
+      <c r="X317" s="86"/>
+      <c r="Y317" s="71"/>
+      <c r="Z317" s="81"/>
+      <c r="AA317" s="81"/>
     </row>
     <row r="318" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A318" s="26">
@@ -10844,12 +10882,12 @@
       <c r="Q318" s="25"/>
       <c r="R318" s="25"/>
       <c r="S318" s="27"/>
-      <c r="V318" s="69"/>
-      <c r="W318" s="84"/>
-      <c r="X318" s="84"/>
-      <c r="Y318" s="69"/>
-      <c r="Z318" s="79"/>
-      <c r="AA318" s="79"/>
+      <c r="V318" s="71"/>
+      <c r="W318" s="86"/>
+      <c r="X318" s="86"/>
+      <c r="Y318" s="71"/>
+      <c r="Z318" s="81"/>
+      <c r="AA318" s="81"/>
     </row>
     <row r="319" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A319" s="26">
@@ -10873,12 +10911,12 @@
       <c r="Q319" s="25"/>
       <c r="R319" s="25"/>
       <c r="S319" s="27"/>
-      <c r="V319" s="69"/>
-      <c r="W319" s="84"/>
-      <c r="X319" s="84"/>
-      <c r="Y319" s="69"/>
-      <c r="Z319" s="79"/>
-      <c r="AA319" s="79"/>
+      <c r="V319" s="71"/>
+      <c r="W319" s="86"/>
+      <c r="X319" s="86"/>
+      <c r="Y319" s="71"/>
+      <c r="Z319" s="81"/>
+      <c r="AA319" s="81"/>
     </row>
     <row r="320" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A320" s="26">
@@ -10902,12 +10940,12 @@
       <c r="Q320" s="25"/>
       <c r="R320" s="25"/>
       <c r="S320" s="27"/>
-      <c r="V320" s="69"/>
-      <c r="W320" s="84"/>
-      <c r="X320" s="84"/>
-      <c r="Y320" s="69"/>
-      <c r="Z320" s="79"/>
-      <c r="AA320" s="79"/>
+      <c r="V320" s="71"/>
+      <c r="W320" s="86"/>
+      <c r="X320" s="86"/>
+      <c r="Y320" s="71"/>
+      <c r="Z320" s="81"/>
+      <c r="AA320" s="81"/>
     </row>
     <row r="321" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A321" s="26">
@@ -10931,12 +10969,12 @@
       <c r="Q321" s="25"/>
       <c r="R321" s="25"/>
       <c r="S321" s="27"/>
-      <c r="V321" s="69"/>
-      <c r="W321" s="84"/>
-      <c r="X321" s="84"/>
-      <c r="Y321" s="69"/>
-      <c r="Z321" s="79"/>
-      <c r="AA321" s="79"/>
+      <c r="V321" s="71"/>
+      <c r="W321" s="86"/>
+      <c r="X321" s="86"/>
+      <c r="Y321" s="71"/>
+      <c r="Z321" s="81"/>
+      <c r="AA321" s="81"/>
     </row>
     <row r="322" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A322" s="26">
@@ -10960,12 +10998,12 @@
       <c r="Q322" s="25"/>
       <c r="R322" s="25"/>
       <c r="S322" s="27"/>
-      <c r="V322" s="69"/>
-      <c r="W322" s="84"/>
-      <c r="X322" s="84"/>
-      <c r="Y322" s="69"/>
-      <c r="Z322" s="79"/>
-      <c r="AA322" s="79"/>
+      <c r="V322" s="71"/>
+      <c r="W322" s="86"/>
+      <c r="X322" s="86"/>
+      <c r="Y322" s="71"/>
+      <c r="Z322" s="81"/>
+      <c r="AA322" s="81"/>
     </row>
     <row r="323" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A323" s="26">
@@ -10989,12 +11027,12 @@
       <c r="Q323" s="25"/>
       <c r="R323" s="25"/>
       <c r="S323" s="27"/>
-      <c r="V323" s="69"/>
-      <c r="W323" s="84"/>
-      <c r="X323" s="84"/>
-      <c r="Y323" s="69"/>
-      <c r="Z323" s="79"/>
-      <c r="AA323" s="79"/>
+      <c r="V323" s="71"/>
+      <c r="W323" s="86"/>
+      <c r="X323" s="86"/>
+      <c r="Y323" s="71"/>
+      <c r="Z323" s="81"/>
+      <c r="AA323" s="81"/>
     </row>
     <row r="324" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A324" s="26">
@@ -11018,12 +11056,12 @@
       <c r="Q324" s="25"/>
       <c r="R324" s="25"/>
       <c r="S324" s="27"/>
-      <c r="V324" s="69"/>
-      <c r="W324" s="84"/>
-      <c r="X324" s="84"/>
-      <c r="Y324" s="69"/>
-      <c r="Z324" s="79"/>
-      <c r="AA324" s="79"/>
+      <c r="V324" s="71"/>
+      <c r="W324" s="86"/>
+      <c r="X324" s="86"/>
+      <c r="Y324" s="71"/>
+      <c r="Z324" s="81"/>
+      <c r="AA324" s="81"/>
     </row>
     <row r="325" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K325" s="23">
@@ -11034,46 +11072,46 @@
       </c>
     </row>
     <row r="326" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A326" s="80" t="s">
+      <c r="A326" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B326" s="80"/>
-      <c r="C326" s="80"/>
-      <c r="D326" s="80"/>
-      <c r="E326" s="80"/>
-      <c r="F326" s="81" t="s">
+      <c r="B326" s="82"/>
+      <c r="C326" s="82"/>
+      <c r="D326" s="82"/>
+      <c r="E326" s="82"/>
+      <c r="F326" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="G326" s="81"/>
-      <c r="H326" s="81"/>
-      <c r="I326" s="81"/>
-      <c r="J326" s="81"/>
-      <c r="K326" s="81"/>
-      <c r="L326" s="81"/>
-      <c r="M326" s="81"/>
-      <c r="N326" s="81"/>
-      <c r="O326" s="81"/>
-      <c r="P326" s="81"/>
-      <c r="Q326" s="81"/>
-      <c r="R326" s="81"/>
-      <c r="S326" s="81"/>
-      <c r="T326" s="81"/>
+      <c r="G326" s="83"/>
+      <c r="H326" s="83"/>
+      <c r="I326" s="83"/>
+      <c r="J326" s="83"/>
+      <c r="K326" s="83"/>
+      <c r="L326" s="83"/>
+      <c r="M326" s="83"/>
+      <c r="N326" s="83"/>
+      <c r="O326" s="83"/>
+      <c r="P326" s="83"/>
+      <c r="Q326" s="83"/>
+      <c r="R326" s="83"/>
+      <c r="S326" s="83"/>
+      <c r="T326" s="83"/>
     </row>
     <row r="327" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="F327" s="82"/>
-      <c r="G327" s="82"/>
-      <c r="H327" s="82"/>
-      <c r="V327" s="57" t="s">
+      <c r="F327" s="84"/>
+      <c r="G327" s="84"/>
+      <c r="H327" s="84"/>
+      <c r="V327" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="W327" s="57"/>
-      <c r="X327" s="57"/>
-      <c r="Y327" s="57"/>
-      <c r="Z327" s="57"/>
-      <c r="AA327" s="57"/>
+      <c r="W327" s="59"/>
+      <c r="X327" s="59"/>
+      <c r="Y327" s="59"/>
+      <c r="Z327" s="59"/>
+      <c r="AA327" s="59"/>
     </row>
     <row r="329" spans="1:27" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A329" s="104" t="s">
+      <c r="A329" s="42" t="s">
         <v>42</v>
       </c>
       <c r="B329" s="44" t="s">
@@ -11101,10 +11139,10 @@
       <c r="V329" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="W329" s="90" t="s">
+      <c r="W329" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="X329" s="90"/>
+      <c r="X329" s="92"/>
       <c r="Y329" s="13" t="s">
         <v>38</v>
       </c>
@@ -11116,7 +11154,7 @@
       </c>
     </row>
     <row r="330" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="105"/>
+      <c r="A330" s="43"/>
       <c r="B330" s="47"/>
       <c r="C330" s="48"/>
       <c r="D330" s="48"/>
@@ -11139,21 +11177,21 @@
       <c r="S330" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="V330" s="69" t="str">
+      <c r="V330" s="71" t="str">
         <f>IF(K330="","",K330)</f>
         <v>{{DATES_USTAVY}}</v>
       </c>
-      <c r="W330" s="97" t="s">
+      <c r="W330" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="X330" s="97"/>
-      <c r="Y330" s="69">
+      <c r="X330" s="99"/>
+      <c r="Y330" s="71">
         <v>1</v>
       </c>
-      <c r="Z330" s="101" t="s">
+      <c r="Z330" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="AA330" s="79"/>
+      <c r="AA330" s="81"/>
     </row>
     <row r="331" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A331" s="26">
@@ -11180,13 +11218,15 @@
       <c r="P331" s="25"/>
       <c r="Q331" s="25"/>
       <c r="R331" s="25"/>
-      <c r="S331" s="27"/>
-      <c r="V331" s="69"/>
-      <c r="W331" s="97"/>
-      <c r="X331" s="97"/>
-      <c r="Y331" s="69"/>
-      <c r="Z331" s="102"/>
-      <c r="AA331" s="79"/>
+      <c r="S331" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="V331" s="71"/>
+      <c r="W331" s="99"/>
+      <c r="X331" s="99"/>
+      <c r="Y331" s="71"/>
+      <c r="Z331" s="104"/>
+      <c r="AA331" s="81"/>
     </row>
     <row r="332" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A332" s="26">
@@ -11210,12 +11250,12 @@
       <c r="Q332" s="25"/>
       <c r="R332" s="25"/>
       <c r="S332" s="27"/>
-      <c r="V332" s="69"/>
-      <c r="W332" s="97"/>
-      <c r="X332" s="97"/>
-      <c r="Y332" s="69"/>
-      <c r="Z332" s="102"/>
-      <c r="AA332" s="79"/>
+      <c r="V332" s="71"/>
+      <c r="W332" s="99"/>
+      <c r="X332" s="99"/>
+      <c r="Y332" s="71"/>
+      <c r="Z332" s="104"/>
+      <c r="AA332" s="81"/>
     </row>
     <row r="333" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A333" s="26">
@@ -11239,12 +11279,12 @@
       <c r="Q333" s="25"/>
       <c r="R333" s="25"/>
       <c r="S333" s="27"/>
-      <c r="V333" s="69"/>
-      <c r="W333" s="97"/>
-      <c r="X333" s="97"/>
-      <c r="Y333" s="69"/>
-      <c r="Z333" s="103"/>
-      <c r="AA333" s="79"/>
+      <c r="V333" s="71"/>
+      <c r="W333" s="99"/>
+      <c r="X333" s="99"/>
+      <c r="Y333" s="71"/>
+      <c r="Z333" s="105"/>
+      <c r="AA333" s="81"/>
     </row>
     <row r="334" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A334" s="26">
@@ -11268,21 +11308,21 @@
       <c r="Q334" s="25"/>
       <c r="R334" s="25"/>
       <c r="S334" s="27"/>
-      <c r="V334" s="69" t="str">
+      <c r="V334" s="71" t="str">
         <f>IF(L330="","",L330)</f>
         <v/>
       </c>
-      <c r="W334" s="97" t="s">
+      <c r="W334" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="X334" s="97"/>
-      <c r="Y334" s="69">
+      <c r="X334" s="99"/>
+      <c r="Y334" s="71">
         <v>1</v>
       </c>
-      <c r="Z334" s="101" t="s">
+      <c r="Z334" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="AA334" s="79"/>
+      <c r="AA334" s="81"/>
     </row>
     <row r="335" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A335" s="26">
@@ -11306,12 +11346,12 @@
       <c r="Q335" s="25"/>
       <c r="R335" s="25"/>
       <c r="S335" s="27"/>
-      <c r="V335" s="69"/>
-      <c r="W335" s="97"/>
-      <c r="X335" s="97"/>
-      <c r="Y335" s="69"/>
-      <c r="Z335" s="102"/>
-      <c r="AA335" s="79"/>
+      <c r="V335" s="71"/>
+      <c r="W335" s="99"/>
+      <c r="X335" s="99"/>
+      <c r="Y335" s="71"/>
+      <c r="Z335" s="104"/>
+      <c r="AA335" s="81"/>
     </row>
     <row r="336" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A336" s="26">
@@ -11335,12 +11375,12 @@
       <c r="Q336" s="25"/>
       <c r="R336" s="25"/>
       <c r="S336" s="27"/>
-      <c r="V336" s="69"/>
-      <c r="W336" s="97"/>
-      <c r="X336" s="97"/>
-      <c r="Y336" s="69"/>
-      <c r="Z336" s="102"/>
-      <c r="AA336" s="79"/>
+      <c r="V336" s="71"/>
+      <c r="W336" s="99"/>
+      <c r="X336" s="99"/>
+      <c r="Y336" s="71"/>
+      <c r="Z336" s="104"/>
+      <c r="AA336" s="81"/>
     </row>
     <row r="337" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A337" s="26">
@@ -11364,12 +11404,12 @@
       <c r="Q337" s="25"/>
       <c r="R337" s="25"/>
       <c r="S337" s="27"/>
-      <c r="V337" s="69"/>
-      <c r="W337" s="97"/>
-      <c r="X337" s="97"/>
-      <c r="Y337" s="69"/>
-      <c r="Z337" s="103"/>
-      <c r="AA337" s="79"/>
+      <c r="V337" s="71"/>
+      <c r="W337" s="99"/>
+      <c r="X337" s="99"/>
+      <c r="Y337" s="71"/>
+      <c r="Z337" s="105"/>
+      <c r="AA337" s="81"/>
     </row>
     <row r="338" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A338" s="26">
@@ -11393,21 +11433,21 @@
       <c r="Q338" s="25"/>
       <c r="R338" s="25"/>
       <c r="S338" s="27"/>
-      <c r="V338" s="98" t="str">
+      <c r="V338" s="100" t="str">
         <f>IF(M330="","",M330)</f>
         <v/>
       </c>
-      <c r="W338" s="97" t="s">
+      <c r="W338" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="X338" s="97"/>
-      <c r="Y338" s="69">
+      <c r="X338" s="99"/>
+      <c r="Y338" s="71">
         <v>1</v>
       </c>
-      <c r="Z338" s="101" t="s">
+      <c r="Z338" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="AA338" s="79"/>
+      <c r="AA338" s="81"/>
     </row>
     <row r="339" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A339" s="26">
@@ -11431,12 +11471,12 @@
       <c r="Q339" s="25"/>
       <c r="R339" s="25"/>
       <c r="S339" s="27"/>
-      <c r="V339" s="99"/>
-      <c r="W339" s="97"/>
-      <c r="X339" s="97"/>
-      <c r="Y339" s="69"/>
-      <c r="Z339" s="102"/>
-      <c r="AA339" s="79"/>
+      <c r="V339" s="101"/>
+      <c r="W339" s="99"/>
+      <c r="X339" s="99"/>
+      <c r="Y339" s="71"/>
+      <c r="Z339" s="104"/>
+      <c r="AA339" s="81"/>
     </row>
     <row r="340" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A340" s="26">
@@ -11460,12 +11500,12 @@
       <c r="Q340" s="25"/>
       <c r="R340" s="25"/>
       <c r="S340" s="27"/>
-      <c r="V340" s="99"/>
-      <c r="W340" s="97"/>
-      <c r="X340" s="97"/>
-      <c r="Y340" s="69"/>
-      <c r="Z340" s="102"/>
-      <c r="AA340" s="79"/>
+      <c r="V340" s="101"/>
+      <c r="W340" s="99"/>
+      <c r="X340" s="99"/>
+      <c r="Y340" s="71"/>
+      <c r="Z340" s="104"/>
+      <c r="AA340" s="81"/>
     </row>
     <row r="341" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A341" s="26">
@@ -11489,12 +11529,12 @@
       <c r="Q341" s="25"/>
       <c r="R341" s="25"/>
       <c r="S341" s="27"/>
-      <c r="V341" s="100"/>
-      <c r="W341" s="97"/>
-      <c r="X341" s="97"/>
-      <c r="Y341" s="69"/>
-      <c r="Z341" s="103"/>
-      <c r="AA341" s="79"/>
+      <c r="V341" s="102"/>
+      <c r="W341" s="99"/>
+      <c r="X341" s="99"/>
+      <c r="Y341" s="71"/>
+      <c r="Z341" s="105"/>
+      <c r="AA341" s="81"/>
     </row>
     <row r="342" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A342" s="26">
@@ -11518,21 +11558,21 @@
       <c r="Q342" s="25"/>
       <c r="R342" s="25"/>
       <c r="S342" s="27"/>
-      <c r="V342" s="98" t="str">
+      <c r="V342" s="100" t="str">
         <f>IF(N330="","",N330)</f>
         <v/>
       </c>
-      <c r="W342" s="97" t="s">
+      <c r="W342" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="X342" s="97"/>
-      <c r="Y342" s="69">
+      <c r="X342" s="99"/>
+      <c r="Y342" s="71">
         <v>1</v>
       </c>
-      <c r="Z342" s="96" t="s">
+      <c r="Z342" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AA342" s="79"/>
+      <c r="AA342" s="81"/>
     </row>
     <row r="343" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A343" s="26">
@@ -11556,12 +11596,12 @@
       <c r="Q343" s="25"/>
       <c r="R343" s="25"/>
       <c r="S343" s="27"/>
-      <c r="V343" s="99"/>
-      <c r="W343" s="97"/>
-      <c r="X343" s="97"/>
-      <c r="Y343" s="69"/>
-      <c r="Z343" s="96"/>
-      <c r="AA343" s="79"/>
+      <c r="V343" s="101"/>
+      <c r="W343" s="99"/>
+      <c r="X343" s="99"/>
+      <c r="Y343" s="71"/>
+      <c r="Z343" s="98"/>
+      <c r="AA343" s="81"/>
     </row>
     <row r="344" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A344" s="26">
@@ -11585,12 +11625,12 @@
       <c r="Q344" s="25"/>
       <c r="R344" s="25"/>
       <c r="S344" s="27"/>
-      <c r="V344" s="99"/>
-      <c r="W344" s="97"/>
-      <c r="X344" s="97"/>
-      <c r="Y344" s="69"/>
-      <c r="Z344" s="96"/>
-      <c r="AA344" s="79"/>
+      <c r="V344" s="101"/>
+      <c r="W344" s="99"/>
+      <c r="X344" s="99"/>
+      <c r="Y344" s="71"/>
+      <c r="Z344" s="98"/>
+      <c r="AA344" s="81"/>
     </row>
     <row r="345" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A345" s="26">
@@ -11614,12 +11654,12 @@
       <c r="Q345" s="25"/>
       <c r="R345" s="25"/>
       <c r="S345" s="27"/>
-      <c r="V345" s="100"/>
-      <c r="W345" s="97"/>
-      <c r="X345" s="97"/>
-      <c r="Y345" s="69"/>
-      <c r="Z345" s="96"/>
-      <c r="AA345" s="79"/>
+      <c r="V345" s="102"/>
+      <c r="W345" s="99"/>
+      <c r="X345" s="99"/>
+      <c r="Y345" s="71"/>
+      <c r="Z345" s="98"/>
+      <c r="AA345" s="81"/>
     </row>
     <row r="346" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A346" s="26">
@@ -11643,21 +11683,21 @@
       <c r="Q346" s="25"/>
       <c r="R346" s="25"/>
       <c r="S346" s="27"/>
-      <c r="V346" s="69" t="str">
+      <c r="V346" s="71" t="str">
         <f>IF(O330="","",O330)</f>
         <v/>
       </c>
-      <c r="W346" s="97" t="s">
+      <c r="W346" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="X346" s="97"/>
-      <c r="Y346" s="69">
+      <c r="X346" s="99"/>
+      <c r="Y346" s="71">
         <v>1</v>
       </c>
-      <c r="Z346" s="96" t="s">
+      <c r="Z346" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AA346" s="79"/>
+      <c r="AA346" s="81"/>
     </row>
     <row r="347" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A347" s="26">
@@ -11681,12 +11721,12 @@
       <c r="Q347" s="25"/>
       <c r="R347" s="25"/>
       <c r="S347" s="27"/>
-      <c r="V347" s="69"/>
-      <c r="W347" s="97"/>
-      <c r="X347" s="97"/>
-      <c r="Y347" s="69"/>
-      <c r="Z347" s="96"/>
-      <c r="AA347" s="79"/>
+      <c r="V347" s="71"/>
+      <c r="W347" s="99"/>
+      <c r="X347" s="99"/>
+      <c r="Y347" s="71"/>
+      <c r="Z347" s="98"/>
+      <c r="AA347" s="81"/>
     </row>
     <row r="348" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A348" s="26">
@@ -11710,12 +11750,12 @@
       <c r="Q348" s="25"/>
       <c r="R348" s="25"/>
       <c r="S348" s="27"/>
-      <c r="V348" s="69"/>
-      <c r="W348" s="97"/>
-      <c r="X348" s="97"/>
-      <c r="Y348" s="69"/>
-      <c r="Z348" s="96"/>
-      <c r="AA348" s="79"/>
+      <c r="V348" s="71"/>
+      <c r="W348" s="99"/>
+      <c r="X348" s="99"/>
+      <c r="Y348" s="71"/>
+      <c r="Z348" s="98"/>
+      <c r="AA348" s="81"/>
     </row>
     <row r="349" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A349" s="26">
@@ -11739,12 +11779,12 @@
       <c r="Q349" s="25"/>
       <c r="R349" s="25"/>
       <c r="S349" s="27"/>
-      <c r="V349" s="69"/>
-      <c r="W349" s="97"/>
-      <c r="X349" s="97"/>
-      <c r="Y349" s="69"/>
-      <c r="Z349" s="96"/>
-      <c r="AA349" s="79"/>
+      <c r="V349" s="71"/>
+      <c r="W349" s="99"/>
+      <c r="X349" s="99"/>
+      <c r="Y349" s="71"/>
+      <c r="Z349" s="98"/>
+      <c r="AA349" s="81"/>
     </row>
     <row r="350" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A350" s="26">
@@ -11768,21 +11808,21 @@
       <c r="Q350" s="25"/>
       <c r="R350" s="25"/>
       <c r="S350" s="27"/>
-      <c r="V350" s="69" t="str">
+      <c r="V350" s="71" t="str">
         <f>IF(P330="","",P330)</f>
         <v/>
       </c>
-      <c r="W350" s="97" t="s">
+      <c r="W350" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="X350" s="97"/>
-      <c r="Y350" s="69">
+      <c r="X350" s="99"/>
+      <c r="Y350" s="71">
         <v>1</v>
       </c>
-      <c r="Z350" s="96" t="s">
+      <c r="Z350" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AA350" s="79"/>
+      <c r="AA350" s="81"/>
     </row>
     <row r="351" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A351" s="26">
@@ -11806,12 +11846,12 @@
       <c r="Q351" s="25"/>
       <c r="R351" s="25"/>
       <c r="S351" s="27"/>
-      <c r="V351" s="69"/>
-      <c r="W351" s="97"/>
-      <c r="X351" s="97"/>
-      <c r="Y351" s="69"/>
-      <c r="Z351" s="96"/>
-      <c r="AA351" s="79"/>
+      <c r="V351" s="71"/>
+      <c r="W351" s="99"/>
+      <c r="X351" s="99"/>
+      <c r="Y351" s="71"/>
+      <c r="Z351" s="98"/>
+      <c r="AA351" s="81"/>
     </row>
     <row r="352" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A352" s="26">
@@ -11835,12 +11875,12 @@
       <c r="Q352" s="25"/>
       <c r="R352" s="25"/>
       <c r="S352" s="27"/>
-      <c r="V352" s="69"/>
-      <c r="W352" s="97"/>
-      <c r="X352" s="97"/>
-      <c r="Y352" s="69"/>
-      <c r="Z352" s="96"/>
-      <c r="AA352" s="79"/>
+      <c r="V352" s="71"/>
+      <c r="W352" s="99"/>
+      <c r="X352" s="99"/>
+      <c r="Y352" s="71"/>
+      <c r="Z352" s="98"/>
+      <c r="AA352" s="81"/>
     </row>
     <row r="353" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A353" s="26">
@@ -11864,12 +11904,12 @@
       <c r="Q353" s="25"/>
       <c r="R353" s="25"/>
       <c r="S353" s="27"/>
-      <c r="V353" s="69"/>
-      <c r="W353" s="97"/>
-      <c r="X353" s="97"/>
-      <c r="Y353" s="69"/>
-      <c r="Z353" s="96"/>
-      <c r="AA353" s="79"/>
+      <c r="V353" s="71"/>
+      <c r="W353" s="99"/>
+      <c r="X353" s="99"/>
+      <c r="Y353" s="71"/>
+      <c r="Z353" s="98"/>
+      <c r="AA353" s="81"/>
     </row>
     <row r="354" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A354" s="26">
@@ -11893,12 +11933,12 @@
       <c r="Q354" s="25"/>
       <c r="R354" s="25"/>
       <c r="S354" s="27"/>
-      <c r="V354" s="69"/>
-      <c r="W354" s="97"/>
-      <c r="X354" s="97"/>
-      <c r="Y354" s="69"/>
-      <c r="Z354" s="96"/>
-      <c r="AA354" s="79"/>
+      <c r="V354" s="71"/>
+      <c r="W354" s="99"/>
+      <c r="X354" s="99"/>
+      <c r="Y354" s="71"/>
+      <c r="Z354" s="98"/>
+      <c r="AA354" s="81"/>
     </row>
     <row r="355" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A355" s="26">
@@ -11922,21 +11962,21 @@
       <c r="Q355" s="25"/>
       <c r="R355" s="25"/>
       <c r="S355" s="27"/>
-      <c r="V355" s="69" t="str">
+      <c r="V355" s="71" t="str">
         <f>IF(Q330="","",Q330)</f>
         <v/>
       </c>
-      <c r="W355" s="97" t="s">
+      <c r="W355" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="X355" s="97"/>
-      <c r="Y355" s="69">
+      <c r="X355" s="99"/>
+      <c r="Y355" s="71">
         <v>1</v>
       </c>
-      <c r="Z355" s="96" t="s">
+      <c r="Z355" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AA355" s="79"/>
+      <c r="AA355" s="81"/>
     </row>
     <row r="356" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A356" s="26">
@@ -11960,12 +12000,12 @@
       <c r="Q356" s="25"/>
       <c r="R356" s="25"/>
       <c r="S356" s="27"/>
-      <c r="V356" s="69"/>
-      <c r="W356" s="97"/>
-      <c r="X356" s="97"/>
-      <c r="Y356" s="69"/>
-      <c r="Z356" s="96"/>
-      <c r="AA356" s="79"/>
+      <c r="V356" s="71"/>
+      <c r="W356" s="99"/>
+      <c r="X356" s="99"/>
+      <c r="Y356" s="71"/>
+      <c r="Z356" s="98"/>
+      <c r="AA356" s="81"/>
     </row>
     <row r="357" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A357" s="26">
@@ -11989,12 +12029,12 @@
       <c r="Q357" s="25"/>
       <c r="R357" s="25"/>
       <c r="S357" s="27"/>
-      <c r="V357" s="69"/>
-      <c r="W357" s="97"/>
-      <c r="X357" s="97"/>
-      <c r="Y357" s="69"/>
-      <c r="Z357" s="96"/>
-      <c r="AA357" s="79"/>
+      <c r="V357" s="71"/>
+      <c r="W357" s="99"/>
+      <c r="X357" s="99"/>
+      <c r="Y357" s="71"/>
+      <c r="Z357" s="98"/>
+      <c r="AA357" s="81"/>
     </row>
     <row r="358" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A358" s="26">
@@ -12018,12 +12058,12 @@
       <c r="Q358" s="25"/>
       <c r="R358" s="25"/>
       <c r="S358" s="27"/>
-      <c r="V358" s="69"/>
-      <c r="W358" s="97"/>
-      <c r="X358" s="97"/>
-      <c r="Y358" s="69"/>
-      <c r="Z358" s="96"/>
-      <c r="AA358" s="79"/>
+      <c r="V358" s="71"/>
+      <c r="W358" s="99"/>
+      <c r="X358" s="99"/>
+      <c r="Y358" s="71"/>
+      <c r="Z358" s="98"/>
+      <c r="AA358" s="81"/>
     </row>
     <row r="359" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A359" s="26">
@@ -12047,12 +12087,12 @@
       <c r="Q359" s="25"/>
       <c r="R359" s="25"/>
       <c r="S359" s="27"/>
-      <c r="V359" s="69"/>
-      <c r="W359" s="97"/>
-      <c r="X359" s="97"/>
-      <c r="Y359" s="69"/>
-      <c r="Z359" s="96"/>
-      <c r="AA359" s="79"/>
+      <c r="V359" s="71"/>
+      <c r="W359" s="99"/>
+      <c r="X359" s="99"/>
+      <c r="Y359" s="71"/>
+      <c r="Z359" s="98"/>
+      <c r="AA359" s="81"/>
     </row>
     <row r="360" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A360" s="26">
@@ -12076,21 +12116,21 @@
       <c r="Q360" s="25"/>
       <c r="R360" s="25"/>
       <c r="S360" s="27"/>
-      <c r="V360" s="69" t="str">
+      <c r="V360" s="71" t="str">
         <f>IF(R330="","",R330)</f>
         <v/>
       </c>
-      <c r="W360" s="97" t="s">
+      <c r="W360" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="X360" s="97"/>
-      <c r="Y360" s="69">
+      <c r="X360" s="99"/>
+      <c r="Y360" s="71">
         <v>1</v>
       </c>
-      <c r="Z360" s="96" t="s">
+      <c r="Z360" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AA360" s="79"/>
+      <c r="AA360" s="81"/>
     </row>
     <row r="361" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A361" s="26">
@@ -12114,12 +12154,12 @@
       <c r="Q361" s="25"/>
       <c r="R361" s="25"/>
       <c r="S361" s="27"/>
-      <c r="V361" s="69"/>
-      <c r="W361" s="97"/>
-      <c r="X361" s="97"/>
-      <c r="Y361" s="69"/>
-      <c r="Z361" s="96"/>
-      <c r="AA361" s="79"/>
+      <c r="V361" s="71"/>
+      <c r="W361" s="99"/>
+      <c r="X361" s="99"/>
+      <c r="Y361" s="71"/>
+      <c r="Z361" s="98"/>
+      <c r="AA361" s="81"/>
     </row>
     <row r="362" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A362" s="26">
@@ -12143,12 +12183,12 @@
       <c r="Q362" s="25"/>
       <c r="R362" s="25"/>
       <c r="S362" s="27"/>
-      <c r="V362" s="69"/>
-      <c r="W362" s="97"/>
-      <c r="X362" s="97"/>
-      <c r="Y362" s="69"/>
-      <c r="Z362" s="96"/>
-      <c r="AA362" s="79"/>
+      <c r="V362" s="71"/>
+      <c r="W362" s="99"/>
+      <c r="X362" s="99"/>
+      <c r="Y362" s="71"/>
+      <c r="Z362" s="98"/>
+      <c r="AA362" s="81"/>
     </row>
     <row r="363" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K363" s="23">
